--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trece\Documents\Code\unked\mi-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49CC7FB5-BE62-4E5C-886F-078F2D57D9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D9C63B-6BD3-4D14-BE83-14A56DE141DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{15C9D418-315A-4B88-91DE-BBEFAE06072D}"/>
+    <workbookView xWindow="7305" yWindow="0" windowWidth="21600" windowHeight="11835" xr2:uid="{15C9D418-315A-4B88-91DE-BBEFAE06072D}"/>
   </bookViews>
   <sheets>
     <sheet name="TABLA" sheetId="2" r:id="rId1"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="G278" s="1"/>
       <c r="H278" s="1">
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>1459</v>

--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5725835-0323-4794-B0C7-B836627682E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6594E5E4-F67C-4ACA-9767-CE6F4C28FAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TABLA" sheetId="2" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="1509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="1518">
   <si>
     <t>id</t>
   </si>
@@ -18430,6 +18430,77 @@
   </si>
   <si>
     <t>https://i.postimg.cc/htGbkgSZ/497.png</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXKMHZmk-8g/</t>
+  </si>
+  <si>
+    <t>Cuando se habla de fútbol, no todo está inventando. Aquí vemos a Jan Virgili del Mallorca marcando con los dos pies a la vez.</t>
+  </si>
+  <si>
+    <t>El RCD Mallorca se enfrentó al Rayo Vallecano este domingo pasado y lo goleó 3-0 con dos goles del pirata del gol, Vedat Muriqi, y otro gol de Jan Virgili.</t>
+  </si>
+  <si>
+    <t>Este último gol se dio en el minuto 65 tras un centro al área de Pablo Torre, al que Virgili respondió pateando con los dos pies a la vez.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gol de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jan Virgili</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> con los </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dos pies</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a la vez</t>
+    </r>
+  </si>
+  <si>
+    <t>mallorca, laliga, jan virgili</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/zDTMMbWW/494.png</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/Sx5JnNdf/462.png</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/DwD8Sy6c/464.png</t>
   </si>
 </sst>
 </file>
@@ -18502,7 +18573,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -18510,6 +18581,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18844,7 +18916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S278"/>
+  <dimension ref="A1:S279"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.42578125" customWidth="1"/>
@@ -19959,7 +20031,7 @@
         <v>46047</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>169</v>
@@ -27569,6 +27641,9 @@
       <c r="I264" s="1" t="s">
         <v>1389</v>
       </c>
+      <c r="J264" s="7" t="s">
+        <v>1516</v>
+      </c>
       <c r="K264" s="3" t="s">
         <v>1390</v>
       </c>
@@ -27605,6 +27680,9 @@
       <c r="I265" s="1" t="s">
         <v>1395</v>
       </c>
+      <c r="J265" s="6" t="s">
+        <v>1517</v>
+      </c>
       <c r="K265" s="3" t="s">
         <v>1396</v>
       </c>
@@ -28035,7 +28113,7 @@
       </c>
       <c r="G276" s="1"/>
       <c r="H276" s="1">
-        <v>922000</v>
+        <v>1000000</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>1477</v>
@@ -28074,7 +28152,7 @@
       </c>
       <c r="G277" s="1"/>
       <c r="H277" s="1">
-        <v>4000000</v>
+        <v>5000000</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>1484</v>
@@ -28096,44 +28174,83 @@
       <c r="A278">
         <v>277</v>
       </c>
-      <c r="B278" s="6">
-        <v>497</v>
+      <c r="B278" s="1">
+        <v>494</v>
       </c>
       <c r="C278" s="2">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="D278" s="1" t="s">
         <v>39</v>
       </c>
       <c r="E278" s="6" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F278" s="6" t="s">
+        <v>1513</v>
+      </c>
+      <c r="G278" s="6"/>
+      <c r="H278" s="1">
+        <v>250000</v>
+      </c>
+      <c r="I278" s="6" t="s">
+        <v>1509</v>
+      </c>
+      <c r="J278" s="6" t="s">
+        <v>1515</v>
+      </c>
+      <c r="K278" s="3" t="s">
+        <v>1510</v>
+      </c>
+      <c r="L278" s="3" t="s">
+        <v>1511</v>
+      </c>
+      <c r="M278" s="3" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A279">
+        <v>278</v>
+      </c>
+      <c r="B279" s="6">
+        <v>497</v>
+      </c>
+      <c r="C279" s="2">
+        <v>46128</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E279" s="6" t="s">
         <v>1504</v>
       </c>
-      <c r="F278" s="6" t="s">
+      <c r="F279" s="6" t="s">
         <v>1503</v>
       </c>
-      <c r="G278" s="6"/>
-      <c r="H278" s="6">
-        <v>369000</v>
-      </c>
-      <c r="I278" s="6" t="s">
+      <c r="G279" s="6"/>
+      <c r="H279" s="6">
+        <v>950000</v>
+      </c>
+      <c r="I279" s="6" t="s">
         <v>1502</v>
       </c>
-      <c r="J278" s="6" t="s">
+      <c r="J279" s="6" t="s">
         <v>1508</v>
       </c>
-      <c r="K278" s="3" t="s">
+      <c r="K279" s="3" t="s">
         <v>1505</v>
       </c>
-      <c r="L278" s="3" t="s">
+      <c r="L279" s="3" t="s">
         <v>1506</v>
       </c>
-      <c r="M278" s="3" t="s">
+      <c r="M279" s="3" t="s">
         <v>1507</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6594E5E4-F67C-4ACA-9767-CE6F4C28FAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB31C76-9142-4C8A-94E7-E19191EF0CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="1518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="1538">
   <si>
     <t>id</t>
   </si>
@@ -18501,6 +18501,186 @@
   </si>
   <si>
     <t>https://i.postimg.cc/DwD8Sy6c/464.png</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXPpIl8E3Bn/</t>
+  </si>
+  <si>
+    <t>Esto ha ocurrido en la fase de grupos de la CONMEBOL Sudamericana.</t>
+  </si>
+  <si>
+    <t>EL Red Bull Bragantino de Brasil se ha enfrentado al Blooming de Bolivia cuando el argentino Diago Giménez ha cometido dos entradas dignas de carnicero a dos jugadores del Bragantino.</t>
+  </si>
+  <si>
+    <t>Insólito que tras esas dos entradas, encima se quejara al árbitro por su decisión de sacar dos tarjetas amarillas seguidas con su consiguiente expulsión.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2 tarjetas amarillas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en la misma jugada, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tarjeta roja</t>
+    </r>
+  </si>
+  <si>
+    <t>conmebol, brasil, argentina, bolivia</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXRGrC5E2p3/</t>
+  </si>
+  <si>
+    <t>¿Quién tiene más mala suerte, una víctima de la isla de Jeffrey Epstein o Pedro Buenpito?</t>
+  </si>
+  <si>
+    <t>En el último partido del Real Murcia en Primera RFEF, el delantero Pedro Benito tuvo la mala suerte de que una irregularidad en el césped le despejara un chute que iba directo a la red.</t>
+  </si>
+  <si>
+    <t>Para más inri, el partido acabó 2-3 a favor del Antequera, así que este gol hubiese cambiado el resultado de derrota a empate.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>césped</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> despeja un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gol</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> que estaba casi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>asegurado</t>
+    </r>
+  </si>
+  <si>
+    <t>primera rfef, real murcia, pedro benito</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXR-2q1E8Ox/</t>
+  </si>
+  <si>
+    <t>Así actúa un buen capitán. Como hizo Natxo Insa, el futbolista que pasó por equipos como el RC Celta, Valencia CF, Real Zaragoza o Levante UD.</t>
+  </si>
+  <si>
+    <t>Jugó ayer con su equipo, el Johor DT, en la primera división de Malasia, y pudimos ver su frustración cuando su compañero Jairo se encontraba en el suelo y pese a que pedían atención médica nadie del staff médico reaccionaba.</t>
+  </si>
+  <si>
+    <t>Como buen capitán, hizo todo lo posible para darle solución. Fue a quitarle el banderín al árbitro, y pegó un sprint para llegar donde los médicos y pateó al camillero para que despertara y fueran a atender a su compañero.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lo que haga falta para que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>atiendan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a su </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>compañero</t>
+    </r>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/Y07LYNPv/502.png</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/7h4J01RC/503.png</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/6qK4nVPy/505.png</t>
   </si>
 </sst>
 </file>
@@ -18573,7 +18753,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -18581,7 +18761,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18916,7 +19095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S279"/>
+  <dimension ref="A1:S282"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.42578125" customWidth="1"/>
@@ -27641,7 +27820,7 @@
       <c r="I264" s="1" t="s">
         <v>1389</v>
       </c>
-      <c r="J264" s="7" t="s">
+      <c r="J264" s="6" t="s">
         <v>1516</v>
       </c>
       <c r="K264" s="3" t="s">
@@ -28246,6 +28425,119 @@
       </c>
       <c r="M279" s="3" t="s">
         <v>1507</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A280">
+        <v>279</v>
+      </c>
+      <c r="B280" s="6">
+        <v>502</v>
+      </c>
+      <c r="C280" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E280" s="6" t="s">
+        <v>1523</v>
+      </c>
+      <c r="F280" s="6" t="s">
+        <v>1522</v>
+      </c>
+      <c r="G280" s="6"/>
+      <c r="H280" s="6">
+        <v>101000</v>
+      </c>
+      <c r="I280" s="6" t="s">
+        <v>1518</v>
+      </c>
+      <c r="J280" s="6" t="s">
+        <v>1535</v>
+      </c>
+      <c r="K280" s="3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="L280" s="3" t="s">
+        <v>1520</v>
+      </c>
+      <c r="M280" s="3" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A281">
+        <v>280</v>
+      </c>
+      <c r="B281" s="6">
+        <v>503</v>
+      </c>
+      <c r="C281" s="2">
+        <v>46129</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E281" s="6" t="s">
+        <v>1529</v>
+      </c>
+      <c r="F281" s="6" t="s">
+        <v>1528</v>
+      </c>
+      <c r="G281" s="6"/>
+      <c r="H281" s="6">
+        <v>100000</v>
+      </c>
+      <c r="I281" s="6" t="s">
+        <v>1524</v>
+      </c>
+      <c r="J281" s="6" t="s">
+        <v>1536</v>
+      </c>
+      <c r="K281" s="3" t="s">
+        <v>1525</v>
+      </c>
+      <c r="L281" s="3" t="s">
+        <v>1526</v>
+      </c>
+      <c r="M281" s="3" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A282">
+        <v>281</v>
+      </c>
+      <c r="B282" s="6">
+        <v>505</v>
+      </c>
+      <c r="C282" s="2">
+        <v>46130</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F282" s="6" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H282" s="6">
+        <v>1500000</v>
+      </c>
+      <c r="I282" s="6" t="s">
+        <v>1530</v>
+      </c>
+      <c r="J282" s="6" t="s">
+        <v>1537</v>
+      </c>
+      <c r="K282" s="3" t="s">
+        <v>1531</v>
+      </c>
+      <c r="L282" s="3" t="s">
+        <v>1532</v>
+      </c>
+      <c r="M282" s="3" t="s">
+        <v>1533</v>
       </c>
     </row>
   </sheetData>

--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB31C76-9142-4C8A-94E7-E19191EF0CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463F0708-2283-4EAC-89BF-AD9E188ABDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28292,7 +28292,7 @@
       </c>
       <c r="G276" s="1"/>
       <c r="H276" s="1">
-        <v>1000000</v>
+        <v>1100000</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>1477</v>
@@ -28331,7 +28331,7 @@
       </c>
       <c r="G277" s="1"/>
       <c r="H277" s="1">
-        <v>5000000</v>
+        <v>5500000</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>1484</v>
@@ -28370,7 +28370,7 @@
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="1">
-        <v>250000</v>
+        <v>402000</v>
       </c>
       <c r="I278" s="6" t="s">
         <v>1509</v>
@@ -28409,7 +28409,7 @@
       </c>
       <c r="G279" s="6"/>
       <c r="H279" s="6">
-        <v>950000</v>
+        <v>973000</v>
       </c>
       <c r="I279" s="6" t="s">
         <v>1502</v>

--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463F0708-2283-4EAC-89BF-AD9E188ABDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C32FB9-F32C-41D5-BBE9-0ED1ECD3E9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27005,7 +27005,7 @@
       </c>
       <c r="G242" s="1"/>
       <c r="H242" s="1">
-        <v>588000</v>
+        <v>589000</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>1249</v>
@@ -27445,7 +27445,7 @@
       </c>
       <c r="G254" s="1"/>
       <c r="H254" s="1">
-        <v>254000</v>
+        <v>255000</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>1325</v>
@@ -27519,7 +27519,7 @@
         <v>1336</v>
       </c>
       <c r="H256" s="1">
-        <v>742000</v>
+        <v>743000</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>1337</v>
@@ -27740,7 +27740,7 @@
       </c>
       <c r="G262" s="1"/>
       <c r="H262" s="1">
-        <v>500000</v>
+        <v>501000</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>1376</v>
@@ -27815,7 +27815,7 @@
       </c>
       <c r="G264" s="1"/>
       <c r="H264" s="1">
-        <v>134000</v>
+        <v>135000</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>1389</v>
@@ -27890,7 +27890,7 @@
       </c>
       <c r="G266" s="1"/>
       <c r="H266" s="1">
-        <v>182000</v>
+        <v>183000</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>1400</v>
@@ -27974,7 +27974,7 @@
       </c>
       <c r="G268" s="1"/>
       <c r="H268" s="1">
-        <v>100000</v>
+        <v>101000</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>1417</v>
@@ -28051,7 +28051,7 @@
         <v>1431</v>
       </c>
       <c r="H270" s="1">
-        <v>59000</v>
+        <v>60000</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>1432</v>
@@ -28129,7 +28129,7 @@
       </c>
       <c r="G272" s="1"/>
       <c r="H272" s="1">
-        <v>731000</v>
+        <v>733000</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>1446</v>
@@ -28170,7 +28170,7 @@
         <v>1453</v>
       </c>
       <c r="H273" s="1">
-        <v>331000</v>
+        <v>332000</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>1454</v>
@@ -28209,7 +28209,7 @@
       </c>
       <c r="G274" s="1"/>
       <c r="H274" s="1">
-        <v>204000</v>
+        <v>205000</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>1461</v>
@@ -28250,7 +28250,7 @@
         <v>1468</v>
       </c>
       <c r="H275" s="1">
-        <v>788000</v>
+        <v>789000</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>1469</v>

--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C32FB9-F32C-41D5-BBE9-0ED1ECD3E9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD126E1-EDFD-4559-AD82-907E91D3A0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28370,7 +28370,7 @@
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="1">
-        <v>402000</v>
+        <v>412000</v>
       </c>
       <c r="I278" s="6" t="s">
         <v>1509</v>
@@ -28448,7 +28448,7 @@
       </c>
       <c r="G280" s="6"/>
       <c r="H280" s="6">
-        <v>101000</v>
+        <v>102000</v>
       </c>
       <c r="I280" s="6" t="s">
         <v>1518</v>
@@ -28522,7 +28522,7 @@
         <v>1534</v>
       </c>
       <c r="H282" s="6">
-        <v>1500000</v>
+        <v>1600000</v>
       </c>
       <c r="I282" s="6" t="s">
         <v>1530</v>

--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD126E1-EDFD-4559-AD82-907E91D3A0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC67E34C-0F1E-42B9-B9AB-EC81A75835E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TABLA" sheetId="2" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="1538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="1553">
   <si>
     <t>id</t>
   </si>
@@ -18681,6 +18681,157 @@
   </si>
   <si>
     <t>https://i.postimg.cc/6qK4nVPy/505.png</t>
+  </si>
+  <si>
+    <t>copa del rey, atleti, cholo simeone, real sociedad</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXTxWhmk9Ok/</t>
+  </si>
+  <si>
+    <t>Esa es la Cholo Mentality.</t>
+  </si>
+  <si>
+    <t>Anoche se jugó la final de la Copa del Rey entre el Atlético de Madrid y la Real Sociedad, encuentro que terminó 2-2 y se decidió en penaltis, donde la Real se impuso y acabó alzando la copa.</t>
+  </si>
+  <si>
+    <t>Se trata de una final que el Cholo Simeone ha estado persiguiendo durante los últimos 13 años, y el primer tanto del equipo rival llegó a tan solo 14 segundos del pitido inicial. Pechofriada histórica del argentino.</t>
+  </si>
+  <si>
+    <r>
+      <t>13 años</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> persiguiendo una </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>final</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>copa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> para que te marquen a los </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>14 segundos</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXT6fJ1E5L5/</t>
+  </si>
+  <si>
+    <t>Cada jugador tiene sus tácticas para rendir más en el terreno de juego.</t>
+  </si>
+  <si>
+    <t>En la final de la Copa del Rey entre el Atlético de Madrid y la Real Sociedad, pudimos ver a Oyarzabal aplicando métodos que le han funcionado de forma regular a Bellingham, pero al parecer a él le sirvió para activar el modo Terreneitor y llevarse la copa.</t>
+  </si>
+  <si>
+    <t>Darío Eme Hache, que se encontraba narrando la retransmisión del partido junto a Ibai Llanos en su canal, se percató del suceso y comentó: "No hombre no, para rendir cubatas no, es mucho mejor darle a la línea de cal".</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Oyarzabal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> potando el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ron negrita</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> para reactivarse</t>
+    </r>
+  </si>
+  <si>
+    <t>Cositas de Bellingham</t>
+  </si>
+  <si>
+    <t>copa del rey, atleti, real sociedad, oyarzabal</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/MKsp1sW6/506.png</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/MKsp1sWZ/507.png</t>
   </si>
 </sst>
 </file>
@@ -19095,7 +19246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S282"/>
+  <dimension ref="A1:S284"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.42578125" customWidth="1"/>
@@ -28331,7 +28482,7 @@
       </c>
       <c r="G277" s="1"/>
       <c r="H277" s="1">
-        <v>5500000</v>
+        <v>5600000</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>1484</v>
@@ -28370,7 +28521,7 @@
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="1">
-        <v>412000</v>
+        <v>440000</v>
       </c>
       <c r="I278" s="6" t="s">
         <v>1509</v>
@@ -28409,7 +28560,7 @@
       </c>
       <c r="G279" s="6"/>
       <c r="H279" s="6">
-        <v>973000</v>
+        <v>975000</v>
       </c>
       <c r="I279" s="6" t="s">
         <v>1502</v>
@@ -28448,7 +28599,7 @@
       </c>
       <c r="G280" s="6"/>
       <c r="H280" s="6">
-        <v>102000</v>
+        <v>107000</v>
       </c>
       <c r="I280" s="6" t="s">
         <v>1518</v>
@@ -28487,7 +28638,7 @@
       </c>
       <c r="G281" s="6"/>
       <c r="H281" s="6">
-        <v>100000</v>
+        <v>109000</v>
       </c>
       <c r="I281" s="6" t="s">
         <v>1524</v>
@@ -28521,8 +28672,9 @@
       <c r="F282" s="6" t="s">
         <v>1534</v>
       </c>
+      <c r="G282" s="6"/>
       <c r="H282" s="6">
-        <v>1600000</v>
+        <v>2200000</v>
       </c>
       <c r="I282" s="6" t="s">
         <v>1530</v>
@@ -28538,6 +28690,86 @@
       </c>
       <c r="M282" s="3" t="s">
         <v>1533</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A283">
+        <v>282</v>
+      </c>
+      <c r="B283" s="6">
+        <v>506</v>
+      </c>
+      <c r="C283" s="2">
+        <v>46131</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E283" s="6" t="s">
+        <v>1538</v>
+      </c>
+      <c r="F283" s="5" t="s">
+        <v>1543</v>
+      </c>
+      <c r="G283" s="6"/>
+      <c r="H283" s="6">
+        <v>85000</v>
+      </c>
+      <c r="I283" s="6" t="s">
+        <v>1539</v>
+      </c>
+      <c r="J283" s="6" t="s">
+        <v>1551</v>
+      </c>
+      <c r="K283" s="3" t="s">
+        <v>1540</v>
+      </c>
+      <c r="L283" s="3" t="s">
+        <v>1541</v>
+      </c>
+      <c r="M283" s="3" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A284">
+        <v>283</v>
+      </c>
+      <c r="B284" s="6">
+        <v>507</v>
+      </c>
+      <c r="C284" s="2">
+        <v>46131</v>
+      </c>
+      <c r="D284" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E284" s="6" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F284" s="6" t="s">
+        <v>1548</v>
+      </c>
+      <c r="G284" s="6" t="s">
+        <v>1549</v>
+      </c>
+      <c r="H284" s="6">
+        <v>100000</v>
+      </c>
+      <c r="I284" s="6" t="s">
+        <v>1544</v>
+      </c>
+      <c r="J284" s="6" t="s">
+        <v>1552</v>
+      </c>
+      <c r="K284" s="3" t="s">
+        <v>1545</v>
+      </c>
+      <c r="L284" s="3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M284" s="3" t="s">
+        <v>1547</v>
       </c>
     </row>
   </sheetData>

--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC67E34C-0F1E-42B9-B9AB-EC81A75835E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB127B43-07EB-4FE7-A78F-4630A47C2F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28521,7 +28521,7 @@
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="1">
-        <v>440000</v>
+        <v>447000</v>
       </c>
       <c r="I278" s="6" t="s">
         <v>1509</v>
@@ -28599,7 +28599,7 @@
       </c>
       <c r="G280" s="6"/>
       <c r="H280" s="6">
-        <v>107000</v>
+        <v>108000</v>
       </c>
       <c r="I280" s="6" t="s">
         <v>1518</v>
@@ -28638,7 +28638,7 @@
       </c>
       <c r="G281" s="6"/>
       <c r="H281" s="6">
-        <v>109000</v>
+        <v>111000</v>
       </c>
       <c r="I281" s="6" t="s">
         <v>1524</v>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="G282" s="6"/>
       <c r="H282" s="6">
-        <v>2200000</v>
+        <v>2300000</v>
       </c>
       <c r="I282" s="6" t="s">
         <v>1530</v>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="G283" s="6"/>
       <c r="H283" s="6">
-        <v>85000</v>
+        <v>100000</v>
       </c>
       <c r="I283" s="6" t="s">
         <v>1539</v>
@@ -28754,7 +28754,7 @@
         <v>1549</v>
       </c>
       <c r="H284" s="6">
-        <v>100000</v>
+        <v>115000</v>
       </c>
       <c r="I284" s="6" t="s">
         <v>1544</v>

--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB127B43-07EB-4FE7-A78F-4630A47C2F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626815E1-9F39-48B5-900E-9595FC89513E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TABLA" sheetId="2" r:id="rId1"/>
@@ -28521,7 +28521,7 @@
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="1">
-        <v>447000</v>
+        <v>456000</v>
       </c>
       <c r="I278" s="6" t="s">
         <v>1509</v>
@@ -28560,7 +28560,7 @@
       </c>
       <c r="G279" s="6"/>
       <c r="H279" s="6">
-        <v>975000</v>
+        <v>976000</v>
       </c>
       <c r="I279" s="6" t="s">
         <v>1502</v>
@@ -28599,7 +28599,7 @@
       </c>
       <c r="G280" s="6"/>
       <c r="H280" s="6">
-        <v>108000</v>
+        <v>110000</v>
       </c>
       <c r="I280" s="6" t="s">
         <v>1518</v>
@@ -28638,7 +28638,7 @@
       </c>
       <c r="G281" s="6"/>
       <c r="H281" s="6">
-        <v>111000</v>
+        <v>113000</v>
       </c>
       <c r="I281" s="6" t="s">
         <v>1524</v>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="G283" s="6"/>
       <c r="H283" s="6">
-        <v>100000</v>
+        <v>125000</v>
       </c>
       <c r="I283" s="6" t="s">
         <v>1539</v>
@@ -28754,7 +28754,7 @@
         <v>1549</v>
       </c>
       <c r="H284" s="6">
-        <v>115000</v>
+        <v>149000</v>
       </c>
       <c r="I284" s="6" t="s">
         <v>1544</v>

--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626815E1-9F39-48B5-900E-9595FC89513E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E92998-A571-4ACC-A89E-3217BE0042D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28482,7 +28482,7 @@
       </c>
       <c r="G277" s="1"/>
       <c r="H277" s="1">
-        <v>5600000</v>
+        <v>5700000</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>1484</v>
@@ -28521,7 +28521,7 @@
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="1">
-        <v>456000</v>
+        <v>498000</v>
       </c>
       <c r="I278" s="6" t="s">
         <v>1509</v>
@@ -28560,7 +28560,7 @@
       </c>
       <c r="G279" s="6"/>
       <c r="H279" s="6">
-        <v>976000</v>
+        <v>978000</v>
       </c>
       <c r="I279" s="6" t="s">
         <v>1502</v>
@@ -28599,7 +28599,7 @@
       </c>
       <c r="G280" s="6"/>
       <c r="H280" s="6">
-        <v>110000</v>
+        <v>114000</v>
       </c>
       <c r="I280" s="6" t="s">
         <v>1518</v>
@@ -28638,7 +28638,7 @@
       </c>
       <c r="G281" s="6"/>
       <c r="H281" s="6">
-        <v>113000</v>
+        <v>121000</v>
       </c>
       <c r="I281" s="6" t="s">
         <v>1524</v>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="G283" s="6"/>
       <c r="H283" s="6">
-        <v>125000</v>
+        <v>215000</v>
       </c>
       <c r="I283" s="6" t="s">
         <v>1539</v>
@@ -28754,7 +28754,7 @@
         <v>1549</v>
       </c>
       <c r="H284" s="6">
-        <v>149000</v>
+        <v>271000</v>
       </c>
       <c r="I284" s="6" t="s">
         <v>1544</v>

--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E92998-A571-4ACC-A89E-3217BE0042D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F12C30-5160-4E8D-B0F1-2CC6C5F6FD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="1553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="1560">
   <si>
     <t>id</t>
   </si>
@@ -18832,6 +18832,100 @@
   </si>
   <si>
     <t>https://i.postimg.cc/MKsp1sWZ/507.png</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXUAoP0E5eL/</t>
+  </si>
+  <si>
+    <t>copa del rey, atleti, real sociedad, rtve</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RTVE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tenía preparado el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cartel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> del </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Atleti</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ganando la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>copa</t>
+    </r>
+  </si>
+  <si>
+    <t>En la retransmisión de La1 de Radio Televisión Española de la final de la Copa del Rey, ocurrió un percance.</t>
+  </si>
+  <si>
+    <t>Una vez acabado el partido y con la victoria de la Real Sociedad frente al Atlético de Madrid, conectaron con el reportero que se encontraba en San Sebastián para cubrir la celebración de los aficionados de la Real.</t>
+  </si>
+  <si>
+    <t>Pero intervino la mala pata y el cartelito que mostraron fue describiendo la celebración del Atleti, ya que por lo visto ese era el grafismo que tenían preparado para el final del partido.</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/MKtJbB5Y/508.png</t>
   </si>
 </sst>
 </file>
@@ -19246,7 +19340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S284"/>
+  <dimension ref="A1:S285"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.42578125" customWidth="1"/>
@@ -28443,7 +28537,7 @@
       </c>
       <c r="G276" s="1"/>
       <c r="H276" s="1">
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>1477</v>
@@ -28482,7 +28576,7 @@
       </c>
       <c r="G277" s="1"/>
       <c r="H277" s="1">
-        <v>5700000</v>
+        <v>6100000</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>1484</v>
@@ -28521,7 +28615,7 @@
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="1">
-        <v>498000</v>
+        <v>625000</v>
       </c>
       <c r="I278" s="6" t="s">
         <v>1509</v>
@@ -28560,7 +28654,7 @@
       </c>
       <c r="G279" s="6"/>
       <c r="H279" s="6">
-        <v>978000</v>
+        <v>982000</v>
       </c>
       <c r="I279" s="6" t="s">
         <v>1502</v>
@@ -28599,7 +28693,7 @@
       </c>
       <c r="G280" s="6"/>
       <c r="H280" s="6">
-        <v>114000</v>
+        <v>128000</v>
       </c>
       <c r="I280" s="6" t="s">
         <v>1518</v>
@@ -28638,7 +28732,7 @@
       </c>
       <c r="G281" s="6"/>
       <c r="H281" s="6">
-        <v>121000</v>
+        <v>136000</v>
       </c>
       <c r="I281" s="6" t="s">
         <v>1524</v>
@@ -28713,7 +28807,7 @@
       </c>
       <c r="G283" s="6"/>
       <c r="H283" s="6">
-        <v>215000</v>
+        <v>445000</v>
       </c>
       <c r="I283" s="6" t="s">
         <v>1539</v>
@@ -28754,7 +28848,7 @@
         <v>1549</v>
       </c>
       <c r="H284" s="6">
-        <v>271000</v>
+        <v>441000</v>
       </c>
       <c r="I284" s="6" t="s">
         <v>1544</v>
@@ -28770,6 +28864,45 @@
       </c>
       <c r="M284" s="3" t="s">
         <v>1547</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A285">
+        <v>284</v>
+      </c>
+      <c r="B285" s="6">
+        <v>508</v>
+      </c>
+      <c r="C285" s="2">
+        <v>46131</v>
+      </c>
+      <c r="D285" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E285" s="6" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F285" s="6" t="s">
+        <v>1555</v>
+      </c>
+      <c r="G285" s="6"/>
+      <c r="H285" s="6">
+        <v>245000</v>
+      </c>
+      <c r="I285" s="6" t="s">
+        <v>1553</v>
+      </c>
+      <c r="J285" s="6" t="s">
+        <v>1559</v>
+      </c>
+      <c r="K285" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="L285" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="M285" s="3" t="s">
+        <v>1558</v>
       </c>
     </row>
   </sheetData>

--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F12C30-5160-4E8D-B0F1-2CC6C5F6FD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A2FFB4-913E-4F6E-92AB-F484577A4D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TABLA" sheetId="2" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="1560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="1566">
   <si>
     <t>id</t>
   </si>
@@ -18926,6 +18926,58 @@
   </si>
   <si>
     <t>https://i.postimg.cc/MKtJbB5Y/508.png</t>
+  </si>
+  <si>
+    <t>chiringuito, brad pitt, juanma rodríguez</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para cuando te hablen de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>injusticias</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fútbol</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXPXiLKDPtM/</t>
+  </si>
+  <si>
+    <t>Hablando sobre el partido de Bayern de Múnich - Real Madrid de Champions en el programa de radio El Primer Palo, el reconocido periodista Juanma Rodríguez tuvo que dar su opinión.</t>
+  </si>
+  <si>
+    <t>El también tertuliano de El Chiringuito de Jugones dio su opinión sobre el concepto de argumentar de justicia o injusticia en el fútbol extrapolándolo a una temática más cruda y real.</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/kgVpv5G5/501.png</t>
   </si>
 </sst>
 </file>
@@ -19340,7 +19392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S285"/>
+  <dimension ref="A1:S286"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.42578125" customWidth="1"/>
@@ -28576,7 +28628,7 @@
       </c>
       <c r="G277" s="1"/>
       <c r="H277" s="1">
-        <v>6100000</v>
+        <v>7000000</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>1484</v>
@@ -28615,7 +28667,7 @@
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="1">
-        <v>625000</v>
+        <v>917000</v>
       </c>
       <c r="I278" s="6" t="s">
         <v>1509</v>
@@ -28654,7 +28706,7 @@
       </c>
       <c r="G279" s="6"/>
       <c r="H279" s="6">
-        <v>982000</v>
+        <v>997000</v>
       </c>
       <c r="I279" s="6" t="s">
         <v>1502</v>
@@ -28677,7 +28729,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="6">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C280" s="2">
         <v>46129</v>
@@ -28686,29 +28738,26 @@
         <v>39</v>
       </c>
       <c r="E280" s="6" t="s">
-        <v>1523</v>
+        <v>1560</v>
       </c>
       <c r="F280" s="6" t="s">
-        <v>1522</v>
+        <v>1561</v>
       </c>
       <c r="G280" s="6"/>
       <c r="H280" s="6">
-        <v>128000</v>
+        <v>87000</v>
       </c>
       <c r="I280" s="6" t="s">
-        <v>1518</v>
+        <v>1562</v>
       </c>
       <c r="J280" s="6" t="s">
-        <v>1535</v>
+        <v>1565</v>
       </c>
       <c r="K280" s="3" t="s">
-        <v>1519</v>
+        <v>1563</v>
       </c>
       <c r="L280" s="3" t="s">
-        <v>1520</v>
-      </c>
-      <c r="M280" s="3" t="s">
-        <v>1521</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="281" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -28716,7 +28765,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="6">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C281" s="2">
         <v>46129</v>
@@ -28725,29 +28774,29 @@
         <v>39</v>
       </c>
       <c r="E281" s="6" t="s">
-        <v>1529</v>
+        <v>1523</v>
       </c>
       <c r="F281" s="6" t="s">
-        <v>1528</v>
+        <v>1522</v>
       </c>
       <c r="G281" s="6"/>
       <c r="H281" s="6">
-        <v>136000</v>
+        <v>188000</v>
       </c>
       <c r="I281" s="6" t="s">
-        <v>1524</v>
+        <v>1518</v>
       </c>
       <c r="J281" s="6" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="K281" s="3" t="s">
-        <v>1525</v>
+        <v>1519</v>
       </c>
       <c r="L281" s="3" t="s">
-        <v>1526</v>
+        <v>1520</v>
       </c>
       <c r="M281" s="3" t="s">
-        <v>1527</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="282" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -28755,35 +28804,38 @@
         <v>281</v>
       </c>
       <c r="B282" s="6">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C282" s="2">
-        <v>46130</v>
+        <v>46129</v>
       </c>
       <c r="D282" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="E282" s="6" t="s">
+        <v>1529</v>
+      </c>
       <c r="F282" s="6" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
       <c r="G282" s="6"/>
       <c r="H282" s="6">
-        <v>2300000</v>
+        <v>174000</v>
       </c>
       <c r="I282" s="6" t="s">
-        <v>1530</v>
+        <v>1524</v>
       </c>
       <c r="J282" s="6" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="K282" s="3" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
       <c r="L282" s="3" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
       <c r="M282" s="3" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="283" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -28791,38 +28843,35 @@
         <v>282</v>
       </c>
       <c r="B283" s="6">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C283" s="2">
-        <v>46131</v>
+        <v>46130</v>
       </c>
       <c r="D283" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E283" s="6" t="s">
-        <v>1538</v>
-      </c>
-      <c r="F283" s="5" t="s">
-        <v>1543</v>
+      <c r="F283" s="6" t="s">
+        <v>1534</v>
       </c>
       <c r="G283" s="6"/>
       <c r="H283" s="6">
-        <v>445000</v>
+        <v>2400000</v>
       </c>
       <c r="I283" s="6" t="s">
-        <v>1539</v>
+        <v>1530</v>
       </c>
       <c r="J283" s="6" t="s">
-        <v>1551</v>
+        <v>1537</v>
       </c>
       <c r="K283" s="3" t="s">
-        <v>1540</v>
+        <v>1531</v>
       </c>
       <c r="L283" s="3" t="s">
-        <v>1541</v>
+        <v>1532</v>
       </c>
       <c r="M283" s="3" t="s">
-        <v>1542</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="284" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -28830,40 +28879,38 @@
         <v>283</v>
       </c>
       <c r="B284" s="6">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C284" s="2">
         <v>46131</v>
       </c>
-      <c r="D284" s="6" t="s">
+      <c r="D284" s="1" t="s">
         <v>39</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>1550</v>
-      </c>
-      <c r="F284" s="6" t="s">
-        <v>1548</v>
-      </c>
-      <c r="G284" s="6" t="s">
-        <v>1549</v>
-      </c>
+        <v>1538</v>
+      </c>
+      <c r="F284" s="5" t="s">
+        <v>1543</v>
+      </c>
+      <c r="G284" s="6"/>
       <c r="H284" s="6">
-        <v>441000</v>
+        <v>593000</v>
       </c>
       <c r="I284" s="6" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="J284" s="6" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="K284" s="3" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="L284" s="3" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="M284" s="3" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="285" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -28871,7 +28918,7 @@
         <v>284</v>
       </c>
       <c r="B285" s="6">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C285" s="2">
         <v>46131</v>
@@ -28880,28 +28927,66 @@
         <v>39</v>
       </c>
       <c r="E285" s="6" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F285" s="6" t="s">
+        <v>1548</v>
+      </c>
+      <c r="G285" s="6" t="s">
+        <v>1549</v>
+      </c>
+      <c r="H285" s="6">
+        <v>530000</v>
+      </c>
+      <c r="I285" s="6" t="s">
+        <v>1544</v>
+      </c>
+      <c r="J285" s="6" t="s">
+        <v>1552</v>
+      </c>
+      <c r="K285" s="3" t="s">
+        <v>1545</v>
+      </c>
+      <c r="L285" s="3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M285" s="3" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="286" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B286" s="6">
+        <v>508</v>
+      </c>
+      <c r="C286" s="2">
+        <v>46131</v>
+      </c>
+      <c r="D286" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E286" s="6" t="s">
         <v>1554</v>
       </c>
-      <c r="F285" s="6" t="s">
+      <c r="F286" s="6" t="s">
         <v>1555</v>
       </c>
-      <c r="G285" s="6"/>
-      <c r="H285" s="6">
-        <v>245000</v>
-      </c>
-      <c r="I285" s="6" t="s">
+      <c r="G286" s="6"/>
+      <c r="H286" s="6">
+        <v>307000</v>
+      </c>
+      <c r="I286" s="6" t="s">
         <v>1553</v>
       </c>
-      <c r="J285" s="6" t="s">
+      <c r="J286" s="6" t="s">
         <v>1559</v>
       </c>
-      <c r="K285" s="3" t="s">
+      <c r="K286" s="3" t="s">
         <v>1556</v>
       </c>
-      <c r="L285" s="3" t="s">
+      <c r="L286" s="3" t="s">
         <v>1557</v>
       </c>
-      <c r="M285" s="3" t="s">
+      <c r="M286" s="3" t="s">
         <v>1558</v>
       </c>
     </row>

--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A2FFB4-913E-4F6E-92AB-F484577A4D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA243E3-1F8B-4517-BB67-8C523CADF64F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="1566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="1573">
   <si>
     <t>id</t>
   </si>
@@ -18978,6 +18978,89 @@
   </si>
   <si>
     <t>https://i.postimg.cc/kgVpv5G5/501.png</t>
+  </si>
+  <si>
+    <t>rayo vallecano, laliga</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Aficionado</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> del </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rayo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: "No, a mí no, que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>yo no juego</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXgY2Jok8ja/</t>
+  </si>
+  <si>
+    <t>¡Momento digno de La Sotanita!</t>
+  </si>
+  <si>
+    <t>En el partido de liga entre el Rayo Vallecano y el Espanyol disputado en el Estadio de Vallecas, el centrocampista Óscar Valentín realizó este desacertado pase que parecía más dirigido hacia la grada que hacia un compañero, lo que provocó que un aficionado le hiciera gestos haciéndole saber que él no jugaba.</t>
+  </si>
+  <si>
+    <t>El encuentro terminó en 1-0 a favor del Rayo Vallecano con gol de Sergio Camello en el minuto 87.</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/tRr3dNG1/516.png</t>
   </si>
 </sst>
 </file>
@@ -19392,7 +19475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S286"/>
+  <dimension ref="A1:S287"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.42578125" customWidth="1"/>
@@ -25702,7 +25785,7 @@
       </c>
       <c r="G196" s="1"/>
       <c r="H196" s="1">
-        <v>90000</v>
+        <v>91000</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>978</v>
@@ -25966,7 +26049,7 @@
       </c>
       <c r="G204" s="1"/>
       <c r="H204" s="1">
-        <v>470000</v>
+        <v>471000</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>1021</v>
@@ -26409,7 +26492,7 @@
       </c>
       <c r="G217" s="1"/>
       <c r="H217" s="1">
-        <v>245000</v>
+        <v>246000</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>1094</v>
@@ -26507,7 +26590,7 @@
       </c>
       <c r="G220" s="1"/>
       <c r="H220" s="1">
-        <v>427000</v>
+        <v>428000</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>1111</v>
@@ -26781,7 +26864,7 @@
       </c>
       <c r="G228" s="1"/>
       <c r="H228" s="1">
-        <v>150000</v>
+        <v>151000</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>1157</v>
@@ -27529,7 +27612,7 @@
       </c>
       <c r="G248" s="1"/>
       <c r="H248" s="1">
-        <v>783000</v>
+        <v>784000</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>1289</v>
@@ -27816,7 +27899,7 @@
         <v>1336</v>
       </c>
       <c r="H256" s="1">
-        <v>743000</v>
+        <v>744000</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>1337</v>
@@ -27891,7 +27974,7 @@
       </c>
       <c r="G258" s="1"/>
       <c r="H258" s="1">
-        <v>130000</v>
+        <v>131000</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>1350</v>
@@ -28076,7 +28159,7 @@
       </c>
       <c r="G263" s="1"/>
       <c r="H263" s="1">
-        <v>287000</v>
+        <v>288000</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>1383</v>
@@ -28229,7 +28312,7 @@
       </c>
       <c r="G267" s="1"/>
       <c r="H267" s="1">
-        <v>130000</v>
+        <v>131000</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>1409</v>
@@ -28426,7 +28509,7 @@
       </c>
       <c r="G272" s="1"/>
       <c r="H272" s="1">
-        <v>733000</v>
+        <v>734000</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>1446</v>
@@ -28506,7 +28589,7 @@
       </c>
       <c r="G274" s="1"/>
       <c r="H274" s="1">
-        <v>205000</v>
+        <v>206000</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>1461</v>
@@ -28547,7 +28630,7 @@
         <v>1468</v>
       </c>
       <c r="H275" s="1">
-        <v>789000</v>
+        <v>790000</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>1469</v>
@@ -28589,7 +28672,7 @@
       </c>
       <c r="G276" s="1"/>
       <c r="H276" s="1">
-        <v>1200000</v>
+        <v>1300000</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>1477</v>
@@ -28628,7 +28711,7 @@
       </c>
       <c r="G277" s="1"/>
       <c r="H277" s="1">
-        <v>7000000</v>
+        <v>7300000</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>1484</v>
@@ -28667,7 +28750,7 @@
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="1">
-        <v>917000</v>
+        <v>950000</v>
       </c>
       <c r="I278" s="6" t="s">
         <v>1509</v>
@@ -28706,7 +28789,7 @@
       </c>
       <c r="G279" s="6"/>
       <c r="H279" s="6">
-        <v>997000</v>
+        <v>998000</v>
       </c>
       <c r="I279" s="6" t="s">
         <v>1502</v>
@@ -28745,7 +28828,7 @@
       </c>
       <c r="G280" s="6"/>
       <c r="H280" s="6">
-        <v>87000</v>
+        <v>92000</v>
       </c>
       <c r="I280" s="6" t="s">
         <v>1562</v>
@@ -28781,7 +28864,7 @@
       </c>
       <c r="G281" s="6"/>
       <c r="H281" s="6">
-        <v>188000</v>
+        <v>200000</v>
       </c>
       <c r="I281" s="6" t="s">
         <v>1518</v>
@@ -28820,7 +28903,7 @@
       </c>
       <c r="G282" s="6"/>
       <c r="H282" s="6">
-        <v>174000</v>
+        <v>177000</v>
       </c>
       <c r="I282" s="6" t="s">
         <v>1524</v>
@@ -28895,7 +28978,7 @@
       </c>
       <c r="G284" s="6"/>
       <c r="H284" s="6">
-        <v>593000</v>
+        <v>601000</v>
       </c>
       <c r="I284" s="6" t="s">
         <v>1539</v>
@@ -28936,7 +29019,7 @@
         <v>1549</v>
       </c>
       <c r="H285" s="6">
-        <v>530000</v>
+        <v>537000</v>
       </c>
       <c r="I285" s="6" t="s">
         <v>1544</v>
@@ -28955,6 +29038,9 @@
       </c>
     </row>
     <row r="286" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A286">
+        <v>285</v>
+      </c>
       <c r="B286" s="6">
         <v>508</v>
       </c>
@@ -28972,7 +29058,7 @@
       </c>
       <c r="G286" s="6"/>
       <c r="H286" s="6">
-        <v>307000</v>
+        <v>308000</v>
       </c>
       <c r="I286" s="6" t="s">
         <v>1553</v>
@@ -28988,6 +29074,45 @@
       </c>
       <c r="M286" s="3" t="s">
         <v>1558</v>
+      </c>
+    </row>
+    <row r="287" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A287">
+        <v>286</v>
+      </c>
+      <c r="B287" s="6">
+        <v>516</v>
+      </c>
+      <c r="C287" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D287" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E287" s="6" t="s">
+        <v>1566</v>
+      </c>
+      <c r="F287" s="6" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G287" s="6"/>
+      <c r="H287" s="6">
+        <v>114000</v>
+      </c>
+      <c r="I287" s="6" t="s">
+        <v>1568</v>
+      </c>
+      <c r="J287" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="K287" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="L287" s="3" t="s">
+        <v>1570</v>
+      </c>
+      <c r="M287" s="3" t="s">
+        <v>1571</v>
       </c>
     </row>
   </sheetData>

--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA243E3-1F8B-4517-BB67-8C523CADF64F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B20173-410B-45F9-A932-B9D2B47D2A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="1573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="1693">
   <si>
     <t>id</t>
   </si>
@@ -19061,6 +19061,1253 @@
   </si>
   <si>
     <t>https://i.postimg.cc/tRr3dNG1/516.png</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXeq7UBkzhH/</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pues menos mal que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>no</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> le </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gustaba hablar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mucho…</t>
+    </r>
+  </si>
+  <si>
+    <t>Take Kubo es único</t>
+  </si>
+  <si>
+    <t>Hay que proteger a Take Kubo a toda costa...</t>
+  </si>
+  <si>
+    <t>La Real Sociedad alzó la Copa del Rey este fin de semana y su plantilla lo celebró por todo lo grande.</t>
+  </si>
+  <si>
+    <t>Uno de los que más momentos históricos nos está dando cada vez que agarra el micrófono es el japonés Take Kubo, y estas fueron sus palabras para la afición.</t>
+  </si>
+  <si>
+    <t>copa del rey, real sociedad, take kubo</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXjYfHhkxGb/</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cómo olvidar cuando </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ballesteros</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> le ganó un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sprint</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cristiano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> prime</t>
+    </r>
+  </si>
+  <si>
+    <t>Corría el año 2011 cuando un pletórico Cristiano Ronaldo de 26 años en su prime físico, cursando su cuarta temporada en el Real Madrid, se enfrentó contra un Sergio Ballesteros de 36 años con los huevos negros, y no tuvo nada que hacer ante su velocidad punta.</t>
+  </si>
+  <si>
+    <t>Se trataba de un Levante - Real Madrid en la jornada 4 de LaLiga. En la mítica temporada madridista en la que lograron 100 puntos, tuvieron este tropiezo a principios de temporada perdiendo contra el Levante 1-0.</t>
+  </si>
+  <si>
+    <t>Cristiano había entrado en la segunda parte para intentar conseguir la victoria, mientras que Ballesteros llevaba desde el inicio del partido. En el minuto 68 llegó el gol del Levante, y tan solo 10 minutos más tarde Ballesteros nos dejó claro que la victoria iba a ser para el Levante, y defendió ese resultado con energías sacadas de a saber dónde, ganándole un sprint al mismísimo Cristiano Ronaldo pese a la diferencia de edad y a la diferencia de cansancio en ese partido. Un momento icónico de LaLiga.</t>
+  </si>
+  <si>
+    <t>laliga, real madrid, getafe, sergio ballesteros, cristiano ronaldo</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXjmCQgExLq/</t>
+  </si>
+  <si>
+    <t>Tras el empate entre el Betis y el Real Madrid, el futbolista Camavinga y el presidente de su equipo Florentino Pérez, salieron a disfrutar un poco de la Feria de Abril celebrada en Sevilla.</t>
+  </si>
+  <si>
+    <t>Se pudo ver al centrocampista "blanco" demostrando que goza de talento bailando (a diferencia de jugando a fútbol), y perreando hasta abajo una canción de Bad Gyal en la Feria de Abril.</t>
+  </si>
+  <si>
+    <t>Se rumorea que tras esta noche de pasión entre ambos, se podría venir una renovación con un generoso aumento de sueldo en el contrato del francés.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Camavinga</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Florentino</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dándolo todo en la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Feria de Sevilla</t>
+    </r>
+  </si>
+  <si>
+    <t>real madrid, camavinga, florentino, feria de abril</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXj1tljE-rJ/</t>
+  </si>
+  <si>
+    <t>El que lleva apenas un mes siendo entrenador del Sevilla F.C. ha salido a dar estas sonadas declaraciones en las que se compara con los autistas.</t>
+  </si>
+  <si>
+    <t>Compara su hiperfijación y su obsesión con el trabajo con pertenecer al espectro autista, tras lo que rápidamente pide disculpas y tira la mítica carta de "tengo un familiar que lo es".</t>
+  </si>
+  <si>
+    <t>Puede que la verdadera hiperfijación del entrenador sea con la liga Hypermotion, ya que a día de hoy el Sevilla FC se encuentra en posición de descenso y puede que no siga en primera división el año que viene.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Entrenador</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> del </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sevilla</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: "Parezco un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>autista</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>sevilla, autismo, laliga</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/bwnrG2tB/512.png</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/8zvcFr6n/519.png</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/2SWyqBZJ/520.png</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/kgSGVtbH/521.png</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXhLAtEk0S-/</t>
+  </si>
+  <si>
+    <t>Esta es una de esas estadísticas curiosas del fútbol.</t>
+  </si>
+  <si>
+    <t>El palmarés combinado de los dos franceses Kylian Mbappé, que actualmente milita en el Real Madrid, y Ousmane Dembélé que actualmente milita en el PSG, incluye, entre otras cosas, lo siguiente:</t>
+  </si>
+  <si>
+    <t>1 Balón de Oro que recibió Dembélé este último año.</t>
+  </si>
+  <si>
+    <t>1 título de la Champions que alzó Dembélé la temporada pasada con el PSG.</t>
+  </si>
+  <si>
+    <t>3 títulos de LaLiga que ganó Dembélé en su paso por el FC Barcelona.</t>
+  </si>
+  <si>
+    <t>Mbappé, con sus 7 temporadas en el PSG y sus 2 temporadas en el Real Madrid, todavía no ha logrado coleccionar ninguno de esos tres galardones. Para pensar.</t>
+  </si>
+  <si>
+    <t>Y nada lo tiene Mbappé</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Balón de oro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Champions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>títulos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LaLiga</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en una sola foto</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXlsC1lk_nr/</t>
+  </si>
+  <si>
+    <t>Esto ha ocurrido durante el Talavera - Real Madrid Castilla de Primera RFEF.</t>
+  </si>
+  <si>
+    <t>El delantero de 21 años Pol Fortuny marcó un doblete para darle la victoria al Real Madrid Castilla, y durante la celebración del segundo gol con sus compañeros en la banda del campo, la primera línea de aficionados lo celebró tanto que se vino literalmente abajo la valla, y tras ella, los aficionados.</t>
+  </si>
+  <si>
+    <t>A los jugadores del Castilla se la turbopelaba el hecho y prosiguieron con su vaina.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>valla</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> se viene literalmente </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>abajo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y a los jugadores se la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>turbopela</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXl7pKfk_6P/</t>
+  </si>
+  <si>
+    <t>Esto ha ocurrido en la Final de la Champions asiática.</t>
+  </si>
+  <si>
+    <t>El Al-Ahli de Arabia Saudí se enfrentó al Machida Zelvia de Japón, en la final de un torneo que acabó coronando el equipo árabe gracias a un gol de Firas Al-Buraikan en la prórroga.</t>
+  </si>
+  <si>
+    <t>Se pudo vivir este estrambótico momento en el que tres jugadores del Machida llevaron a cabo esta jugada ensayada con bastantes complicaciones, hasta tal punto que parecía más que estaban jugando a los bolos que al fútbol. Dos de ellos chocaron frontalmente y cayeron desplomados al suelo, a lo que acto seguido el tercero en discordia se tiró también al suelo para no dejarlos solos.</t>
+  </si>
+  <si>
+    <t>Estamos ante una jugada ensayada que no te firma ni Pep Guardiola con el mejor Manchester City ni Luis Enrique con el mejor PSG.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>jugada ensayada</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> parecía más de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bolos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> que de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fútbol</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXm8A6dE7xj/</t>
+  </si>
+  <si>
+    <t>Así es la liga Hypertensiones.</t>
+  </si>
+  <si>
+    <t>El S.D. Huesca - Real Zaragoza de LaLiga Hypermotion de hoy ha estado especialmente calentito.</t>
+  </si>
+  <si>
+    <t>Ambos equipos se juegan el descenso y este partido a finales de temporada es decisivo.</t>
+  </si>
+  <si>
+    <t>Tanto es así, que ha habido un momento con el partido prácticamente acabado en el que hasta el portero del Real Zaragoza, Esteban Andrada, ante la derrota 1-0 por el gol de penalti de Oscar Sielva en el minuto 65, se ha visto sobrepasado, se ha calentado que flipas y ha empujado al defensa y capitán del Huesca, Jorge Pulido, tirándolo al suelo. El colegiado le ha hecho saber que lo expulsaba con una tarjeta roja, y Andrada ha dicho "pues que me quiten lo bailado" y ha aprovechado para acabar la faena derribando del todo a Pulido, tras lo que se ha formado una trifulca interesante.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"Ya que me </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>expulsan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, que me quiten lo </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bailao</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXnEJLGkye0/</t>
+  </si>
+  <si>
+    <t>Esteban Andrada, el portero del Real Zaragoza, le ha propinado un contundente derechazo a Jorge Pulido del S.D. Huesca tras una roja que vio desproporcionada tras empujar al césped a dicho jugador rival.</t>
+  </si>
+  <si>
+    <t>Pensó "Ya que me expulsan, que lo hagan con razones de sobra" y se lanzó a acabar el trabajo cargando el puño en contra del contrincante con el que había tenido el roce.</t>
+  </si>
+  <si>
+    <t>Se trata de dos equipos peleando el descenso en LaLiga Hypermotion, y la locura colectiva de los aficionados del Real Zaragoza no ha impedido que vivan el momento en el bar del vídeo como si se tratase de La Velada de Ibai y fuese Illojuan quien le da el puñetazo a TheGrefg.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Así se ha vivido el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>derechazo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> del portero del </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Real Zaragoza</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXoU8NXjHu6/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXouE2_DM8I/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXq3ARFEzyO/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DXuO3VWk0fS/</t>
+  </si>
+  <si>
+    <r>
+      <t>Golazo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> del </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Arsenal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> femenino en la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Champions</t>
+    </r>
+  </si>
+  <si>
+    <t>Imposible de parar</t>
+  </si>
+  <si>
+    <t>En la Champions femenina se acaba de dar uno de esos goles imposiles de parar.</t>
+  </si>
+  <si>
+    <t>Le tocaba al Arsenal chutar un tiro libre en el minuto 57 y lo colocó en un ángulo imposible de parar.</t>
+  </si>
+  <si>
+    <t>Para nada fue culpa de la habilidad de la portera, quien sin duda lo dio todo.</t>
+  </si>
+  <si>
+    <t>femenino, arsenal, champions</t>
+  </si>
+  <si>
+    <t>El portero del Real Zaragoza, Esteban Andrada, protagonizó ayer una acción bastante criminal en la que noqueó con un certero puñetazo a un jugador del S.D. Huesca peleando el descenso de la segunda división española.</t>
+  </si>
+  <si>
+    <t>Pues al parecer, el futbolista acarrea un historial bastante curioso. No contento con haber jugado en el Monterrey de la liga mexicana, resulta que también ha sido violento anteriormente en LaLiga Hypermotion, como se puede apreciar en el vídeo.</t>
+  </si>
+  <si>
+    <t>Para sus compañeros de equipo, la calentada de ayer con Jorge Pulido debe ser simplemente la cereza sobre el pastel, the cherry on the top como dicen los jóvenes de ahora.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Andrada</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ya tenía </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>antecedentes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> penales</t>
+    </r>
+  </si>
+  <si>
+    <t>hypermotion, real zaragoza, andrada</t>
+  </si>
+  <si>
+    <t>El aura que maneja Chiqui Ibai es de otro mundo.</t>
+  </si>
+  <si>
+    <t>El Galatasaray jugó recientemente un partido contra el Fenerbahçe que terminó con una paliza 3-0 en la que marcaron Victor Oshimen (el gemelo de Kolderiu), Yilmaz y Lucas Torreira.</t>
+  </si>
+  <si>
+    <t>En el inicio del partido, los jugadores realizaron el clásico paseo con niños del equipo rival agarrados de la mano, y los jugadores del Galatasaray tuvieron que soportar a un inesperado pequeñajo que les vaciló en la cara.</t>
+  </si>
+  <si>
+    <t>Se trataba de nada más y nada menos que el travieso de Chiqui Ibai, el cual se encuentra actualmente en un cambio físico interminable, para lo que ha ido a Turquía a implantarse pelo y hacer looksmaxxing, con lo que ha podido aprovechar y asistir a un partido de la liga turca.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Chiqui Ibai turco</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> manda a callar a los rivales</t>
+    </r>
+  </si>
+  <si>
+    <t>chiqui ibai, galatasaray</t>
+  </si>
+  <si>
+    <t>Enzo Fernández se acercó a saludar a la familia de Jude Bellingham en el Mutua Madrid Open.</t>
+  </si>
+  <si>
+    <t>Muchos aficionados se percataron de que el argentino saludó tanto a Jude como a Jobe (los Zipi y Zape británicos) pero no saludó a Vinicius Jr. que se encontraba ahí también, pero es que no se trataba de Vini, se trataba de la madre de los Bellingham.</t>
+  </si>
+  <si>
+    <t>Denise Bellingham iba caracterizada así porque se está preparando para un papel en la gran pantalla. Se enfrentará al reto actoral de interpretar al astro brasileño del Real Madrid, a Mr. Champions, en su biopic que llegará a todos los cines el 30 de febrero del próximo año.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">madre </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bellingham</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hará de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vinicius</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en su nuevo </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>biopic</t>
+    </r>
+  </si>
+  <si>
+    <t>bellingham, real madrid, vinicius, tenis</t>
+  </si>
+  <si>
+    <t>real madrid</t>
+  </si>
+  <si>
+    <t>bolos, japón</t>
+  </si>
+  <si>
+    <t>dembélé, mbappé</t>
+  </si>
+  <si>
+    <t>malasia</t>
+  </si>
+  <si>
+    <t>kanye west</t>
+  </si>
+  <si>
+    <t>israel, bosnia</t>
+  </si>
+  <si>
+    <t>mundial, gyökeres, suecia</t>
+  </si>
+  <si>
+    <t>ishowspeed</t>
+  </si>
+  <si>
+    <t>kanye west, bad bunny, tainy, reggaeton</t>
+  </si>
+  <si>
+    <t>trump, netanyahu, roblox, israel, usa</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DX1Rw6vz4Kq/</t>
+  </si>
+  <si>
+    <t>Un aficionado se topó con el mítico futbolista argentino Gonzalo 'Pipita' Higuaín en el Decathlon de Majadahonda.</t>
+  </si>
+  <si>
+    <t>El exfutbolista que pasó por equipos como el Real Madrid, Napoli, Juventus, AC Milan o Chelsea, se encuentra actualmente con 38 años y viviendo una vida alejada de los focos.</t>
+  </si>
+  <si>
+    <t>Es curioso ver a alguien que ha sido de talla mundial con un estado físico dejado, desaliñado, calvo como una sepia y con estas pintas. Hace apenas tres años estaba acabando su carrera profesional en el Inter Miami, antes de que llegara Leo Messi.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Este es el estado </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>físico</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> actual del pipita </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Higuaín</t>
+    </r>
+  </si>
+  <si>
+    <t>higuaín, argentina, real madrid</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DX4Xt_lzBvz/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DX65C0OTJO7/</t>
+  </si>
+  <si>
+    <t>El delantero Thomasz Skublak del Inter Toronto marcó un golazo ante el Atlético Ottawa en la Premier League Canadiense.</t>
+  </si>
+  <si>
+    <t>Cuando se acercó a la banda para celebrar, optó por sacarse del calcetín su tarjeta de visita de su segundo trabajo: agente inmobiliario.</t>
+  </si>
+  <si>
+    <t>El futbolista aprovechó el momento para publicitar su otro trabajo, y salió mucho mejor de lo esperado, ya que el vídeo está dando la vuelta al mundo.</t>
+  </si>
+  <si>
+    <t>Esta es una de esas jugadas que demuestran el alto IQ futbolístico con el que cuenta Robert Lewandowski.</t>
+  </si>
+  <si>
+    <t>Al delantero polaco está en la tercera edad y ha decidido volcar todo su IQ para encontrar la forma de no tener que correr.</t>
+  </si>
+  <si>
+    <t>En esta jugada se aprecia cómo le indica a Fermín que haga un sprint al área para que los defensas se tiren sobre él y así se queda con el espacio libre para recibir el pase de Raphinha y chutar. High IQ play.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lewandowski</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> le dice a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fermín</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> que corra para </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>confundir</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a los rivales</t>
+    </r>
+  </si>
+  <si>
+    <t>lewandowski, fermín, barça, laliga</t>
+  </si>
+  <si>
+    <t>canadá</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Marca </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gol</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y aprovecha para </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>publicitarse</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> como </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>agente inmobiliario</t>
+    </r>
+  </si>
+  <si>
+    <t>ábalos</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DX6sDSNgnac/</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vivimos en un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pais</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en el que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>amar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> es </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>delito</t>
+    </r>
+  </si>
+  <si>
+    <t>José Luis Ábalos sigue bajo el escrutinio público cuando su único delito ha sido amar demasiado.</t>
+  </si>
+  <si>
+    <t>El que fue secretario de organización del Partido Socialista Obrero Español y mano derecha de Pedro Sánchez se encuentra hoy en día encarcelado junto a Nicolás Maduro y Diddy en la prisión de Soto del Real.</t>
+  </si>
+  <si>
+    <t>El caso Ábalos sigue juicio tras juicio y se está persiguiendo a un hombre familiar, romántico, y ante todo patriota. FREE ÁBALOS.</t>
   </si>
 </sst>
 </file>
@@ -19475,7 +20722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S287"/>
+  <dimension ref="A1:S304"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.42578125" customWidth="1"/>
@@ -20433,7 +21680,7 @@
         <v>148</v>
       </c>
       <c r="H31" s="1">
-        <v>533000</v>
+        <v>534000</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>149</v>
@@ -22393,7 +23640,7 @@
       </c>
       <c r="G96" s="1"/>
       <c r="H96" s="1">
-        <v>766000</v>
+        <v>767000</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>425</v>
@@ -22455,7 +23702,7 @@
       </c>
       <c r="G98" s="1"/>
       <c r="H98" s="1">
-        <v>204000</v>
+        <v>205000</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>434</v>
@@ -22968,7 +24215,7 @@
       </c>
       <c r="G113" s="1"/>
       <c r="H113" s="1">
-        <v>544000</v>
+        <v>545000</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>516</v>
@@ -23135,7 +24382,7 @@
       </c>
       <c r="G118" s="1"/>
       <c r="H118" s="1">
-        <v>441000</v>
+        <v>442000</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>543</v>
@@ -23465,7 +24712,7 @@
         <v>599</v>
       </c>
       <c r="H127" s="1">
-        <v>996000</v>
+        <v>997000</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>600</v>
@@ -23745,7 +24992,7 @@
       </c>
       <c r="G135" s="1"/>
       <c r="H135" s="1">
-        <v>421000</v>
+        <v>422000</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>646</v>
@@ -24217,7 +25464,7 @@
       </c>
       <c r="G149" s="1"/>
       <c r="H149" s="1">
-        <v>238000</v>
+        <v>239000</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>722</v>
@@ -24384,7 +25631,7 @@
         <v>748</v>
       </c>
       <c r="H154" s="1">
-        <v>108000</v>
+        <v>110000</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>749</v>
@@ -24846,7 +26093,7 @@
       </c>
       <c r="G167" s="1"/>
       <c r="H167" s="1">
-        <v>171000</v>
+        <v>172000</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>828</v>
@@ -25042,7 +26289,7 @@
       </c>
       <c r="G173" s="1"/>
       <c r="H173" s="1">
-        <v>728000</v>
+        <v>729000</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>862</v>
@@ -25327,7 +26574,7 @@
       </c>
       <c r="G182" s="1"/>
       <c r="H182" s="1">
-        <v>93000</v>
+        <v>94000</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>906</v>
@@ -25429,7 +26676,7 @@
       </c>
       <c r="G185" s="1"/>
       <c r="H185" s="1">
-        <v>82000</v>
+        <v>83000</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>923</v>
@@ -25950,7 +27197,7 @@
       </c>
       <c r="G201" s="1"/>
       <c r="H201" s="1">
-        <v>276000</v>
+        <v>277000</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>1005</v>
@@ -25983,7 +27230,7 @@
       </c>
       <c r="G202" s="1"/>
       <c r="H202" s="1">
-        <v>584000</v>
+        <v>585000</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>1010</v>
@@ -26253,7 +27500,7 @@
       </c>
       <c r="G210" s="1"/>
       <c r="H210" s="1">
-        <v>340000</v>
+        <v>342000</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>1056</v>
@@ -26525,7 +27772,7 @@
       </c>
       <c r="G218" s="1"/>
       <c r="H218" s="1">
-        <v>412000</v>
+        <v>413000</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>1099</v>
@@ -26689,7 +27936,7 @@
       </c>
       <c r="G223" s="1"/>
       <c r="H223" s="1">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>1128</v>
@@ -26720,6 +27967,9 @@
       <c r="D224" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="E224" s="6" t="s">
+        <v>1668</v>
+      </c>
       <c r="F224" s="1" t="s">
         <v>1133</v>
       </c>
@@ -26753,12 +28003,15 @@
       <c r="D225" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="E225" s="6" t="s">
+        <v>1667</v>
+      </c>
       <c r="F225" s="1" t="s">
         <v>1138</v>
       </c>
       <c r="G225" s="1"/>
       <c r="H225" s="1">
-        <v>264000</v>
+        <v>265000</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>1139</v>
@@ -26789,6 +28042,9 @@
       <c r="D226" s="1" t="s">
         <v>73</v>
       </c>
+      <c r="E226" s="6" t="s">
+        <v>1666</v>
+      </c>
       <c r="F226" s="1" t="s">
         <v>1144</v>
       </c>
@@ -26796,7 +28052,7 @@
         <v>1145</v>
       </c>
       <c r="H226" s="1">
-        <v>89000</v>
+        <v>90000</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>1146</v>
@@ -26824,6 +28080,9 @@
       <c r="D227" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="E227" s="6" t="s">
+        <v>1665</v>
+      </c>
       <c r="F227" s="1" t="s">
         <v>1150</v>
       </c>
@@ -26859,12 +28118,15 @@
       <c r="D228" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="E228" s="6" t="s">
+        <v>1664</v>
+      </c>
       <c r="F228" s="1" t="s">
         <v>1156</v>
       </c>
       <c r="G228" s="1"/>
       <c r="H228" s="1">
-        <v>151000</v>
+        <v>152000</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>1157</v>
@@ -26894,6 +28156,9 @@
       </c>
       <c r="D229" s="1" t="s">
         <v>31</v>
+      </c>
+      <c r="E229" s="6" t="s">
+        <v>1663</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>1162</v>
@@ -27426,7 +28691,7 @@
         <v>1256</v>
       </c>
       <c r="H243" s="1">
-        <v>387000</v>
+        <v>388000</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>1257</v>
@@ -27465,7 +28730,7 @@
       </c>
       <c r="G244" s="1"/>
       <c r="H244" s="1">
-        <v>184000</v>
+        <v>185000</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>1264</v>
@@ -27899,7 +29164,7 @@
         <v>1336</v>
       </c>
       <c r="H256" s="1">
-        <v>744000</v>
+        <v>746000</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>1337</v>
@@ -28120,7 +29385,7 @@
       </c>
       <c r="G262" s="1"/>
       <c r="H262" s="1">
-        <v>501000</v>
+        <v>502000</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>1376</v>
@@ -28159,7 +29424,7 @@
       </c>
       <c r="G263" s="1"/>
       <c r="H263" s="1">
-        <v>288000</v>
+        <v>289000</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>1383</v>
@@ -28195,7 +29460,7 @@
       </c>
       <c r="G264" s="1"/>
       <c r="H264" s="1">
-        <v>135000</v>
+        <v>136000</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>1389</v>
@@ -28509,7 +29774,7 @@
       </c>
       <c r="G272" s="1"/>
       <c r="H272" s="1">
-        <v>734000</v>
+        <v>741000</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>1446</v>
@@ -28589,7 +29854,7 @@
       </c>
       <c r="G274" s="1"/>
       <c r="H274" s="1">
-        <v>206000</v>
+        <v>272000</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>1461</v>
@@ -28711,7 +29976,7 @@
       </c>
       <c r="G277" s="1"/>
       <c r="H277" s="1">
-        <v>7300000</v>
+        <v>8200000</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>1484</v>
@@ -28750,7 +30015,7 @@
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="1">
-        <v>950000</v>
+        <v>1000000</v>
       </c>
       <c r="I278" s="6" t="s">
         <v>1509</v>
@@ -28789,7 +30054,7 @@
       </c>
       <c r="G279" s="6"/>
       <c r="H279" s="6">
-        <v>998000</v>
+        <v>1000000</v>
       </c>
       <c r="I279" s="6" t="s">
         <v>1502</v>
@@ -28828,7 +30093,7 @@
       </c>
       <c r="G280" s="6"/>
       <c r="H280" s="6">
-        <v>92000</v>
+        <v>102000</v>
       </c>
       <c r="I280" s="6" t="s">
         <v>1562</v>
@@ -28864,7 +30129,7 @@
       </c>
       <c r="G281" s="6"/>
       <c r="H281" s="6">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="I281" s="6" t="s">
         <v>1518</v>
@@ -28903,7 +30168,7 @@
       </c>
       <c r="G282" s="6"/>
       <c r="H282" s="6">
-        <v>177000</v>
+        <v>188000</v>
       </c>
       <c r="I282" s="6" t="s">
         <v>1524</v>
@@ -28934,6 +30199,9 @@
       <c r="D283" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="E283" s="6" t="s">
+        <v>1662</v>
+      </c>
       <c r="F283" s="6" t="s">
         <v>1534</v>
       </c>
@@ -28978,7 +30246,7 @@
       </c>
       <c r="G284" s="6"/>
       <c r="H284" s="6">
-        <v>601000</v>
+        <v>625000</v>
       </c>
       <c r="I284" s="6" t="s">
         <v>1539</v>
@@ -29019,7 +30287,7 @@
         <v>1549</v>
       </c>
       <c r="H285" s="6">
-        <v>537000</v>
+        <v>546000</v>
       </c>
       <c r="I285" s="6" t="s">
         <v>1544</v>
@@ -29058,7 +30326,7 @@
       </c>
       <c r="G286" s="6"/>
       <c r="H286" s="6">
-        <v>308000</v>
+        <v>312000</v>
       </c>
       <c r="I286" s="6" t="s">
         <v>1553</v>
@@ -29081,38 +30349,686 @@
         <v>286</v>
       </c>
       <c r="B287" s="6">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C287" s="2">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="D287" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E287" s="6" t="s">
+        <v>1579</v>
+      </c>
+      <c r="F287" s="6" t="s">
+        <v>1574</v>
+      </c>
+      <c r="G287" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="H287" s="6">
+        <v>51000</v>
+      </c>
+      <c r="I287" s="6" t="s">
+        <v>1573</v>
+      </c>
+      <c r="J287" s="6" t="s">
+        <v>1598</v>
+      </c>
+      <c r="K287" s="3" t="s">
+        <v>1576</v>
+      </c>
+      <c r="L287" s="3" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M287" s="3" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="288" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A288">
+        <v>287</v>
+      </c>
+      <c r="B288" s="6">
+        <v>516</v>
+      </c>
+      <c r="C288" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D288" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E288" s="6" t="s">
         <v>1566</v>
       </c>
-      <c r="F287" s="6" t="s">
+      <c r="F288" s="6" t="s">
         <v>1567</v>
       </c>
-      <c r="G287" s="6"/>
-      <c r="H287" s="6">
-        <v>114000</v>
-      </c>
-      <c r="I287" s="6" t="s">
+      <c r="G288" s="6"/>
+      <c r="H288" s="6">
+        <v>226000</v>
+      </c>
+      <c r="I288" s="6" t="s">
         <v>1568</v>
       </c>
-      <c r="J287" s="6" t="s">
+      <c r="J288" s="6" t="s">
         <v>1572</v>
       </c>
-      <c r="K287" s="3" t="s">
+      <c r="K288" s="3" t="s">
         <v>1569</v>
       </c>
-      <c r="L287" s="3" t="s">
+      <c r="L288" s="3" t="s">
         <v>1570</v>
       </c>
-      <c r="M287" s="3" t="s">
+      <c r="M288" s="3" t="s">
         <v>1571</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A289">
+        <v>288</v>
+      </c>
+      <c r="B289" s="6">
+        <v>517</v>
+      </c>
+      <c r="C289" s="2">
+        <v>46136</v>
+      </c>
+      <c r="D289" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E289" s="6" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F289" s="6" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G289" s="6" t="s">
+        <v>1609</v>
+      </c>
+      <c r="H289" s="6">
+        <v>69000</v>
+      </c>
+      <c r="I289" s="6" t="s">
+        <v>1602</v>
+      </c>
+      <c r="K289" s="3" t="s">
+        <v>1603</v>
+      </c>
+      <c r="L289" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="M289" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="N289" s="3" t="s">
+        <v>1606</v>
+      </c>
+      <c r="O289" s="3" t="s">
+        <v>1607</v>
+      </c>
+      <c r="P289" s="3" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A290">
+        <v>289</v>
+      </c>
+      <c r="B290" s="6">
+        <v>519</v>
+      </c>
+      <c r="C290" s="2">
+        <v>46137</v>
+      </c>
+      <c r="D290" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E290" s="6" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F290" s="6" t="s">
+        <v>1581</v>
+      </c>
+      <c r="G290" s="6"/>
+      <c r="H290" s="6">
+        <v>800000</v>
+      </c>
+      <c r="I290" s="6" t="s">
+        <v>1580</v>
+      </c>
+      <c r="J290" s="6" t="s">
+        <v>1599</v>
+      </c>
+      <c r="K290" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="L290" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="M290" s="3" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A291">
+        <v>290</v>
+      </c>
+      <c r="B291" s="6">
+        <v>520</v>
+      </c>
+      <c r="C291" s="2">
+        <v>46137</v>
+      </c>
+      <c r="D291" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E291" s="6" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F291" s="6" t="s">
+        <v>1590</v>
+      </c>
+      <c r="G291" s="6"/>
+      <c r="H291" s="6">
+        <v>394000</v>
+      </c>
+      <c r="I291" s="6" t="s">
+        <v>1586</v>
+      </c>
+      <c r="J291" s="6" t="s">
+        <v>1600</v>
+      </c>
+      <c r="K291" s="3" t="s">
+        <v>1587</v>
+      </c>
+      <c r="L291" s="3" t="s">
+        <v>1588</v>
+      </c>
+      <c r="M291" s="3" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="292" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A292">
+        <v>291</v>
+      </c>
+      <c r="B292" s="6">
+        <v>521</v>
+      </c>
+      <c r="C292" s="2">
+        <v>46137</v>
+      </c>
+      <c r="D292" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E292" s="6" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F292" s="6" t="s">
+        <v>1596</v>
+      </c>
+      <c r="G292" s="6"/>
+      <c r="H292" s="6">
+        <v>882000</v>
+      </c>
+      <c r="I292" s="6" t="s">
+        <v>1592</v>
+      </c>
+      <c r="J292" s="6" t="s">
+        <v>1601</v>
+      </c>
+      <c r="K292" s="3" t="s">
+        <v>1593</v>
+      </c>
+      <c r="L292" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="M292" s="3" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="293" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A293">
+        <v>292</v>
+      </c>
+      <c r="B293" s="6">
+        <v>523</v>
+      </c>
+      <c r="C293" s="2">
+        <v>46138</v>
+      </c>
+      <c r="D293" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E293" s="6" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F293" s="6" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G293" s="6"/>
+      <c r="H293" s="6">
+        <v>199000</v>
+      </c>
+      <c r="I293" s="6" t="s">
+        <v>1611</v>
+      </c>
+      <c r="K293" s="3" t="s">
+        <v>1612</v>
+      </c>
+      <c r="L293" s="3" t="s">
+        <v>1613</v>
+      </c>
+      <c r="M293" s="3" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="294" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A294">
+        <v>293</v>
+      </c>
+      <c r="B294" s="6">
+        <v>524</v>
+      </c>
+      <c r="C294" s="2">
+        <v>46138</v>
+      </c>
+      <c r="D294" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E294" s="6" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F294" s="6" t="s">
+        <v>1621</v>
+      </c>
+      <c r="G294" s="6"/>
+      <c r="H294" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="I294" s="6" t="s">
+        <v>1616</v>
+      </c>
+      <c r="K294" s="3" t="s">
+        <v>1617</v>
+      </c>
+      <c r="L294" s="3" t="s">
+        <v>1618</v>
+      </c>
+      <c r="M294" s="3" t="s">
+        <v>1619</v>
+      </c>
+      <c r="N294" s="3" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="295" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A295">
+        <v>294</v>
+      </c>
+      <c r="B295" s="6">
+        <v>526</v>
+      </c>
+      <c r="C295" s="2">
+        <v>46138</v>
+      </c>
+      <c r="D295" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E295" s="6" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F295" s="6" t="s">
+        <v>1627</v>
+      </c>
+      <c r="G295" s="6"/>
+      <c r="H295" s="6">
+        <v>8300000</v>
+      </c>
+      <c r="I295" s="6" t="s">
+        <v>1622</v>
+      </c>
+      <c r="K295" s="3" t="s">
+        <v>1623</v>
+      </c>
+      <c r="L295" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="M295" s="3" t="s">
+        <v>1625</v>
+      </c>
+      <c r="N295" s="3" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="296" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A296">
+        <v>295</v>
+      </c>
+      <c r="B296" s="6">
+        <v>527</v>
+      </c>
+      <c r="C296" s="2">
+        <v>46138</v>
+      </c>
+      <c r="D296" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E296" s="6" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F296" s="6" t="s">
+        <v>1632</v>
+      </c>
+      <c r="G296" s="6"/>
+      <c r="H296" s="6">
+        <v>174000</v>
+      </c>
+      <c r="I296" s="6" t="s">
+        <v>1628</v>
+      </c>
+      <c r="K296" s="3" t="s">
+        <v>1629</v>
+      </c>
+      <c r="L296" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="M296" s="3" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="297" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A297">
+        <v>296</v>
+      </c>
+      <c r="B297" s="6">
+        <v>528</v>
+      </c>
+      <c r="C297" s="2">
+        <v>46139</v>
+      </c>
+      <c r="D297" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E297" s="6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F297" s="5" t="s">
+        <v>1637</v>
+      </c>
+      <c r="G297" s="6" t="s">
+        <v>1638</v>
+      </c>
+      <c r="H297" s="6">
+        <v>404000</v>
+      </c>
+      <c r="I297" s="6" t="s">
+        <v>1633</v>
+      </c>
+      <c r="K297" s="3" t="s">
+        <v>1639</v>
+      </c>
+      <c r="L297" s="3" t="s">
+        <v>1640</v>
+      </c>
+      <c r="M297" s="3" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="298" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A298">
+        <v>297</v>
+      </c>
+      <c r="B298" s="6">
+        <v>529</v>
+      </c>
+      <c r="C298" s="2">
+        <v>46139</v>
+      </c>
+      <c r="D298" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E298" s="6" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F298" s="6" t="s">
+        <v>1646</v>
+      </c>
+      <c r="G298" s="6"/>
+      <c r="H298" s="6">
+        <v>392000</v>
+      </c>
+      <c r="I298" s="6" t="s">
+        <v>1634</v>
+      </c>
+      <c r="K298" s="3" t="s">
+        <v>1643</v>
+      </c>
+      <c r="L298" s="3" t="s">
+        <v>1644</v>
+      </c>
+      <c r="M298" s="3" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="299" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A299">
+        <v>298</v>
+      </c>
+      <c r="B299" s="6">
+        <v>530</v>
+      </c>
+      <c r="C299" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D299" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E299" s="6" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F299" s="6" t="s">
+        <v>1652</v>
+      </c>
+      <c r="G299" s="6"/>
+      <c r="H299" s="6">
+        <v>218000</v>
+      </c>
+      <c r="I299" s="6" t="s">
+        <v>1635</v>
+      </c>
+      <c r="K299" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="L299" s="3" t="s">
+        <v>1649</v>
+      </c>
+      <c r="M299" s="3" t="s">
+        <v>1650</v>
+      </c>
+      <c r="N299" s="3" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="300" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A300">
+        <v>299</v>
+      </c>
+      <c r="B300" s="6">
+        <v>531</v>
+      </c>
+      <c r="C300" s="2">
+        <v>46141</v>
+      </c>
+      <c r="D300" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E300" s="6" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F300" s="6" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G300" s="6"/>
+      <c r="H300" s="6">
+        <v>739000</v>
+      </c>
+      <c r="I300" s="6" t="s">
+        <v>1636</v>
+      </c>
+      <c r="K300" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="L300" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="M300" s="3" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="301" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A301">
+        <v>300</v>
+      </c>
+      <c r="B301" s="6">
+        <v>535</v>
+      </c>
+      <c r="C301" s="2">
+        <v>46144</v>
+      </c>
+      <c r="D301" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E301" s="6" t="s">
+        <v>1674</v>
+      </c>
+      <c r="F301" s="6" t="s">
+        <v>1673</v>
+      </c>
+      <c r="G301" s="6"/>
+      <c r="H301" s="6">
+        <v>410000</v>
+      </c>
+      <c r="I301" s="6" t="s">
+        <v>1669</v>
+      </c>
+      <c r="K301" s="3" t="s">
+        <v>1670</v>
+      </c>
+      <c r="L301" s="3" t="s">
+        <v>1671</v>
+      </c>
+      <c r="M301" s="3" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="302" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A302">
+        <v>301</v>
+      </c>
+      <c r="B302" s="6">
+        <v>538</v>
+      </c>
+      <c r="C302" s="2">
+        <v>46145</v>
+      </c>
+      <c r="D302" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E302" s="6" t="s">
+        <v>1685</v>
+      </c>
+      <c r="F302" s="6" t="s">
+        <v>1686</v>
+      </c>
+      <c r="G302" s="6"/>
+      <c r="H302" s="6">
+        <v>293000</v>
+      </c>
+      <c r="I302" s="6" t="s">
+        <v>1675</v>
+      </c>
+      <c r="K302" s="3" t="s">
+        <v>1677</v>
+      </c>
+      <c r="L302" s="3" t="s">
+        <v>1678</v>
+      </c>
+      <c r="M302" s="3" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="303" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A303">
+        <v>302</v>
+      </c>
+      <c r="B303" s="6">
+        <v>541</v>
+      </c>
+      <c r="C303" s="2">
+        <v>46146</v>
+      </c>
+      <c r="D303" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E303" s="6" t="s">
+        <v>1687</v>
+      </c>
+      <c r="F303" s="6" t="s">
+        <v>1689</v>
+      </c>
+      <c r="G303" s="6"/>
+      <c r="H303" s="6">
+        <v>62000</v>
+      </c>
+      <c r="I303" s="6" t="s">
+        <v>1688</v>
+      </c>
+      <c r="K303" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="L303" s="3" t="s">
+        <v>1691</v>
+      </c>
+      <c r="M303" s="3" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="304" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A304">
+        <v>303</v>
+      </c>
+      <c r="B304" s="6">
+        <v>542</v>
+      </c>
+      <c r="C304" s="2">
+        <v>46146</v>
+      </c>
+      <c r="D304" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E304" s="6" t="s">
+        <v>1684</v>
+      </c>
+      <c r="F304" s="6" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G304" s="6"/>
+      <c r="H304" s="6">
+        <v>50000</v>
+      </c>
+      <c r="I304" s="6" t="s">
+        <v>1676</v>
+      </c>
+      <c r="K304" s="3" t="s">
+        <v>1680</v>
+      </c>
+      <c r="L304" s="3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="M304" s="3" t="s">
+        <v>1682</v>
       </c>
     </row>
   </sheetData>

--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B20173-410B-45F9-A932-B9D2B47D2A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B906D7-22B8-49FA-BE53-81A8FB932A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TABLA" sheetId="2" r:id="rId1"/>
@@ -20243,6 +20243,15 @@
     <t>https://www.instagram.com/reel/DX6sDSNgnac/</t>
   </si>
   <si>
+    <t>José Luis Ábalos sigue bajo el escrutinio público cuando su único delito ha sido amar demasiado.</t>
+  </si>
+  <si>
+    <t>El que fue secretario de organización del Partido Socialista Obrero Español y mano derecha de Pedro Sánchez se encuentra hoy en día encarcelado junto a Nicolás Maduro y Diddy en la prisión de Soto del Real.</t>
+  </si>
+  <si>
+    <t>El caso Ábalos sigue juicio tras juicio y se está persiguiendo a un hombre familiar, romántico, y ante todo patriota. FREE ÁBALOS.</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Vivimos en un </t>
     </r>
@@ -20255,7 +20264,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>pais</t>
+      <t>país</t>
     </r>
     <r>
       <rPr>
@@ -20299,15 +20308,6 @@
       </rPr>
       <t>delito</t>
     </r>
-  </si>
-  <si>
-    <t>José Luis Ábalos sigue bajo el escrutinio público cuando su único delito ha sido amar demasiado.</t>
-  </si>
-  <si>
-    <t>El que fue secretario de organización del Partido Socialista Obrero Español y mano derecha de Pedro Sánchez se encuentra hoy en día encarcelado junto a Nicolás Maduro y Diddy en la prisión de Soto del Real.</t>
-  </si>
-  <si>
-    <t>El caso Ábalos sigue juicio tras juicio y se está persiguiendo a un hombre familiar, romántico, y ante todo patriota. FREE ÁBALOS.</t>
   </si>
 </sst>
 </file>
@@ -30976,7 +30976,7 @@
         <v>1687</v>
       </c>
       <c r="F303" s="6" t="s">
-        <v>1689</v>
+        <v>1692</v>
       </c>
       <c r="G303" s="6"/>
       <c r="H303" s="6">
@@ -30986,13 +30986,13 @@
         <v>1688</v>
       </c>
       <c r="K303" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="L303" s="3" t="s">
         <v>1690</v>
       </c>
-      <c r="L303" s="3" t="s">
+      <c r="M303" s="3" t="s">
         <v>1691</v>
-      </c>
-      <c r="M303" s="3" t="s">
-        <v>1692</v>
       </c>
     </row>
     <row r="304" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">

--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B906D7-22B8-49FA-BE53-81A8FB932A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EBD61C-B437-4153-A5D0-91E35C486DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="1693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2399" uniqueCount="2081">
   <si>
     <t>id</t>
   </si>
@@ -20307,6 +20307,5215 @@
         <scheme val="minor"/>
       </rPr>
       <t>delito</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DX7JBBaj6F7/</t>
+  </si>
+  <si>
+    <t>North West, la hija de Kanye y Kim Kardashian, ha estrenado su primer EP musical con tan solo 12 años, y pese a no ser un trabajo del todo completo se ven reminiscencias del talento de su padre y se le augura un brillante futuro en la industria.</t>
+  </si>
+  <si>
+    <t>Con motivo del estreno, North celebró una release party en Los Ángeles a la que acudió el patrón Kanye West con la primera dama Bianca Censori.</t>
+  </si>
+  <si>
+    <t>Pudimos ver al goat paseándose por ahí mientras se gozaba una tarrina de yogurt helado del Llaollao que compró para la ocasión. Al parecer su sabor favorito es el de unicornio.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Simplemente un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>padre apoyando</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a su </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hija</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y gozándose un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Llaollao</t>
+    </r>
+  </si>
+  <si>
+    <t>kanye west, north west</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DX7XTTFFa5M/</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quevedo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, icono marxista, en contra de la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">especulación </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">de la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vivienda</t>
+    </r>
+  </si>
+  <si>
+    <t>El cantante financiado por el PSOE y abiertamente comunista, Pedro Luis Domínguez Quevedo acudió al stream de Jay Wheeler en Puerto Rico tras el lanzamiento de su nuevo álbum 'El Baifo' y hablaron de multitud de temas.</t>
+  </si>
+  <si>
+    <t>En un momento la conversación derivó a hablar sobre si tenía alguna casa en propiedad o si tenía pensado tenerla, y Quevedo, tras decir que todavía no se ha comprado una casa, activó el modo político para posicionarse en contra de la especulación de la vivienda que está afectando a toda España en general, pero en específico a las islas canarias, de donde Quevedo es abanderado.</t>
+  </si>
+  <si>
+    <t>El también canario Cruz Cafuné aplaudió al ver esto ya que él opina lo mismo, como hizo saber en su canción protesta de 2017 llamada 'Mi Casa', la cual era un statement político reivindicando algo similar.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DX7ds9hztu2/</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Golazo de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chilena</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>João Pedro</t>
+    </r>
+  </si>
+  <si>
+    <t>Este es el golazo de chilena que acaba de marcar João Pedro en la Premier League.</t>
+  </si>
+  <si>
+    <t>Ha sido en un Chelsea - Nottingham Forest bastante atropellado que ha acabado 1 - 3 a favor del Forest. En el minuto 93 ha caído este precioso gol de João Pedro que ha puesto el balón contra la red con una chilena.</t>
+  </si>
+  <si>
+    <t>Con este, ya tenemos otro contendiente para el premio Puskás de este año 2026, entre los que figuran jugadores como Arda Güler, Michael Folorunsho o Dominic Solanke.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DX82v6JzWKF/</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mbappé</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> es más importante parecer </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>heterosexual</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> que el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Real Madrid</t>
+    </r>
+  </si>
+  <si>
+    <t>El astro Kylian Mbappé ha pasado unas vacaciones por Europa con su nueva pareja, la actriz Ester Expósito, mientras 'sufre' una lesión en la zona perianal.</t>
+  </si>
+  <si>
+    <t>Simultáneamente, el Real Madrid está pasando por un bache bastante duro. Tras dos años sin títulos, a la plantilla merengue le toca cerrar una temporada que ya se da por perdida, y enfrentará al FC Barcelona en El Clásico el fin de semana que viene.</t>
+  </si>
+  <si>
+    <t>La permanencia de Mbappé en el Real Madrid está altamente en duda. Al dictador se le han visto las costuras y todo el vestuario parece haberse puesto en su contra. Veremos cuál es el futuro del equipo.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DX80RcgAuPH/</t>
+  </si>
+  <si>
+    <t>El streamer iShowSpeed se encuentra de visita en Puerto Rico conociendo las maravillas de la isla, donde ha tenido la oportunidad de juntarse con artistas como Eladio Carrión o De La Ghetto en un ambiente eroticofestivo.</t>
+  </si>
+  <si>
+    <t>Entre lanzarse de un puente o hablar con Daddy Yankee por Facetime, una de las cosas que ha hecho ha sido toparse con el cantante Elvis Crespo (pseudónimo que usa Rosalía para sacar otro tipo de música), que ha sacado un hueco en su agenda tras grabar la última temporada de Euphoria junto a Zendaya, Sydney Sweeney y Jacob Elordi, y cantar junto a él su hit masivo 'Suavemente'.</t>
+  </si>
+  <si>
+    <t>Pese a no conocer ni una sola palabra de la letra de la canción, el chamaquito le mete ganas y eso es lo que cuenta. Está claro que Speed se irá de Puerto Rico, la isla del reggaeton, con un muy agradable recuerdo.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IShowSpeed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en PR cantando </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Suavemente</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> con </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rosalía</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DX9AxBMD7Nn/</t>
+  </si>
+  <si>
+    <t>IShowSpeed está tapped in en cuanto a reggaeton antiguo se refiere.</t>
+  </si>
+  <si>
+    <t>El streamer se encontraba en directo visitando Puerto Rico junto a Eladio Carrión y este le pasó el móvil para que hablara por videollamada con la leyenda Daddy Yankee.</t>
+  </si>
+  <si>
+    <t>Lo que hizo Speed nada más recibir el móvil fue tararearle la canción de Zion &amp; Lennox 'Yo Voy', en la que Daddy Yankee colabora.</t>
+  </si>
+  <si>
+    <t>Intercambiaron un par de palabras y Speed finalizó la llamada cantándole su hit 'La Gasolina'.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Speed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> habla con </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Daddy Yankee</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y le demuestra que está </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tapped in</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DX9mXSxm5Dt/</t>
+  </si>
+  <si>
+    <t>Una camada de judíos antisionistas en Nueva York ha salido a las calles a reivindicar su derecho de estar en contra del estado de Israel.</t>
+  </si>
+  <si>
+    <t>¿Qué tendrá el estado de Israel que hasta las comunidades judías esparcidas por el mundo se están poniendo en su contra? Netanyahu no se tomará nada bien esto.</t>
+  </si>
+  <si>
+    <t>Como sea, en el vídeo se puede apreciar a los judíos profanando símbolos del estado de Israel, bailando, riendo y celebrando, como si viviesen en un mundo idílico.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Judíos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> antisionistas en </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nueva York</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> quemando la</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bandera</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Israel</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DX-A1aSj4pL/</t>
+  </si>
+  <si>
+    <t>Acudió a la Met Gala de Nueva York Aaron Rose Philip, la primera mujer trans, negra y parapléjica de esta gala de moda.</t>
+  </si>
+  <si>
+    <t>En un evento plagado de celebridades vistiendo sus mejores ropajes como es el caso de Bad Bunny, Rihanna o la parienta de Cristiano Ronaldo, también logró captar la atención de todos los fotógrafos esta modelo que tacha varios ticks en la papeleta de minorías desfavorecidas.</t>
+  </si>
+  <si>
+    <t>Su acto de presencia ha sentado unos precedentes muy importantes, y es que al dar un paso adelante (figuradamente hablando) quizás motiva a más mujeres trans negras y parapléjicas a brillar en el mundo ouh yeah let's go.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El Final Boss de la inclusión: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mujer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>trans</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>negra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>parapléjica</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DX-M_GDshSo/</t>
+  </si>
+  <si>
+    <t>Así decidió llegar Heidi Klum a la Met Gala, haciendo honor a mi calcetín todo lechado que guardo escondido en una esquina del armario para que mis padres no lo vean.</t>
+  </si>
+  <si>
+    <t>La Met Gala es un evento de moda al que asisten celebridades del calibre de Rauw Alejandro, Jacob Elordi, RickyEdit y Edu Casanova.</t>
+  </si>
+  <si>
+    <t>Pues este año la modelo y streamer amiga de Ampeterby7, Heidi Klum, ha decidido ir con un velo todo empapado con leche de Central Lechera Asturiana.</t>
+  </si>
+  <si>
+    <r>
+      <t>Mi</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> calcetín </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">de las </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pajas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> todo lechado llegando a la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Met Gala</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DX_cUGaTCke/</t>
+  </si>
+  <si>
+    <t>El periodista José Miguel Villarroya se levantó basado.</t>
+  </si>
+  <si>
+    <t>En una conversación telemática con el también periodista Siro López, debatieron sobre el estado actual del vestuario del Real Madrid, las licencias del dictador Kylian Mbappé y la inestabilidad de la directiva del equipo.</t>
+  </si>
+  <si>
+    <t>Villarroya vio bien comparar la caída del Real Madrid con la caída de otros regímenes que él ha presenciado, como lo son el de la Unión Soviética y el de la República Democrática Alemana.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>URSS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RDA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Real Madrid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, mayores </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>regímenes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de la historia</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYAPavBT6r2/</t>
+  </si>
+  <si>
+    <t>Con todo el quilombo que está habiendo en el vestuario del Real Madrid y la caída de la dictadura de Kylian Mbappé, no viene mal recordar este momento.</t>
+  </si>
+  <si>
+    <t>Según muchos, este intercambio de palabras protagonizado por Ferran Torres y Vinicius Jr. podría haber sido el inicio de una bola de nieve devastadora para el equipo blanco.</t>
+  </si>
+  <si>
+    <t>Sea como sea, lo único claro es que la permanencia del jugador francés en la ciudad de Madrid está complicada. Todo el vestuario parece haberse puesto en su contra. Todos menos Álvaro Carreras que el pobre no se sabe ni la tabla del 1.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Y pensar que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ferran Torres</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> fue el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>detonador</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>caída</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> del dictador </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mbappé</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYA3mcoM8ol/</t>
+  </si>
+  <si>
+    <t>Se están viviendo cosas paranormales en la mesa de BlackJack de Zona Gemelos.</t>
+  </si>
+  <si>
+    <t>En lugar del habitual crupier (Manolito el acondroplásico), los gemelos Zipi y Zape han decidido poner a dos personas con ideologías un pelín opuestas.</t>
+  </si>
+  <si>
+    <t>Por un lado, un judío ortodoxo, el cual encaja perfectamente en un entorno repleto de dinero y avaricia. Y por otro lado, un fanático acérrimo del pintor austriaco que hizo alguna que otra canallada el siglo pasado.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No esperaba ver a un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>judío</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y a un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nazi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pelearse en mesa de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BlackJack</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYC4OCEGoGx/</t>
+  </si>
+  <si>
+    <t>La multigalardonada artista colombiana conocida como Shakira, ha anunciado que sacará una nueva canción con motivo del mundial de fútbol que se celebrará este verano.</t>
+  </si>
+  <si>
+    <t>La artista salida de Barranquilla es mundialmente conocida por su hit 'Waka Waka' que dio la vuelta al mundo en el año 2010, hit que fue la banda sonora para ese mundial de fútbol histórico que ganó la selección española de David Villa, Fernando Torres, Gerard Piqué y Sergio Ramos entre otros.</t>
+  </si>
+  <si>
+    <t>El mundial de este año se celebrará entre Canadá, Estados Unidos y México, y las selecciones de España (con Lamine Yamal y Pedri), Francia (con Dembélé y Mbappé) y Argentina (con Messi y Julián Álvarez) son fuertes candidatas para ganarlo. Veremos qué es lo que sucede.</t>
+  </si>
+  <si>
+    <r>
+      <t>Shakira</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> amenaza con </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sacar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> una nueva </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>canción</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> para este</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mundial</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYDNLFkjQcO/</t>
+  </si>
+  <si>
+    <t>El streamer iShowSpeed visitó República Dominicana en su labor de primermundizar el globo terráqueo.</t>
+  </si>
+  <si>
+    <t>En su visita ahí, estuvo con Alofoke, con Los Futbolitos, con uno que ladraba como loco, y con gente muy rara.</t>
+  </si>
+  <si>
+    <t>Hubo un momento en concreto en el que Speed recibió a un niño a manos de su madre, que le dijo "Oye, puedes firmarle un cromo de Cristiano Ronaldo a mi hijo". Sus seguratas le pasaron rápido porque al ser un niño calvito pensaron que tenía cáncer o algo, pero en realidad solo estaba rapado porque hace escasos días había tenido piojos. Cosas de la vida.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Speed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gestionó esta interacción con un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>niño calvo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> satisfactoriamente</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYKhjWugpva/</t>
+  </si>
+  <si>
+    <t>El rapero 6ix9ine ha celebrado una enorme fiesta en stream para revelar el género del futuro hijo que tendrá con la 'señorita' Aliday Alter (estos raperos no aprenden...).</t>
+  </si>
+  <si>
+    <t>A dicho evento invitó a controversiales y polémicos streamers americanos como el 'brand-risk' canadiense, Adin Ross, el elegido por Kanye West, N3ON, o el looksmaxxing mogger, Clavicular.</t>
+  </si>
+  <si>
+    <t>Durante la celebración, 6ix9ine dijo sin filtro lo que se le pasaba por la cabeza, como ya es costumbre en él, e hizo saber a los asistentes que lo tiene claro: si no es hijo varón, lo que será es un aborto sin pensárselo dos veces. Este comentario generó un silencio brootal.</t>
+  </si>
+  <si>
+    <t>Este se trata del tercer hijo reconocido de 6ix9ine y resulta que los dos que tiene han sido mujeres, por eso tenía tantas ganas de que fuera un niño. Y no solo eso, también durante su truculenta relación con Yailin La Más Viral, convivió estrechamente junto a la hija de Yailin y Anuel AA la cabra del trap.</t>
+  </si>
+  <si>
+    <t>Aliday Alter más tarde preguntó cómo funciona eso de la genética, y si su futuro hijo o hija heredará sus rasgos faciales actuales o los previos a la operación. Nadie fue capaz de resolver dicha incógnita.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6ix9ine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> suelta esta </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>barbaridad</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y genera un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>silencio sepulcral</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYM-R4eDOgT/</t>
+  </si>
+  <si>
+    <t>Saliendo de la clínica se cruzó con Andy o Lucas. No sé cuál es cuál pero me refiero al de la nariz catastrófica.</t>
+  </si>
+  <si>
+    <t>Están volviéndose tendencia en Corea la mala (la del sur) estos vídeos de modelos o influencers entre el público durante los partidos de baseball de la KBO League.</t>
+  </si>
+  <si>
+    <t>Concretamente esta se trata de Kate Shumskaha (o Mimisskate en redes), quien es una cosplayer y modelo rusa que se hizo famosa en su moemnto por guardar parecido con la actriz Scarlett Johansson y por su cosplay de Black Widow.</t>
+  </si>
+  <si>
+    <t>No hemos podido evitar fijarnos en su poco natural forma de respirar, con la boca constantemente abierta y extrañas palpitaciones. Al parecer, se hizo la rinoplastia con el Dr. Nick Riviera de los Simpson por un precio mucho más barato que de normal, y así salió, que ni siquiera puede respirar por la nariz.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cuando la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rinoplastia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> te la hizo el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dr. Nick</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y no hay de otra que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>respirar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> por la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>boca</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYSmsD6TlqR/</t>
+  </si>
+  <si>
+    <t>Hernández Hernández, el árbitro que se encargó de pitar el reciente Clásico entre el Barça y el Madrid, protagonizó este curioso momento gracias a las cámaras que LaLiga ha incorporado para dar el POV de los colegiados a pie de campo.</t>
+  </si>
+  <si>
+    <t>En un momento de máxima tensión futbolística entre los dos equipos, con una jugada que involucraba a Alexander-Arnold Trent, a Gavi, a Dani Olmo, a Pedri y a Jude Bellingham entre otros, el colegiado se encontraba narrando la jugada y asegurando que no estaba ocurriendo nada grave, que todo era fútbol, acabando con la coletilla de "Fútbol papi".</t>
+  </si>
+  <si>
+    <t>"Fútbol papi" - Talavera de la Reina. El árbitro por un momento pensó que era puertorriqueño y que se iba a grabar un remix junto a Lamine Yamal y Jesé Rodríguez.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Árbitro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> español diciendo "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fútbol papi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" como si fuese de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Puerto Rico</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Arcángel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, orgulloso de que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>España</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> les </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>robara</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>oro</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYPoPQIDmNM/</t>
+  </si>
+  <si>
+    <t>El reggaetonero Arcángel tendiendo puentes entre España y Latinoamérica en su último concierto en el Movistar Arena de Madrid durante su gira por el país ibérico.</t>
+  </si>
+  <si>
+    <t>Arcángel sacó a la palestra a esos panchitos cuyo único argumento para justificar su odio contra España consiste en insistir erre que erre en que "España nos robó el oro", invalidándolo completamente y contraargumentando que España, precisamente con ese oro, fue capaz de invertir en las zonas americanas conquistadas y generar progreso y riqueza tanto cultural como de educación e infraestructuras gubernamentales.</t>
+  </si>
+  <si>
+    <t>Dicho eso, el cantante puertorriqueño alabó a 'su madre patria' España y pidió una bulla del público, el cual contestó con gran clamor. ¿Ayudará esto a poner fin a un debate que lleva tanto tiempo? ¿Quién tiene el mejor doblaje, los españoles o los latinoamericanos?</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYQKRc0EZ4v/</t>
+  </si>
+  <si>
+    <r>
+      <t>La</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> madre</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Omar Montes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> embarazada de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hustle Hard</t>
+    </r>
+  </si>
+  <si>
+    <t>Omar Montes ha vuelto a liarla con los reporteros que le atosigan constantemente para sacarle titulares de prensa rosa.</t>
+  </si>
+  <si>
+    <t>Esta vez al cantante se le ha visto pasando por un bache emocional y se ha visto obligado a contarle el por qué a las reporteras de Telecinco, Neox, UNK y PeereiraTV por lo que estaba pasando en su vida personal.</t>
+  </si>
+  <si>
+    <t>Según nos cuenta, recientemente se ha enterado de una noticia acerca de la situación romántica de su señora madre. Su primogenitora se habría quedado embaraza de nada más y nada menos que el mayor liante de Barcelona, Hustle Hard 304, padre del reconocido jugador del FC Barcelona Lamine Yamal, que recientemente ha levantado el título de LaLiga.</t>
+  </si>
+  <si>
+    <t>Al parecer no lo está llevando del todo mal. El cantante confiesa que le gusta como pareja y que aprueba la relación, lo único, que espera que en el mural que Hustle Hard mandó a pintar en la pared de su casa, de un retrato junto a su hijo en el que el padre sale más grande y más llamativo, añada a su mama como muestra de amor verdadero, y figuren los tres.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYXd-IZiro1/</t>
+  </si>
+  <si>
+    <t>Cuando Jordi Wild anunció Dogfight Wild Tournament 4 Tokyo Blood para finales de mayo, una de las peleas anunciadas mezclaba las batallas de freestyle y el boxeo, con dos exponentes muy contrapuestos como lo son los raperos Swit Eme y Mr. Ego.</t>
+  </si>
+  <si>
+    <t>Jordi ha organizado un debate en su podcast The Wild Project con ambos participantes presentes para que aviven las llamas antes del careo y antes de la pelea. Dicho debate se ha calentado bastante hasta el punto de sacar temas personales, acusaciones graves y gritos por doquier.</t>
+  </si>
+  <si>
+    <t>El aire se puede cortar de la tensión que hay entre estos dos, y solo puedo pensar en lo bien que hubiese gestionado esto la presencia de Elxokas para mediar entre ellos y calmar las aguas. Que en paz descanse Xokas. No ha muerto, pero debe estar descansando ahora viendo una peli en el sofá.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Esto sin </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ElXokas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en medio para </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>separarlos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> es </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>muy peligroso</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYXoW4mzO6r/</t>
+  </si>
+  <si>
+    <t>Un aficionado estaba esperando a que empezara el partido entre el Valencia y el Rayo Vallecano de LaLiga cuando aprovechó para ser productivo en ese rato de espera.</t>
+  </si>
+  <si>
+    <t>El aficionado, de avanzada edad, se dispuso a borrar el historial de búsqueda de su móvil, y analizando su historial, se puede apreciar que es un señor con muchas inquietudes biológicas y de divulgación científica.</t>
+  </si>
+  <si>
+    <t>Lamentablemente no todo era positivo. Contaba en su historial con una búsqueda de 'vito quiles facua'. No todo podía ser bueno.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Esperando</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a que</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> empiece</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>partido</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYZIyTIMFpd/</t>
+  </si>
+  <si>
+    <t>Lamine Yamal, con tan solo 18 años, tiene un palmarés histórico, tanto en lo futbolístico como en lo sentimental.</t>
+  </si>
+  <si>
+    <t>Por si no fuera suficiente con sus conquistas en el terreno de juego, su historial amoroso también da de qué hablar. El originario de Manresa ha estado con multitud de actrices de páginas para curiosos y con celebridades como Nicki Nicole, Olivia Rodrigo (rumor inventado por mí) o la exnovia de Tobbal.</t>
+  </si>
+  <si>
+    <t>Pues su primera dama de honor fue Alex Padilla, su amor de la adolescencia. Y así está la madre... Lamine falló el disparo aquí...</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lamine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, era la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>madre</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, no la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hija</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYaOH7GgSkp/</t>
+  </si>
+  <si>
+    <t>John Travolta reaparece ante el público en el festival de Cannes donde ha recibido una Palma de Oro en honor a toda su carrera.</t>
+  </si>
+  <si>
+    <t>A sus 72 años, el mítico actor y director luce más joven que nunca. Ha asistido al evento con una boinita y unas gafitas muy plumíferas, con la barba recortada como un chaval que acaba de salir de la peluquería de SamuBarber, y con una jovialidad impropia de su edad.</t>
+  </si>
+  <si>
+    <t>Todo apunta a que el actor sería una de tantas celebridades con acceso al adrenocromo, el cual es una sustancia que se sustrae de la sangre de niños apavorados y muy asustados y podría ser la clave para la juventud eterna, y siempre se ha rumoreado que las altas esferas del show business lo consiguen gracias al tráfico de menores, muy relacionado con todo lo de la isla de Jeffrey Epstein y con las denuncias públicas de Justin Bieber y más.</t>
+  </si>
+  <si>
+    <t>En febrero de este mismo año el actor Jim Carrey también causó revuelo al hacer una aparición pública, concretamente en los Premios César, donde su cambio físico y sus expresiones faciales generaron muchas teorías sobre dobles, suplantaciones y demás. El mundo está muy raro.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>John Travolta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a sus </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>72 años</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hasta el culo de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>adrenocromo</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYakLlUnAST/</t>
+  </si>
+  <si>
+    <t>El looksmaxxer Clavicular llegó a los juzgados de Miami, donde le esperaba el Final Boss preparado para moggearlo brutalmente.</t>
+  </si>
+  <si>
+    <t>La gente especula que Clav se vio intimidado por la condición de Chad que tenía el juez.</t>
+  </si>
+  <si>
+    <t>El polémico streamer se enfrenta a un juicio donde se decidirá su sentencia por un tiroteo que ocurrió mientras estaba en directo. La sentencia podría tratarse de seis meses de libertad condicional.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Clavicular moggeado</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> por el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>juez</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> que decide su </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sentencia</t>
+    </r>
+  </si>
+  <si>
+    <t>La gala de Eurovisión de este año se celebró anoche por todo lo grande en Viena, Austria, y se alzó ganador el país de Bulgaria con esta canción llamada Bangarang de Skrillex... digo, Bangaranga de DARA.</t>
+  </si>
+  <si>
+    <t>La choni encargada de representar Bulgaria, que es una mezcla entre Naiara de Operación Triunfo y Metrika la madre fundadora, ha logrado la hazaña de bloquearle el primer puesto a Israel, ganando con 516 puntos ante los 343 del "país" situado en el Oriente Próximo.</t>
+  </si>
+  <si>
+    <t>Por otro lado, España, junto a países como Irlanda, Eslovenia, Islandia o Países Bajos, decidió no ser partícipe del evento debido a la participación en este mismo de Israel y la situación humanitaria actual en Gaza, decisión tomada personalmente por el Perro Sánchez. Yo creo que tendríamos que haber llevado a Eurovisión a Ruth la Empoderada y la victoria hubiese estado asegurada.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYbj4pWD_0E/</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Una </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>choni búlgara</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nos ha </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>salvado</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Israel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ganase </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Eurovisión</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYb4g_pk0lb/</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mike Tyson</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cuenta cómo fue intentar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dejar la coca</t>
+    </r>
+  </si>
+  <si>
+    <t>Mike Tyson acudió al podcast del humorista Theo Von y contó la vez que tuvo que buscar ayuda para dejar la coca y poder superar su adicción.</t>
+  </si>
+  <si>
+    <t>Tyson acudió a la consulta del doctor buscando desesperadamente ayuda. Estaba contra las cuerdas (cosa que ni sus rivales en el ring lograban) y necesitaba una solución para dejar la coca.</t>
+  </si>
+  <si>
+    <t>Al contarle su situación al doctor, este estaba especialmente interesado en el producto y en si Mike llevaba encima en ese momento, y sin ninguna vergüenza le llegó a preguntar si podía probar un poco. Al doctor se le pusieron los ojos como platos solo con pensar en la calidad que debía tener el producto comprado por alguien tan forrado como Mike Tyson.</t>
+  </si>
+  <si>
+    <t>El exboxeador ingresó a Rehabilitación y entregó lo que llevaba encima con la intención de volverse mejor persona, y no pudo evitar mirar para atrás, con lo que se dio cuenta de que el doctor estaba especialmente graciosín. A día de hoy sigue convencido de que ese doctor se quedó con su botín y le dio uso lúdico.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYcT7iKDe3s/</t>
+  </si>
+  <si>
+    <t>Las nuevas generaciones vienen pisando fuerte.</t>
+  </si>
+  <si>
+    <t>Este es Chiqui Ibai, un joven patriota británico que acudió a las recientes protestas nacionalistas que han infestado las calles de Reino Unido para quejarse de la sociedad actual del país en cuanto a cuestiones migratorias y la disconformidad social.</t>
+  </si>
+  <si>
+    <t>El pequeño vivió un emotivo momento al arrancarse a iniciar por primera vez una proclama racista, relacionada con los islamistas, que el resto de asistentes continuó satisfactoriamente. La sonrisa en su cara y la aprobación de sus amigos es algo que sana el corazón y que no olvidará jamás.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>futuro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> del </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>racismo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> está en buenas manos</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYdDPEkT-ND/</t>
+  </si>
+  <si>
+    <t>En la liga brasileña, el árbitro del Santos FC - Coritiba cometió un error garrafal que tuvo que pagar Neymar Jr.</t>
+  </si>
+  <si>
+    <t>El colegiado tenía la orden de hacer un cambio del Santos con el que entraba al terreno de juego Robinho Jr, y como justo en ese momento Neymar se encontraba en el borde del campo para recibir atención médica, dio por hecho que él era el jugador que se iba sentado al banquillo, pero ese no era el caso.</t>
+  </si>
+  <si>
+    <t>Neymar se enfureció con dicho error y hasta agarró el papelito en el que se indicaba correctamente que él no era el jugador que habían indicado, pero las decisiones de los árbitros son irrevocables, incluso siendo errores, y se tuvo que sentar.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sientan a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Neymar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> por </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>error</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y muestra el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>papel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> con los </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cambios correctos</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYejaiEjC6H/</t>
+  </si>
+  <si>
+    <t>Durante el escrutinio de votos de las elecciones de Andalucía, conectaron con la sede de 'Por Andalucía' en Sevilla, partido que representa la influencia entre Izquierda Unida y Podemos.</t>
+  </si>
+  <si>
+    <t>El partido liderado por Antonio Maíllo se pegó un batacazo en las urnas y se posicionó como la quinta fuerza política de la comunidad autónoma.</t>
+  </si>
+  <si>
+    <t>Las elecciones de Andalucía las encabezó el PP con un 41,6% de los votos, seguidos por el PSOE con un 22,7% y de VOX con un 13,8%. Otros partidos destacados fueron ADELANTE con un 9,6% y POR ANDALUCÍA con un 6,3%. Juanma Moreno del PP, con 53 escaños, deberá negociar con VOX, que tiene 15 escaños, para gobernar en la nueva legislatura.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Con toda la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>puestada</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> durante las </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>elecciones</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Andalucía</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYemC50z59Y/</t>
+  </si>
+  <si>
+    <t>Durante las celebraciones por ganar la Bundesliga del Bayern de Múnich ocurrió lo siguiente.</t>
+  </si>
+  <si>
+    <t>Unos aficionados del rival histórico, el 1860 München, se colaron en medio de la rúa con una pancarta enorme que desde abajo parecía que simplemente representaba el escudo del equipo.</t>
+  </si>
+  <si>
+    <t>Pero no era el caso. El escudo estaba modificado para mostrar la siguiente frase "FC Bauern Hurensöhne" que se puede traducir como un 'FC Granjeros Hijos de p*ta", en referencia a que es un equipo con un total de 35 títulos de liga porque se trata de una liga de granjeros.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le cuelan al </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bayern</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> un "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Granjeros hijos de puta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" en su celebración</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La tiktoker </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Carlota Marañón</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> amenaza con hacer </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mainstream</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Biberon</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYezcdkD7Q-/</t>
+  </si>
+  <si>
+    <t>La influencer Carlota Marañón está really tapped in y así lo demuestra con las canciones que siempre usa en sus TikToks.</t>
+  </si>
+  <si>
+    <t>Esta vez se encontraba con su novio Andy Waak en un local del centro para tomarse un té matcha antes de ir a una smash burger e ir a lanzar hachas al hachódromo (planazo de viernes), y comentó que necesita actualizar su playlist. Andy le recomendó alguien del panorama underground español, concretamente Biberon, y la influencer hizo saber que lo tiene en su radar y que pronto lo escuchará.</t>
+  </si>
+  <si>
+    <t>Si Carlota Marañón empieza a compartir canciones del Muddy en sus tiktoks, es inevitable que este se vuelva mainstream y acabe por abandonar el cartel del Riverland para grabar su propia Gallery Session, actuar en la Velada de Ibai Llanos e ir de invitado al Hormiguero.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYfM9VPkbjy/</t>
+  </si>
+  <si>
+    <t>Se ha filtrado el argumento de Vinicius discutiendo con su pareja la modelo Virginia Fonseca en un Smash Burger del centro de Madrid.</t>
+  </si>
+  <si>
+    <t>Durante la acalorada conversación que mantuvieron en la que ella le achacaba que no estaba siendo suficientemente detallista con ella y que estaba dejando de lado cosas muy importantes en una relación amorosa, el astro brasileño cortocircuitó y empezó a argumentar que él tenía 2 champions y haciendo gestos a su pareja como insinuando que iba a mandarla a segunda división.</t>
+  </si>
+  <si>
+    <t>Vini en su cabeza a día de hoy sigue pensando que ganó la discusión, de hecho está esperando que le entreguen el Trofeo Sócrates en la gala del balón de oro por ello.</t>
+  </si>
+  <si>
+    <r>
+      <t>Vinicius discutiendo con su pareja</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Yo tengo 2 Champions y tú te vas a segunda</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYfg3utMpCk/</t>
+  </si>
+  <si>
+    <t>El "artista" Frankie Gee directo desde las islas Canarias ha sacado una canción de rap inspirada en el meme de Six Seven.</t>
+  </si>
+  <si>
+    <t>Es un poco como cuando tu padre quiere hacerse el moderno y te dice de jugar a la play contigo, pero en lugar de tu padre es Frankie Gee y es un tio tatuado y con grills en los dientes.</t>
+  </si>
+  <si>
+    <t>En verdad es un temazo, yo espero que el DJ lo pinche la próxima vez que vaya a la discoteca light.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>padre</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> intentando hacerse el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>moderno</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYfhb1oTFCZ/</t>
+  </si>
+  <si>
+    <t>Así auguro que va a ser la última jornada de LaLiga, concretamente el partido entre la Real Sociedad y el Espanyol.</t>
+  </si>
+  <si>
+    <t>Me imagino a Take Kubo marcando y yendo a celebrar a la esquina sacudiendo el culo. Tras eso, todos los jugadores de ambos equipos se acercarían y montarían una orgía.</t>
+  </si>
+  <si>
+    <t>El fútbol no es siempre competitividad y acabar a puñetazos como en el vestuario del Real Madrid. A veces también es esto.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cuando es la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>última jornada</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y ninguno de los </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>equipos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> se juega </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nada</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYhMM05zwvR/</t>
+  </si>
+  <si>
+    <t>El ecuatoriano Piero Hincapié protagonizó un momento curioso en la Premier League ante el Burnley.</t>
+  </si>
+  <si>
+    <t>En un mano a mano con el defensa congoleño del Burnley, Axel Tuanzebe tuvo la mala pata de aparcar el pie en la raja del trasero de Hincapié, con la mala suerte de hacer palanca y bajarle todo el pantalón, dejándole el culamen al descubierto.</t>
+  </si>
+  <si>
+    <t>No sabemos si es que de la potencia del enganche también agarró calzoncillo o es que el ecuatoriano iba en modo comando.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hincapié</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pensaba que era </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fútbol nudista</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYjyKT9zwWU/</t>
+  </si>
+  <si>
+    <t>Unos aficionados brasileños lograron dar con Neymar en este momento tan íntimo para felicitarle por su inclusión en la selección brasileña para el Mundial de 2026.</t>
+  </si>
+  <si>
+    <t>Le cortaron el ñordo a medio caer pero valió la pena porque este momento lo va a recordar siempre.</t>
+  </si>
+  <si>
+    <t>Carlo Ancelotti finalmente decidió contar con el brasileño para este Mundial, por encima de nombres como el de João Pedro o Eseba, que quedaron fuera de la convocatoria. El pueblo brasileño sonríe.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">¡Qué emotivo! Fans </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>felicitan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Neymar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> por ir al </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mundial</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYm5vBMgRjH/</t>
+  </si>
+  <si>
+    <t>Se ha revelado cómo es el palomitero que se venderá en los cines para la proyección en salas de la esperada película Scary Movie 6.</t>
+  </si>
+  <si>
+    <t>La saga de películas de miedo y comedia 'Scary Movie' vuelve este 2026 y los hermanos Wayans se encuentran publicitando de todas las formas posibles la película por programas de TV y radio.</t>
+  </si>
+  <si>
+    <t>No se nota ni nada que los gringos han aprovechado el buen tirón de Torrente Presidente para copiarlo y revivir una saga humorística antigua y exitosa a toda prisa. Chistes de fumetas, incomprensión de las corrientes transexuales, más chistes de fumetas y un bong de cristal para los espectadores. Todo eso es Scary Movie 6.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>palomitero</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Scary Movie 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> es justamente lo que te esperas</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYm6tZuTN5w/</t>
+  </si>
+  <si>
+    <t>Lamine Yamal ha hecho pública su relación con la tiktoker Inés García.</t>
+  </si>
+  <si>
+    <t>Se les ha visto acudiendo a la cena de celebración del FC Barcelona tras ganar LaLiga ante el Real Madrid.</t>
+  </si>
+  <si>
+    <t>El historial de parejas sentimentales del joven futbolista es curioso. Alex Padilla, Nicki Nicole, La Maeb y ahora Inés García entre otros cabos sueltos por ahí. Se ven reflejados sus gustos.</t>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Negro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> con </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>plata</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> no come </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mulata</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYnQpdSz21h/</t>
+  </si>
+  <si>
+    <t>Así es Brasil.</t>
+  </si>
+  <si>
+    <t>En los entrenos de fútbol es tan importante practicar el deporte en sí como practicar los bailes que harás cuando celebres marcar un gol en el campo.</t>
+  </si>
+  <si>
+    <t>Elegir un buen emote para celebrar los goles es una asignatura más en Brasil. Fútbol y samba corre por sus venas.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Entrenando </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">directamente el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>baile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>celebración</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYo6mnyEhWt/</t>
+  </si>
+  <si>
+    <t>La plantilla del FC Barcelona ha asistido al Port Aventura para celebrar el título de LaLiga y Pedri acudió con su pareja Ferran Torres.</t>
+  </si>
+  <si>
+    <t>Mentalizados para tankearse esta montaña rusa, los dos jugadores estaban la mar de ilusionados cuando Pedri dio un vistazo hacia atrás para ver cómo se encontraba su parienta, a lo que le respondió con una miradita clásica que transmite 'Ya hablaremos en casa', y Pedri al momento supo que la había fastidiado sentándose con Ferran y dejando a la novia sola en el asiento de atrás, pero bueno, solo se vive una vez.</t>
+  </si>
+  <si>
+    <t>Sin duda esta noche al llegar a casa Pedri duerme en el sofá, no sin antes cenar una ración de arroz con voces.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Esta noche </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pedri duerme</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sofá</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYpIZxsjwT3/</t>
+  </si>
+  <si>
+    <t>Sonoro guantazo, y por si se había quedado con hambre, otro sopapo de regalo, oferta 2x1.</t>
+  </si>
+  <si>
+    <t>Dos individuos tuvieron esta disputa en la calle cuando presuntamente uno de ellos había tenido comportamientos indebidos con una menor de edad.</t>
+  </si>
+  <si>
+    <t>El justiciero no pudo dejar pasar la situación por alto y decidió encararle y buscar un ápice de cordura en su mente. Al ver que insistía con excusas baratas del tipo "Es que ella dijo que tenía 19" se vio en la obligación de darle un guantazo bien dado en la quijada, y cuando el tipo se puso farruko preguntando si había quedado grabado como prueba, otro guantazo extra todavía más sonoro para que vea que no anda con tonterías.</t>
+  </si>
+  <si>
+    <t>Una pareja que pasaba por ahí decidió meter las narices y ponerse del lado del supuesto pichafloja que la había liado con una menor de edad, que si llamando a la policía, que si siendo una Charo, etc. Lo que hay que ver.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Los dos </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>guantazos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> más </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>satisfactorios</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> que verás en </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mucho tiempo</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYr4lXOAM79/</t>
+  </si>
+  <si>
+    <t>Shakira amenaza con sacarle un videoclip a su canción 'Dai Dai' que ha hecho junto a Burna Boy para el Mundial de 2026.</t>
+  </si>
+  <si>
+    <t>En un alarde de creatividad, el equipo de Shakira vuelve a recurrir a la estética desolada africana para ver si así el público vincula la canción mentalmente con el 'Waka Waka' del mundial de 2010 y logra generar un poco de ruido, pese a ser coworker music.</t>
+  </si>
+  <si>
+    <t>No hemos podido evitar fijarnos también en la similitud que guarda con ese capítulo de La Que Se Avecina en el que Amador Rivas monta una ONG con niños así marroncitos. ¿Se ha plagiado Shakira del Capitán Salami?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Es clavado al </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>capítulo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LQSA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en el que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Amador</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> monta una </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ONG</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYsD6bFDpbW/</t>
+  </si>
+  <si>
+    <t>Los Mossos d'Esquadra han atrapado a tiros en Barcelona a un miembro de una banda criminal que lleva años actuando principalmente en la zona del Maresme, y están abiertos a contrataciones para bodas, bautizos y comuniones.</t>
+  </si>
+  <si>
+    <t>Se cree que los motivos son porque se trata de un miembro de una banda criminal, pero el verdadreo motivo es que se trata de un propietario de un BMW, y este tipo de calaña debería estar totalmente baneada.</t>
+  </si>
+  <si>
+    <t>Este es uno más de tantos actos de violencia que están azotando la ciudad condal. Se avecina Mad Max: Barcelona Edition.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tiroteo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Barcelona</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> por ser </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>propietario</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BMW</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYtsT4oHQkr/</t>
+  </si>
+  <si>
+    <t>El mítico portero alemán Manuel Neuer tiene una relación muy paternalista con el que va a ser su heredero bajo los palos del Bayern de Múnich, Jonas Urbig, de tan solo 22 años.</t>
+  </si>
+  <si>
+    <t>Está siendo un gran mentor para él y no solo en lo futbolístico. También le está enseñando cosas útiles para fuera del campo.</t>
+  </si>
+  <si>
+    <t>En esta ocasión se puede apreciar cómo le aconseja que debería evitar el saludo nacional socialista del pintor austriaco, y saludar a la ofición de otra forma con menos riesgo.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Neuer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> le aconseja a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Urbig</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> evitar el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>saludo nazi</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYt2mbFDzIk/</t>
+  </si>
+  <si>
+    <t>Imagina meterte tanto que tu camello se piense que lo estás revendiendo.</t>
+  </si>
+  <si>
+    <t>Charlie Sheen cuenta en una entrevista la vez que el cártel que le suministraba crack se pensó que él era un distribuidor que les estaba haciendo competencia desleal, cuando en realidad el tipardo se lo fumaba toda él.</t>
+  </si>
+  <si>
+    <t>Levantó las alarmas del cártel, que le distribuía a través de un intermediario, y estaban convencidos de que era alguien que revendía la mercancía. Dicho middle man tuvo que romper con la confidencialidad y explicarles quién era el cliente con el que estaban tratando, y cuando descubrieron que era Charlie Sheen ahí ya sí les cuadró que fuera para uso personal.</t>
+  </si>
+  <si>
+    <t>Charlie se encuentra actualmente tras una vida llena de excesos y abuso. En la misma entrevista recuerdan la vez que el loco se fue a la colina y se fumó 2 kilos de crack a cara perro. Y ahí sigue el tío, vivito y coleando, representando la verdadera salud.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Charlie Sheen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pedía tanto </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>crack</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> que el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cártel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pensó que era para </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vender</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYuPiMFz0IA/</t>
+  </si>
+  <si>
+    <t>Kylian Mbappé es que ya ni se esfuerza. El vestuario del Real Madrid está completamente roto, y el dictador Kiki ya ni se esfuerza en hacer ver que se deja la piel en el campo.</t>
+  </si>
+  <si>
+    <t>Desubicado como un pato mareado, ahí lo vemos en el último partido de liga ante el Athletic.</t>
+  </si>
+  <si>
+    <t>Mbappé se lleva el pichichi de LaLiga con la cantidad de 8 penaltis de un total de 25 goles. Injustamente ,el pirata Vedat Muriqi se queda a las puertas del pichichi con 23 goles, 5 de ellos de penalti, con los que lamentablemente no ha podido salvar al Mallorca del descenso.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mbappé</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ya es que ni lo </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intenta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> disimular</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYuc0fpjnKi/</t>
+  </si>
+  <si>
+    <t>Bad Bunny ha realizado dos conciertos back to back en la ciudad de Barcelona con su DeBÍ TiRAR MáS FOToS World Tour y así se ven las afueras del Estadi Lluís Companys durante el concierto.</t>
+  </si>
+  <si>
+    <t>Han sido dos días muy especiales para la gente charca que luego ha ido a cenar una smash burger para comentar lo bien que se lo pasaron pagando 500€ de entrada para poder grabarse cuatro tiktoks con las canciones más populares de Bad Bunny, mientras a duras penas lo podían ver.</t>
+  </si>
+  <si>
+    <t>Por si no fuese suficientemente charca ir al concierto de Bad Bunny, hay otro nivel todavía más charcoso, que es haberte quedado sin entrada e ir a las afueras del Estadio Olímpico a juntarte con los charcosos supremos para bailotear la música de dentro del estadio que se logra oír un poco.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No se va a lograr nada más </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>charca</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> que el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">concierto </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bad Bunny</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYuoqhXTrDL/</t>
+  </si>
+  <si>
+    <t>En el minuto 12 del partido entre el FC Andorra y el Ceuta de LaLiga Hypermotion, el portero cometió este error garrafal que acabó en gol en propia.</t>
+  </si>
+  <si>
+    <t>El portero Nico Ratti le dio un pase al defensa Martí Vila, el cual decidió devolver al portero, y fue ahí cuando Ratti intentó despejarlo con la mala pata de resbalarse y dejar pasar el balón contra la red.</t>
+  </si>
+  <si>
+    <t>Tras esta actuación nefasta, el portero fue sustituido en el descanso por Jesús Owono que defendió los palos durante la segunda parte del partido, tampoco con mucha suerte.</t>
+  </si>
+  <si>
+    <t>Se comenta que Gerard Piqué decapitó con sus propias manos a Ratti en los mismos vestuarios del estadio del Andorra.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Error garrafal del </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>portero</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> del </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FC Andorra</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYxa0a9NQji/</t>
+  </si>
+  <si>
+    <t>¡Por las barbas de Matusalén! No se había visto un escándalo público tan grande desde la caída del muro de Berlín.</t>
+  </si>
+  <si>
+    <t>Se ha cometido una atrocidad en vivo en un supermercado de Matalascañas cuando dos carritos se han visto hastiados de su jornada laboral y han decidido desfogarse manteniendo relaciones sin importarles que pasasen clientes por delante.</t>
+  </si>
+  <si>
+    <t>Desde aquí estamos muy a favor de la revolución de la clase obrera pero a su vez impugnamos el amor entre personas del mismo sexo, así que estamos indecisos sobre si apoyar este suceso o no.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">¡Qué obscenidad! Dos </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>carritos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>compra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> copulando en </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>público</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DYzgbltTpqN/</t>
+  </si>
+  <si>
+    <t>Luis Suárez tiene tantas ganas de morder que le da igual si es a un rival o a un compañero.</t>
+  </si>
+  <si>
+    <t>En este altercado ocurrido en un partido del Inter Miami FC, el delantero uruguayo mordió a su compañero Jordi Alba tras confundirlo con un rival.</t>
+  </si>
+  <si>
+    <t>Se rumorea que este podría haber sido el motivo por el que se retiró.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Luis Súarez</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, fruto de una confusión, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>muerde</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jordi Alba</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DY2IVImCfrs/</t>
+  </si>
+  <si>
+    <t>Todo está tan caro que hasta una multimillonaria como Kylie Jenner hace uso de la mítica táctica de colar la petaquita en el bolso.</t>
+  </si>
+  <si>
+    <t>Timothée Chalamet y Kylie Jenner asistieron a apoyar a los New York Knicks en el partido de semifinales donde presenciaron cómo el equipo lograba la victoria y se clasificaba a la final de la NBA, donde se medirá contra quien gane la semifinal de la conferencia oeste (los Oklahoma Thunder o los San Antonio Spurs).</t>
+  </si>
+  <si>
+    <t>Imagina lo overpriced que está todo lo que venden en los eventos deportivos, sea un triste bocata de chorizo en un partido de fútbol o una insípida cerveza en un partido de basket, que hasta Kylie Jenner, con un patrimonio que supera con creces los 500 millones de dólares, hace el truco del almendruco colando alcohol en su bolso para evitar dejarse un riñón en comprar un cubatilla ahí mientras ve el partido.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Todo está carísimo, hasta </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kylie Jenner</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cuela</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> alcohol</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bolso</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DY2TYlpFZRl/</t>
+  </si>
+  <si>
+    <t>Pepe Viyuela, el que interpretaba a Javi, el calvo frutero de la serie Aida, debe andar corto de pasta o si no no me explico esto. Se ha puesto a fardar de lujos y de riquezas para vendernos un curso con el que según él, logrará que estemos en nuestro prime.</t>
+  </si>
+  <si>
+    <t>Este ha leído por ahí que gente como Llados Fitness o Xavi Esquerigüela se están forrando a base de vender cursos falsos y ha decidido hacer lo mismo.</t>
+  </si>
+  <si>
+    <t>Todo esto se trata de una broma hecha por la banda 'La Milagrosa' para promocionar a saber qué, la verdad es que no he investigado mucho, tengo que ir a recoger a los niños al cole y me pilláis liado preparándoles la merienda.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>calvo de Aida</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> se apunta a la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>moda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vender cursos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> milagrosos</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DY2eH4HEoeC/</t>
+  </si>
+  <si>
+    <t>Han creado una versión ni**a de Woody, el afable vaquero de Toy Story, y como no podía ser, han incluido los tópicos raciales propios de la raza negra.</t>
+  </si>
+  <si>
+    <t>Piezas de pollo frito, rodajas de sandía, vasos de lean, música rap. Todo lo que un personaje negro debe tener. Y además, por supuesto el Woody negro cuenta con una pistola, a diferencia del Woody blanco original.</t>
+  </si>
+  <si>
+    <t>El propietario de este juguete en lugar de llamarse Andy se llama André, y probablemente viva en una casa prefabricada en los suburbios y no tenga un padre presente en su vida.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Crean un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Woody negro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, y a diferencia del blanco, este tiene </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pistola</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DY4Yp1sgF54/</t>
+  </si>
+  <si>
+    <t>El hermano de George Floyd se hace una cadena en honor al difunto donde se le puede ver medio león medio adicto al fentanilo.</t>
+  </si>
+  <si>
+    <t>Se cumplen 6 años desde la muerte de George Foyd sin respiración bajo la rodilla de un policía, y para celebrar el que podría ser el mejor día de su vida, su hermano se ha bañado en oro con esta chain peculiar.</t>
+  </si>
+  <si>
+    <t>Según él, representa, a parte de su espíritu de guerrero, su breve carrera como atleta juvenil, durante sus años de instituto y universidad, concretamente por su equipo del instituto llamado 'Jack Yates Lions'.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El hermano de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>George Floyd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> se hace una </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cadena horrenda</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DY4uBdiFVtG/</t>
+  </si>
+  <si>
+    <t>Tras 13 años de beef incesante, Katy Perry y Chief Keef han arreglado sus diferencias.</t>
+  </si>
+  <si>
+    <t>En 2013, Katy Perry criticó por Twitter la canción 'Hate Bein' Sober' tras escucharla en la radio, a lo que Chief Keef respondió con el calentón diciéndole de todo. Acto seguido Katy Perry se disculpó diciéndole que no sabía que esa canción era suya y que en general le gusta como artista, así que Mr. Keef se disculpó de vuelta, pero quedó esa tensión que perduró durante los años.</t>
+  </si>
+  <si>
+    <t>Recientemente, Katy Perry lanza un álbum que consigue ser triple disco de cartón en ventas y ha tenido que recurrir a invocar al Dios del Trap de Chicago para tener un poco de sonido, así que se les ha visto juntos en el estudio haciendo nueva música.</t>
+  </si>
+  <si>
+    <r>
+      <t>Chief Keef</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Katy Perry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> arreglan su </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>beef</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DY49SV_EldR/</t>
+  </si>
+  <si>
+    <t>6ix9ine tuvo que hacer de traductor en tiempo real para ayudar a su colega Deshae a ligar con una venezolana.</t>
+  </si>
+  <si>
+    <t>El streamer Deshae Frost prendió stream para celebrar junto a 6ix9ine un Taco Tuesday en su casa con piscina llena de latinas polioperadas. Se quedó prendado de una venezolana con la que la comunicación se le complicaba puesto que ni ella hablaba inglés fluidamente, ni mucho menos él dominaba el español.</t>
+  </si>
+  <si>
+    <t>Pero el controversial rapero Tekashi 6ix9ine llegó al rescate para hacer de intérprete y lograr que surgiera el amor entre esos dos individuos, con traducciones muy fieles a la realidad y para nada alteradas. Un gesto que demuestra lo buen amigo que es.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6ix9ine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> es el mejor </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>traductor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Inglés-Español</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DY5MJs3jaaM/</t>
+  </si>
+  <si>
+    <t>La comunidad científica ha dejado todas sus tareas de lado y se ha unido para determinar si esta persona se trata de un twink gay o de una lesbiana con el pelo corto.</t>
+  </si>
+  <si>
+    <t>Este nuevo sujeto ha generado un quebradero de cabeza para todos los científicos. Ninguno de sus rasgos físicos sirve para decantarse al 100% hacia un lado o hacia al otro, y sus características están generando mucho debate y confrontación.</t>
+  </si>
+  <si>
+    <t>La teoría que está ganando más fuerza es que no se trata ni de un twink gay ni de una lesbiana pelo corto, si no que se trata de Nil Ojeda.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ciencia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> no logra </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>determinar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> si se trata de un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gay</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> o de una </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lesbiana</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DY7IsUNCHcy/</t>
+  </si>
+  <si>
+    <t>Dula Peep ha publicado en colaboración con Service95 una lista en Google Maps con sus lugares favoritos alrededor del mundo.</t>
+  </si>
+  <si>
+    <t>Una lista de más de 130 lugares que incluye restaurantes, tiendas, bares y más de multitud de ciudades.</t>
+  </si>
+  <si>
+    <t>No hemos podido evitar fijarnos en los lugares que ha elegido Dua Lipa en España. Entre bares de tapeo y restaurantes con estrella michelín, nos ha sorprendido encontrar el bar 'Una Grande Libre', humilde bar regentado por el chino Chen que enaltece la imagen del general Francisco Franco, que según él, hizo que España fuera una nación grande y libre.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Una grande libre</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">' entre los lugares favoritos de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dua Lipa</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DY9qprYlQVP/</t>
+  </si>
+  <si>
+    <t>Durante un evento en Londres para revelar detalles sobre la película Toy Story 5 de Disney Pixar que llegará a los cines el 18 de junio, estuvieron presentes los actores que dan voz a los entrañables juguetes animados.</t>
+  </si>
+  <si>
+    <t>Llegó el momento en el que el elenco de actores decidió recrear el clásico momento de la saga en el que se dice la frase 'Andy se está viniendo' y los juguetes deben hacerse los muertos para que el chico no descubra que sus juguetes tienen vida.</t>
+  </si>
+  <si>
+    <t>Curiosamente, esto no fue una simple referencia al momento cinematográfico. También sirvió de homenaje al difunto Charlie Kirk y fue una recreación del instante de su trágica muerte. Un aplauso a estos actores entre los que se encuentran Tom Hanks, Tim Allen, Joan Cusack y Eduardo Casanova entre otros.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El cast de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Toy Story 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> recrea la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>muerte</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Charlie Kirk</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DY99juaG-2K/</t>
+  </si>
+  <si>
+    <t>Los bailarines de Aitana le demostraron a Plex que tiran para el otro lado a solas en el baño.</t>
+  </si>
+  <si>
+    <t>El youtuber YoSoyPlex se rayó tela cuando vio que en la coreografía de su novia Aitana Ocaña, la cantante restregaba su pepitilla en la cara de sus dos bailarines varones. Esto le activó los celos y se vio obligado a preguntar acerca de ellos.</t>
+  </si>
+  <si>
+    <t>Pero las inseguridades se esclarecieron rápido cuando pudo hablar con ellos y descubrió que eran bujarrillas de campeonato, con lo que no hay nada de que preocuparse... o eso cree él. Porque probablemente le preguntes a alguno de esos bailarines el once titular de la selección española que ganó el mundial y te lo diga sin ningún error.</t>
+  </si>
+  <si>
+    <r>
+      <t>Plex</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, más tranquilo tras ver que los </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bailarines</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Aitana</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> son </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bujarrillas</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DY-UzVtAIoQ/</t>
+  </si>
+  <si>
+    <t>Travieso Scott, el personaje del Fortnite que creo que en sus tiempos libres también hace música, sorprende al aparecer en la final de la Champions entre el PSG y el Arsenal.</t>
+  </si>
+  <si>
+    <t>Pese a ser estadounidense y por lo tanto no saber ni papa de fútbol, se le ha visto muy cercano al mundo del balompié, sobre todo desde su exitosa colaboración junto al FC Barcelona sustituyendo el logo de Spotify en la equipación durante el clásico contra el Real Madrid.</t>
+  </si>
+  <si>
+    <r>
+      <t>Travis Scott</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> el del Fortnite en la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>final</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Champions</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DY-ezmoFFA3/</t>
+  </si>
+  <si>
+    <t>En el cara a cara entre Paweł Jóźwiak y Lukasz Bielon previo a su próximo combate de MMA, este último se ganó todo el protagonismo con la vacilada canallesca que le hizo a su rival.</t>
+  </si>
+  <si>
+    <t>En cuanto tenía el rostro de su rival a escasos centímetros del suyo, amagó con buscar algo en sus bolsillos, y lo que sacó fue una peineta con su dedo del medio y acto seguido una bofetada limpia.</t>
+  </si>
+  <si>
+    <t>El rival se alteró como un gorila espalda plateada, mientras Lukasz mantuvo la compostura y se puso a hacer jestermaxxing burlándose del rival como un niño pequeño.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La mayor vacilada en un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cara a cara</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MMA</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DY_sIyllGgl/</t>
+  </si>
+  <si>
+    <t>Los hermanos Russo al parecer están del lado de los MDLR franceses y usan sus varitas mágicas para atacar a la policía antidisturbios.</t>
+  </si>
+  <si>
+    <t>El PSG ha ganado la Champions y sus aficionados, por extraño que parezca, salen a celebrarlo destrozando y quemando todo lo que ven por la calle. Pues Alex Russo junto a sus hermanos Justin y Max se encuentran también por ahí en un crossover inesperado y están lanzando hechicos para apaciguar a los policías.</t>
+  </si>
+  <si>
+    <t>Supongo que se trata de la grabación de la tercera temporada del reboot de la serie, llamado 'Wizards Beyond Waverly Place' que se puede sufrir en Disney Plus.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Los </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>magos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Waverly Place</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> atacando a la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>policía</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>París</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZAgtAIzvLU/</t>
+  </si>
+  <si>
+    <t>Los jugadores de la selección senegalesa no pueden creer lo que ven sus ojos.</t>
+  </si>
+  <si>
+    <t>Han llegado a Estados Unidos y ya están entrenando en los estadios que se usarán para el Mundial.</t>
+  </si>
+  <si>
+    <t>Concretamente este es uno que no albergará partidos, el Bank of America Stadium de Carolina del Norte, pero preocupa el hecho de que muchos de los estadios podrían compartir el mismo problema: son campos para fútbol americano, y el césped es distinto al que se usa en el fútbol de verdad, lo que hace que la pelota no bote tanto.</t>
+  </si>
+  <si>
+    <t>Si esto es algo que no se solventa antes de que empiece el Mundial, podríamos estar ante uno de los mundiales con fútbol más lento y pesado en muchos años.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Comprobando lo </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>botan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> los </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>balones</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en un estadio del </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mundial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>USA</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZCx4q0zuu7/</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>carrito médico atropella</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a un jugador en pleno partido</t>
+    </r>
+  </si>
+  <si>
+    <t>Esto ha ocurrido en la segunda división ecuatoriana.</t>
+  </si>
+  <si>
+    <t>En el encuentro entre Liga de Portoviejo y El Nacional, el carrito de asistencia médica se estaba llevando a un jugador herido y en el camino atropelló a otro.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZFXNsnDT3y/</t>
+  </si>
+  <si>
+    <t>Sergio Ramos se ha puesto un traje y unas gafitas para parecer un tipo inteligente y se ha ido a exponer su plan para comprar el Sevilla FC.</t>
+  </si>
+  <si>
+    <t>Recuerda mucho a cuando te toca exponer una presentación sobre la célula eucariota ante toda tu clase y no te lo has preparado un cagarro.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sergio Ramos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> exponiendo la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>célula eucariota</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZFcKxDznpR/</t>
+  </si>
+  <si>
+    <t>En un amistoso entre Canadá y Uzbekistán que ha quedado 2 a 0 hemos podido comprobar un poco cuál es el nivel actual de estas selecciones.</t>
+  </si>
+  <si>
+    <t>En esta jugada de Uzbekistán protagonizada por el futbolista Eldor Shomurodov se puede comprobar que jugadores de ambas selecciones tienen carencias. Pinta un mundial curioso.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Este es el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nivel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de algunas de las </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>selecciones</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> del </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mundial</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZFmMEXinYj/</t>
+  </si>
+  <si>
+    <t>El nivel del charcómetro está por las nubes con los conciertos de Bad Bunny.</t>
+  </si>
+  <si>
+    <t>En uno de sus conciertos en la ciudad de Madrid se ha podido ver a un chico de seguridad llorando a moco tendido con la canción 'Callaíta' de Bad Bunny, y cuesta imaginarse a alguien a lagrimones escuchando "Ella es callaíta pero pal sexo es atrevida".</t>
+  </si>
+  <si>
+    <t>Existe una porción demasiado grande de la sociedad que te dirá que esta letra es profundísima y que le llega a la patata. Y esa gente se encuentra entre nosotros y lidiamos con ellos a diario.</t>
+  </si>
+  <si>
+    <r>
+      <t>Llorar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> con "Ella es callaíta pero pal sexo es atrevida" es otro </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nivel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>charca</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZFoBshTDM2/</t>
+  </si>
+  <si>
+    <t>El estadounidense Christian Pulisic que milita en el A.C. Milan está con la selección americana preparándose para el mundial 2026.</t>
+  </si>
+  <si>
+    <t>En un partido amistoso contra la selección de Senegal, que quedó 3-2 a favor de USA, al terminar, el jugador se dio la mano con los jugadores rivales, y nada más darle la mano a Krépin Diatta se limpió la mano, como cuando un político le da la mano a los niños pobres y acto seguido se le ve desinfectándose de los gérmenes.</t>
+  </si>
+  <si>
+    <t>No por nada el delantero recibe el mote de Capitán América.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Futbolista</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>USA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> se </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>limpia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> la mano tras tocar a un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>negro</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZFyRfklZJB/</t>
+  </si>
+  <si>
+    <t>¿Quién es el mayor villano de la actualidad?</t>
+  </si>
+  <si>
+    <t>Si nos ceñimos al lore de los Minions, siempre han servido al mayor villano de cada época. Ese dato nos da a entender que entre el año 1933 y el 1945 es prácticamente seguro que sirvieron a cierto pintor austriaco bigotudo, aunque ese no es el tema del que estamos hablando hoy.</t>
+  </si>
+  <si>
+    <t>Han sacado una promoción de la próxima película de la saga llamada 'Minions &amp; Monsters' y no podía ser con otra persona que con el mayor villano de la actualidad, el dictador Kylian Mbappé, que tiene aterrorizado al vestuario del Real Madrid y cuenta con múltiples cadáveres futbolísticos a sus espaldas. Admás, tiene en común con los minions que a él también le gusta la banana.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Históricamente los </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>minions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sirven al </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mayor villano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de cada </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>época</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZHjCb5DUuJ/</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No sé si </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Macron</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> está con la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>selección francesa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> o con reclusos </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>inmigrantes</t>
+    </r>
+  </si>
+  <si>
+    <t>El presidente de Francia, Emmanuel Macron, visitó en Clairefontaine a los jugadores de la selección francesa, donde se encuentran concentrados cara al Mundial 2026.</t>
+  </si>
+  <si>
+    <t>Ahí, junto a su esposa Brigitte Macron, tuvo la oportunidad de saludar, dar ánimos e intercambiar unas palabras con jugadores franceses como Ousmane Dembélé, Michael Olise, Rayan Cherki, William Saliba, Désiré Doué, N'Golo Kanté, Aurélien Tchouaméni, Jules Koundé o el dictador Kylian Mbappé.</t>
+  </si>
+  <si>
+    <t>Por lo que sea, ver a todos esos jugadores, la mayoría de ascendencia africana, y todos uniformados de chándal, hizo que pareciera más una visita del presidente Macron a un centro penitenciario de extranjeros, que una visita a la concentración de la selección de su país.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZIAhCIndVW/</t>
+  </si>
+  <si>
+    <t>Un profesor musulmán estaba resolviendo dudas de sus alumnos cuando uno le preguntó lo siguiente:</t>
+  </si>
+  <si>
+    <t>"He estado pensando en llevar a cabo una operación de martirio, y me han hablado de un nuevo método que consiste en insertar cápsulas explosivas por el trasero. Para poder hacerlo, debería, durante un período de tiempo, dejar que me sodomicen para ensanchar el bul y que quepan los explosivos. Mi duda es, ya que la sodomía está prohibida pero mis intenciones son nobles, ¿estaría cometiendo pecado?"</t>
+  </si>
+  <si>
+    <t>El profesor fue tajante con su respuesta. El Jihad es el pináculo del Islam y está por encima de todo, así que si se tiene que dejar petar el bul por el Jihad, que lo haga, que ya será perdonado.</t>
+  </si>
+  <si>
+    <r>
+      <t>¿</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ensancharte</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> para que te quepan </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>explosivos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> es halal?</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZIXstZAAZz/</t>
+  </si>
+  <si>
+    <t>El tenista madrileño Rafael Jódar, actualmente de 19 años, es una gran sensación del mundo del tenis español, y acaba de ser derrotado por Zverev en cuartos de final del Roland Garros.</t>
+  </si>
+  <si>
+    <t>En este vídeo que grabó hace casi dos años con el C.D. Leganés, visitando su estadio, conociendo a sus diretivos y compartiendo su amor de toda la vida por el equipo, no podemos evitar fijarnos en el tallaje de su chaqueta, el cual actúa como componente cómico.</t>
+  </si>
+  <si>
+    <t>Es un clásico en la historia de los dibujos animados o en la comedia física, mostrar a dos niños o incluso a dos enanos, uno sentado en los hombros del otro, y una chaqueta enorme por encima para simular que se trata de un adulto de estatura media, quedando bastante cómico, con la finalidad de colarse en la sala de cine, ligar con una joven apuesta o comprar tabaco.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rafa Jódar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> parece un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>enano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hombros</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de otro con una </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chaqueta grande</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZIaYBvzjuz/</t>
+  </si>
+  <si>
+    <t>El aura que transmite Kylian Mbappé saludando es de puro dictador.</t>
+  </si>
+  <si>
+    <t>El presidente de Francia, Emmanuel Macron, visitó en Clairefontaine a los jugadores de la selección francesa, donde se encuentran concentrados cara al Mundial 2026, y se encontraron tanto el presidente de la nación como el dictador, contando Francia con un sistema político único en el mundo.</t>
+  </si>
+  <si>
+    <t>Es alguien que tanto en los equipos por los que ha pasado como en la selección francesa es temido y con razón, ya que ha tirado siempre de sus hilos para deshacerse de la gente que le ponía trabas.</t>
+  </si>
+  <si>
+    <r>
+      <t>Mbappé</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> se mueve literalmente como un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dictador</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZKoMXhCfxQ/</t>
+  </si>
+  <si>
+    <t>Charlie Kirk, el que lleva la llama, al fin ha recibido un homenaje a su altura.</t>
+  </si>
+  <si>
+    <t>Un fontanero italiano bigotudo llamado Mario Mario ha crafteado esta fuente con el rostro de Charlie Kirk esculpido, desde la que sale agua expulsada a través de un agujero en el cuello, simulando la herida de bala que recibió Charlie, contando o no contando violencia de pandillas.</t>
+  </si>
+  <si>
+    <t>Ya hace 9 meses del fallecimiento de Charlie Kirk. Mi pareja y yo ese día copulamos salvajemente tras oír la trágica noticia de su muerte, con tan mala pata que la embaracé con mi potencia desmedida y mi alta testosterona. Hoy ha nacido mi pequeño Carlitos, y le veo un rostro que se me hace familiar... ¿será la reencarnación de Mr. Kirk?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hacen una </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fuente</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en honor a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Charlie Kirk</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZK9KbgheOL/</t>
+  </si>
+  <si>
+    <t>El grupo A del Mundial está conformado por México, Sudáfrica, Corea del Sur y Chequia.</t>
+  </si>
+  <si>
+    <t>Es el grupo de la inclusión, el grupo que celebra sus diferencias.</t>
+  </si>
+  <si>
+    <t>México trae tacos y chimichangas, Sudáfrica dice Ooga Booga y viene con sus lanzas, Corea del Sur dice Ching Chong y tiene los ojos rasgados, y Chequia pues bueno, se salva en esta ocasión, pero probablemente te roben el coche mientras no miras.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">grupo A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">del </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mundial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> es básicamente esto</t>
     </r>
   </si>
 </sst>
@@ -20380,7 +25589,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -20388,6 +25597,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -20722,7 +25934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S304"/>
+  <dimension ref="A1:S415"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.42578125" customWidth="1"/>
@@ -26574,7 +31786,7 @@
       </c>
       <c r="G182" s="1"/>
       <c r="H182" s="1">
-        <v>94000</v>
+        <v>93000</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>906</v>
@@ -26676,7 +31888,7 @@
       </c>
       <c r="G185" s="1"/>
       <c r="H185" s="1">
-        <v>83000</v>
+        <v>82000</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>923</v>
@@ -27197,7 +32409,7 @@
       </c>
       <c r="G201" s="1"/>
       <c r="H201" s="1">
-        <v>277000</v>
+        <v>278000</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>1005</v>
@@ -27296,7 +32508,7 @@
       </c>
       <c r="G204" s="1"/>
       <c r="H204" s="1">
-        <v>471000</v>
+        <v>472000</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>1021</v>
@@ -27739,7 +32951,7 @@
       </c>
       <c r="G217" s="1"/>
       <c r="H217" s="1">
-        <v>246000</v>
+        <v>248000</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>1094</v>
@@ -27772,7 +32984,7 @@
       </c>
       <c r="G218" s="1"/>
       <c r="H218" s="1">
-        <v>413000</v>
+        <v>416000</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>1099</v>
@@ -27873,7 +33085,7 @@
       </c>
       <c r="G221" s="1"/>
       <c r="H221" s="1">
-        <v>618000</v>
+        <v>619000</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>1117</v>
@@ -28052,7 +33264,7 @@
         <v>1145</v>
       </c>
       <c r="H226" s="1">
-        <v>90000</v>
+        <v>89000</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>1146</v>
@@ -28425,7 +33637,7 @@
       </c>
       <c r="G236" s="1"/>
       <c r="H236" s="1">
-        <v>1800000</v>
+        <v>1900000</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>1208</v>
@@ -28766,7 +33978,7 @@
       </c>
       <c r="G245" s="1"/>
       <c r="H245" s="1">
-        <v>391000</v>
+        <v>392000</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>1270</v>
@@ -29424,7 +34636,7 @@
       </c>
       <c r="G263" s="1"/>
       <c r="H263" s="1">
-        <v>289000</v>
+        <v>290000</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>1383</v>
@@ -29499,7 +34711,7 @@
       </c>
       <c r="G265" s="1"/>
       <c r="H265" s="1">
-        <v>3900000</v>
+        <v>4000000</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>1395</v>
@@ -29774,7 +34986,7 @@
       </c>
       <c r="G272" s="1"/>
       <c r="H272" s="1">
-        <v>741000</v>
+        <v>744000</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>1446</v>
@@ -29815,7 +35027,7 @@
         <v>1453</v>
       </c>
       <c r="H273" s="1">
-        <v>332000</v>
+        <v>333000</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>1454</v>
@@ -29854,7 +35066,7 @@
       </c>
       <c r="G274" s="1"/>
       <c r="H274" s="1">
-        <v>272000</v>
+        <v>289000</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>1461</v>
@@ -29976,7 +35188,7 @@
       </c>
       <c r="G277" s="1"/>
       <c r="H277" s="1">
-        <v>8200000</v>
+        <v>8300000</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>1484</v>
@@ -30129,7 +35341,7 @@
       </c>
       <c r="G281" s="6"/>
       <c r="H281" s="6">
-        <v>250000</v>
+        <v>252000</v>
       </c>
       <c r="I281" s="6" t="s">
         <v>1518</v>
@@ -30168,7 +35380,7 @@
       </c>
       <c r="G282" s="6"/>
       <c r="H282" s="6">
-        <v>188000</v>
+        <v>189000</v>
       </c>
       <c r="I282" s="6" t="s">
         <v>1524</v>
@@ -30492,7 +35704,7 @@
       </c>
       <c r="G290" s="6"/>
       <c r="H290" s="6">
-        <v>800000</v>
+        <v>809000</v>
       </c>
       <c r="I290" s="6" t="s">
         <v>1580</v>
@@ -30570,7 +35782,7 @@
       </c>
       <c r="G292" s="6"/>
       <c r="H292" s="6">
-        <v>882000</v>
+        <v>886000</v>
       </c>
       <c r="I292" s="6" t="s">
         <v>1592</v>
@@ -30833,7 +36045,7 @@
       </c>
       <c r="G299" s="6"/>
       <c r="H299" s="6">
-        <v>218000</v>
+        <v>219000</v>
       </c>
       <c r="I299" s="6" t="s">
         <v>1635</v>
@@ -30872,7 +36084,7 @@
       </c>
       <c r="G300" s="6"/>
       <c r="H300" s="6">
-        <v>739000</v>
+        <v>750000</v>
       </c>
       <c r="I300" s="6" t="s">
         <v>1636</v>
@@ -30908,7 +36120,7 @@
       </c>
       <c r="G301" s="6"/>
       <c r="H301" s="6">
-        <v>410000</v>
+        <v>411000</v>
       </c>
       <c r="I301" s="6" t="s">
         <v>1669</v>
@@ -30944,7 +36156,7 @@
       </c>
       <c r="G302" s="6"/>
       <c r="H302" s="6">
-        <v>293000</v>
+        <v>314000</v>
       </c>
       <c r="I302" s="6" t="s">
         <v>1675</v>
@@ -30980,7 +36192,7 @@
       </c>
       <c r="G303" s="6"/>
       <c r="H303" s="6">
-        <v>62000</v>
+        <v>138000</v>
       </c>
       <c r="I303" s="6" t="s">
         <v>1688</v>
@@ -31016,7 +36228,7 @@
       </c>
       <c r="G304" s="6"/>
       <c r="H304" s="6">
-        <v>50000</v>
+        <v>65000</v>
       </c>
       <c r="I304" s="6" t="s">
         <v>1676</v>
@@ -31029,6 +36241,2385 @@
       </c>
       <c r="M304" s="3" t="s">
         <v>1682</v>
+      </c>
+    </row>
+    <row r="305" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A305">
+        <v>304</v>
+      </c>
+      <c r="B305" s="6">
+        <v>544</v>
+      </c>
+      <c r="C305" s="2">
+        <v>46146</v>
+      </c>
+      <c r="D305" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E305" s="6" t="s">
+        <v>1698</v>
+      </c>
+      <c r="F305" s="6" t="s">
+        <v>1697</v>
+      </c>
+      <c r="G305" s="6"/>
+      <c r="H305" s="6">
+        <v>274000</v>
+      </c>
+      <c r="I305" s="6" t="s">
+        <v>1693</v>
+      </c>
+      <c r="K305" s="3" t="s">
+        <v>1694</v>
+      </c>
+      <c r="L305" s="3" t="s">
+        <v>1695</v>
+      </c>
+      <c r="M305" s="3" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="306" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A306">
+        <v>305</v>
+      </c>
+      <c r="B306" s="6">
+        <v>545</v>
+      </c>
+      <c r="C306" s="2">
+        <v>46146</v>
+      </c>
+      <c r="D306" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F306" s="6" t="s">
+        <v>1700</v>
+      </c>
+      <c r="G306" s="6"/>
+      <c r="H306" s="6">
+        <v>169000</v>
+      </c>
+      <c r="I306" s="6" t="s">
+        <v>1699</v>
+      </c>
+      <c r="K306" s="3" t="s">
+        <v>1701</v>
+      </c>
+      <c r="L306" s="3" t="s">
+        <v>1702</v>
+      </c>
+      <c r="M306" s="3" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="307" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B307" s="6">
+        <v>546</v>
+      </c>
+      <c r="C307" s="2">
+        <v>46146</v>
+      </c>
+      <c r="D307" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F307" s="6" t="s">
+        <v>1705</v>
+      </c>
+      <c r="G307" s="6"/>
+      <c r="H307" s="6">
+        <v>57000</v>
+      </c>
+      <c r="I307" s="6" t="s">
+        <v>1704</v>
+      </c>
+      <c r="K307" s="3" t="s">
+        <v>1706</v>
+      </c>
+      <c r="L307" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M307" s="3" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="308" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B308" s="6">
+        <v>547</v>
+      </c>
+      <c r="C308" s="2">
+        <v>46147</v>
+      </c>
+      <c r="D308" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F308" s="6" t="s">
+        <v>1718</v>
+      </c>
+      <c r="G308" s="6"/>
+      <c r="H308" s="6">
+        <v>76000</v>
+      </c>
+      <c r="I308" s="6" t="s">
+        <v>1714</v>
+      </c>
+      <c r="K308" s="3" t="s">
+        <v>1715</v>
+      </c>
+      <c r="L308" s="3" t="s">
+        <v>1716</v>
+      </c>
+      <c r="M308" s="3" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="309" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B309" s="6">
+        <v>548</v>
+      </c>
+      <c r="C309" s="2">
+        <v>46147</v>
+      </c>
+      <c r="D309" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F309" s="6" t="s">
+        <v>1710</v>
+      </c>
+      <c r="G309" s="6"/>
+      <c r="H309" s="6">
+        <v>252000</v>
+      </c>
+      <c r="I309" s="6" t="s">
+        <v>1709</v>
+      </c>
+      <c r="K309" s="3" t="s">
+        <v>1711</v>
+      </c>
+      <c r="L309" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="M309" s="3" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="310" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B310" s="6">
+        <v>549</v>
+      </c>
+      <c r="C310" s="2">
+        <v>46147</v>
+      </c>
+      <c r="D310" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F310" s="6" t="s">
+        <v>1724</v>
+      </c>
+      <c r="G310" s="6"/>
+      <c r="H310" s="6">
+        <v>189000</v>
+      </c>
+      <c r="I310" s="6" t="s">
+        <v>1719</v>
+      </c>
+      <c r="K310" s="3" t="s">
+        <v>1720</v>
+      </c>
+      <c r="L310" s="3" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M310" s="3" t="s">
+        <v>1722</v>
+      </c>
+      <c r="N310" s="3" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="311" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B311" s="6">
+        <v>550</v>
+      </c>
+      <c r="C311" s="2">
+        <v>46147</v>
+      </c>
+      <c r="D311" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F311" s="6" t="s">
+        <v>1729</v>
+      </c>
+      <c r="G311" s="6"/>
+      <c r="H311" s="6">
+        <v>599000</v>
+      </c>
+      <c r="I311" s="6" t="s">
+        <v>1725</v>
+      </c>
+      <c r="K311" s="3" t="s">
+        <v>1726</v>
+      </c>
+      <c r="L311" s="3" t="s">
+        <v>1727</v>
+      </c>
+      <c r="M311" s="3" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="312" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B312" s="6">
+        <v>551</v>
+      </c>
+      <c r="C312" s="2">
+        <v>46147</v>
+      </c>
+      <c r="D312" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F312" s="6" t="s">
+        <v>1734</v>
+      </c>
+      <c r="G312" s="6"/>
+      <c r="H312" s="6">
+        <v>362000</v>
+      </c>
+      <c r="I312" s="6" t="s">
+        <v>1730</v>
+      </c>
+      <c r="K312" s="3" t="s">
+        <v>1731</v>
+      </c>
+      <c r="L312" s="3" t="s">
+        <v>1732</v>
+      </c>
+      <c r="M312" s="3" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="313" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B313" s="6">
+        <v>552</v>
+      </c>
+      <c r="C313" s="2">
+        <v>46147</v>
+      </c>
+      <c r="D313" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F313" s="6" t="s">
+        <v>1739</v>
+      </c>
+      <c r="G313" s="6"/>
+      <c r="H313" s="6">
+        <v>457000</v>
+      </c>
+      <c r="I313" s="6" t="s">
+        <v>1735</v>
+      </c>
+      <c r="K313" s="3" t="s">
+        <v>1736</v>
+      </c>
+      <c r="L313" s="3" t="s">
+        <v>1737</v>
+      </c>
+      <c r="M313" s="3" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="314" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B314" s="6">
+        <v>554</v>
+      </c>
+      <c r="C314" s="2">
+        <v>46148</v>
+      </c>
+      <c r="D314" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F314" s="6" t="s">
+        <v>1744</v>
+      </c>
+      <c r="G314" s="6"/>
+      <c r="H314" s="6">
+        <v>538000</v>
+      </c>
+      <c r="I314" s="6" t="s">
+        <v>1740</v>
+      </c>
+      <c r="K314" s="3" t="s">
+        <v>1741</v>
+      </c>
+      <c r="L314" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="M314" s="3" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="315" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B315" s="6">
+        <v>557</v>
+      </c>
+      <c r="C315" s="2">
+        <v>46148</v>
+      </c>
+      <c r="D315" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F315" s="6" t="s">
+        <v>1749</v>
+      </c>
+      <c r="G315" s="6"/>
+      <c r="H315" s="6">
+        <v>2200000</v>
+      </c>
+      <c r="I315" s="6" t="s">
+        <v>1745</v>
+      </c>
+      <c r="K315" s="3" t="s">
+        <v>1746</v>
+      </c>
+      <c r="L315" s="3" t="s">
+        <v>1747</v>
+      </c>
+      <c r="M315" s="3" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="316" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B316" s="6">
+        <v>561</v>
+      </c>
+      <c r="C316" s="2">
+        <v>46149</v>
+      </c>
+      <c r="D316" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F316" s="6" t="s">
+        <v>1754</v>
+      </c>
+      <c r="G316" s="6"/>
+      <c r="H316" s="6">
+        <v>1700000</v>
+      </c>
+      <c r="I316" s="6" t="s">
+        <v>1750</v>
+      </c>
+      <c r="K316" s="3" t="s">
+        <v>1751</v>
+      </c>
+      <c r="L316" s="3" t="s">
+        <v>1752</v>
+      </c>
+      <c r="M316" s="3" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="317" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B317" s="6">
+        <v>564</v>
+      </c>
+      <c r="C317" s="2">
+        <v>46149</v>
+      </c>
+      <c r="D317" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F317" s="5" t="s">
+        <v>1759</v>
+      </c>
+      <c r="G317" s="6"/>
+      <c r="H317" s="6">
+        <v>110000</v>
+      </c>
+      <c r="I317" s="6" t="s">
+        <v>1755</v>
+      </c>
+      <c r="K317" s="3" t="s">
+        <v>1756</v>
+      </c>
+      <c r="L317" s="3" t="s">
+        <v>1757</v>
+      </c>
+      <c r="M317" s="3" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="318" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B318" s="6">
+        <v>565</v>
+      </c>
+      <c r="C318" s="2">
+        <v>46149</v>
+      </c>
+      <c r="D318" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F318" s="6" t="s">
+        <v>1764</v>
+      </c>
+      <c r="G318" s="6"/>
+      <c r="H318" s="6">
+        <v>96000</v>
+      </c>
+      <c r="I318" s="6" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K318" s="3" t="s">
+        <v>1761</v>
+      </c>
+      <c r="L318" s="3" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M318" s="3" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="319" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B319" s="6">
+        <v>574</v>
+      </c>
+      <c r="C319" s="2">
+        <v>46152</v>
+      </c>
+      <c r="D319" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F319" s="6" t="s">
+        <v>1771</v>
+      </c>
+      <c r="G319" s="6"/>
+      <c r="H319" s="6">
+        <v>2200000</v>
+      </c>
+      <c r="I319" s="6" t="s">
+        <v>1765</v>
+      </c>
+      <c r="K319" s="3" t="s">
+        <v>1766</v>
+      </c>
+      <c r="L319" s="3" t="s">
+        <v>1767</v>
+      </c>
+      <c r="M319" s="3" t="s">
+        <v>1768</v>
+      </c>
+      <c r="N319" s="3" t="s">
+        <v>1769</v>
+      </c>
+      <c r="O319" s="3" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="320" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B320" s="6">
+        <v>579</v>
+      </c>
+      <c r="C320" s="2">
+        <v>46153</v>
+      </c>
+      <c r="D320" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F320" s="6" t="s">
+        <v>1777</v>
+      </c>
+      <c r="G320" s="6"/>
+      <c r="H320" s="6">
+        <v>1600000</v>
+      </c>
+      <c r="I320" s="6" t="s">
+        <v>1772</v>
+      </c>
+      <c r="K320" s="3" t="s">
+        <v>1773</v>
+      </c>
+      <c r="L320" s="3" t="s">
+        <v>1774</v>
+      </c>
+      <c r="M320" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="N320" s="3" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="321" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B321" s="6">
+        <v>583</v>
+      </c>
+      <c r="C321" s="2">
+        <v>46154</v>
+      </c>
+      <c r="D321" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F321" s="6" t="s">
+        <v>1783</v>
+      </c>
+      <c r="G321" s="6"/>
+      <c r="H321" s="6">
+        <v>94000</v>
+      </c>
+      <c r="I321" s="6" t="s">
+        <v>1784</v>
+      </c>
+      <c r="K321" s="3" t="s">
+        <v>1785</v>
+      </c>
+      <c r="L321" s="3" t="s">
+        <v>1786</v>
+      </c>
+      <c r="M321" s="3" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="322" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B322" s="6">
+        <v>586</v>
+      </c>
+      <c r="C322" s="2">
+        <v>46154</v>
+      </c>
+      <c r="D322" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F322" s="6" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G322" s="6"/>
+      <c r="H322" s="6">
+        <v>1600000</v>
+      </c>
+      <c r="I322" s="6" t="s">
+        <v>1788</v>
+      </c>
+      <c r="K322" s="3" t="s">
+        <v>1790</v>
+      </c>
+      <c r="L322" s="3" t="s">
+        <v>1791</v>
+      </c>
+      <c r="M322" s="3" t="s">
+        <v>1792</v>
+      </c>
+      <c r="N322" s="3" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="323" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B323" s="6">
+        <v>589</v>
+      </c>
+      <c r="C323" s="2">
+        <v>46155</v>
+      </c>
+      <c r="D323" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F323" s="6" t="s">
+        <v>1782</v>
+      </c>
+      <c r="G323" s="6"/>
+      <c r="H323" s="6">
+        <v>427000</v>
+      </c>
+      <c r="I323" s="6" t="s">
+        <v>1778</v>
+      </c>
+      <c r="K323" s="3" t="s">
+        <v>1779</v>
+      </c>
+      <c r="L323" s="3" t="s">
+        <v>1780</v>
+      </c>
+      <c r="M323" s="3" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="324" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B324" s="6">
+        <v>593</v>
+      </c>
+      <c r="C324" s="2">
+        <v>46157</v>
+      </c>
+      <c r="D324" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F324" s="6" t="s">
+        <v>1798</v>
+      </c>
+      <c r="G324" s="6"/>
+      <c r="H324" s="6">
+        <v>2100000</v>
+      </c>
+      <c r="I324" s="6" t="s">
+        <v>1794</v>
+      </c>
+      <c r="K324" s="3" t="s">
+        <v>1795</v>
+      </c>
+      <c r="L324" s="3" t="s">
+        <v>1796</v>
+      </c>
+      <c r="M324" s="3" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="325" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B325" s="6">
+        <v>594</v>
+      </c>
+      <c r="C325" s="2">
+        <v>46157</v>
+      </c>
+      <c r="D325" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F325" s="6" t="s">
+        <v>1803</v>
+      </c>
+      <c r="G325" s="6"/>
+      <c r="H325" s="6">
+        <v>3000000</v>
+      </c>
+      <c r="I325" s="6" t="s">
+        <v>1799</v>
+      </c>
+      <c r="K325" s="3" t="s">
+        <v>1800</v>
+      </c>
+      <c r="L325" s="3" t="s">
+        <v>1801</v>
+      </c>
+      <c r="M325" s="3" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="326" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B326" s="6">
+        <v>596</v>
+      </c>
+      <c r="C326" s="2">
+        <v>46158</v>
+      </c>
+      <c r="D326" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F326" s="6" t="s">
+        <v>1808</v>
+      </c>
+      <c r="G326" s="6"/>
+      <c r="H326" s="6">
+        <v>626000</v>
+      </c>
+      <c r="I326" s="6" t="s">
+        <v>1804</v>
+      </c>
+      <c r="K326" s="3" t="s">
+        <v>1805</v>
+      </c>
+      <c r="L326" s="3" t="s">
+        <v>1806</v>
+      </c>
+      <c r="M326" s="3" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="327" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B327" s="6">
+        <v>598</v>
+      </c>
+      <c r="C327" s="2">
+        <v>46158</v>
+      </c>
+      <c r="D327" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F327" s="6" t="s">
+        <v>1814</v>
+      </c>
+      <c r="G327" s="6"/>
+      <c r="H327" s="6">
+        <v>572000</v>
+      </c>
+      <c r="I327" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="K327" s="3" t="s">
+        <v>1810</v>
+      </c>
+      <c r="L327" s="3" t="s">
+        <v>1811</v>
+      </c>
+      <c r="M327" s="3" t="s">
+        <v>1812</v>
+      </c>
+      <c r="N327" s="3" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="328" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B328" s="6">
+        <v>601</v>
+      </c>
+      <c r="C328" s="2">
+        <v>46158</v>
+      </c>
+      <c r="D328" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F328" s="6" t="s">
+        <v>1819</v>
+      </c>
+      <c r="G328" s="6"/>
+      <c r="H328" s="6">
+        <v>303000</v>
+      </c>
+      <c r="I328" s="6" t="s">
+        <v>1815</v>
+      </c>
+      <c r="K328" s="3" t="s">
+        <v>1816</v>
+      </c>
+      <c r="L328" s="3" t="s">
+        <v>1817</v>
+      </c>
+      <c r="M328" s="3" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="329" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B329" s="6">
+        <v>602</v>
+      </c>
+      <c r="C329" s="2">
+        <v>46159</v>
+      </c>
+      <c r="D329" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F329" s="6" t="s">
+        <v>1824</v>
+      </c>
+      <c r="G329" s="6"/>
+      <c r="H329" s="6">
+        <v>558000</v>
+      </c>
+      <c r="I329" s="6" t="s">
+        <v>1823</v>
+      </c>
+      <c r="K329" s="3" t="s">
+        <v>1820</v>
+      </c>
+      <c r="L329" s="3" t="s">
+        <v>1821</v>
+      </c>
+      <c r="M329" s="3" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="330" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B330" s="6">
+        <v>604</v>
+      </c>
+      <c r="C330" s="2">
+        <v>46159</v>
+      </c>
+      <c r="D330" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F330" s="6" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G330" s="6"/>
+      <c r="H330" s="6">
+        <v>2000000</v>
+      </c>
+      <c r="I330" s="6" t="s">
+        <v>1825</v>
+      </c>
+      <c r="K330" s="3" t="s">
+        <v>1827</v>
+      </c>
+      <c r="L330" s="3" t="s">
+        <v>1828</v>
+      </c>
+      <c r="M330" s="3" t="s">
+        <v>1829</v>
+      </c>
+      <c r="N330" s="3" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="331" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B331" s="6">
+        <v>606</v>
+      </c>
+      <c r="C331" s="2">
+        <v>46159</v>
+      </c>
+      <c r="D331" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F331" s="6" t="s">
+        <v>1835</v>
+      </c>
+      <c r="G331" s="6"/>
+      <c r="H331" s="6">
+        <v>533000</v>
+      </c>
+      <c r="I331" s="6" t="s">
+        <v>1831</v>
+      </c>
+      <c r="K331" s="3" t="s">
+        <v>1832</v>
+      </c>
+      <c r="L331" s="3" t="s">
+        <v>1833</v>
+      </c>
+      <c r="M331" s="3" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="332" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B332" s="6">
+        <v>609</v>
+      </c>
+      <c r="C332" s="2">
+        <v>46159</v>
+      </c>
+      <c r="D332" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F332" s="6" t="s">
+        <v>1840</v>
+      </c>
+      <c r="H332" s="6">
+        <v>148000</v>
+      </c>
+      <c r="I332" s="6" t="s">
+        <v>1836</v>
+      </c>
+      <c r="K332" s="3" t="s">
+        <v>1837</v>
+      </c>
+      <c r="L332" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="M332" s="3" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="333" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B333" s="6">
+        <v>614</v>
+      </c>
+      <c r="C333" s="2">
+        <v>46160</v>
+      </c>
+      <c r="D333" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F333" s="6" t="s">
+        <v>1845</v>
+      </c>
+      <c r="H333" s="6">
+        <v>798000</v>
+      </c>
+      <c r="I333" s="6" t="s">
+        <v>1841</v>
+      </c>
+      <c r="K333" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="L333" s="3" t="s">
+        <v>1843</v>
+      </c>
+      <c r="M333" s="3" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="334" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B334" s="6">
+        <v>615</v>
+      </c>
+      <c r="C334" s="2">
+        <v>46160</v>
+      </c>
+      <c r="D334" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F334" s="6" t="s">
+        <v>1850</v>
+      </c>
+      <c r="H334" s="6">
+        <v>430000</v>
+      </c>
+      <c r="I334" s="6" t="s">
+        <v>1846</v>
+      </c>
+      <c r="K334" s="3" t="s">
+        <v>1847</v>
+      </c>
+      <c r="L334" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="M334" s="3" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="335" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B335" s="6">
+        <v>617</v>
+      </c>
+      <c r="C335" s="2">
+        <v>46160</v>
+      </c>
+      <c r="D335" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F335" s="6" t="s">
+        <v>1851</v>
+      </c>
+      <c r="H335" s="6">
+        <v>66000</v>
+      </c>
+      <c r="I335" s="6" t="s">
+        <v>1852</v>
+      </c>
+      <c r="K335" s="3" t="s">
+        <v>1853</v>
+      </c>
+      <c r="L335" s="3" t="s">
+        <v>1854</v>
+      </c>
+      <c r="M335" s="3" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="336" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B336" s="6">
+        <v>618</v>
+      </c>
+      <c r="C336" s="2">
+        <v>46160</v>
+      </c>
+      <c r="D336" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F336" s="5" t="s">
+        <v>1860</v>
+      </c>
+      <c r="H336" s="6">
+        <v>2900000</v>
+      </c>
+      <c r="I336" s="6" t="s">
+        <v>1856</v>
+      </c>
+      <c r="K336" s="3" t="s">
+        <v>1857</v>
+      </c>
+      <c r="L336" s="3" t="s">
+        <v>1858</v>
+      </c>
+      <c r="M336" s="3" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="337" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B337" s="6">
+        <v>621</v>
+      </c>
+      <c r="C337" s="2">
+        <v>46160</v>
+      </c>
+      <c r="D337" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F337" s="6" t="s">
+        <v>1865</v>
+      </c>
+      <c r="H337" s="6">
+        <v>134000</v>
+      </c>
+      <c r="I337" s="6" t="s">
+        <v>1861</v>
+      </c>
+      <c r="K337" s="3" t="s">
+        <v>1862</v>
+      </c>
+      <c r="L337" s="3" t="s">
+        <v>1863</v>
+      </c>
+      <c r="M337" s="3" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="338" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B338" s="6">
+        <v>622</v>
+      </c>
+      <c r="C338" s="2">
+        <v>46160</v>
+      </c>
+      <c r="D338" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F338" s="6" t="s">
+        <v>1870</v>
+      </c>
+      <c r="H338" s="6">
+        <v>83000</v>
+      </c>
+      <c r="I338" s="6" t="s">
+        <v>1866</v>
+      </c>
+      <c r="K338" s="3" t="s">
+        <v>1867</v>
+      </c>
+      <c r="L338" s="3" t="s">
+        <v>1868</v>
+      </c>
+      <c r="M338" s="3" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="339" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B339" s="6">
+        <v>623</v>
+      </c>
+      <c r="C339" s="2">
+        <v>46161</v>
+      </c>
+      <c r="D339" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F339" s="6" t="s">
+        <v>1875</v>
+      </c>
+      <c r="H339" s="6">
+        <v>5200000</v>
+      </c>
+      <c r="I339" s="6" t="s">
+        <v>1871</v>
+      </c>
+      <c r="K339" s="3" t="s">
+        <v>1872</v>
+      </c>
+      <c r="L339" s="3" t="s">
+        <v>1873</v>
+      </c>
+      <c r="M339" s="3" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="340" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B340" s="6">
+        <v>629</v>
+      </c>
+      <c r="C340" s="2">
+        <v>46162</v>
+      </c>
+      <c r="D340" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F340" s="6" t="s">
+        <v>1880</v>
+      </c>
+      <c r="H340" s="6">
+        <v>34900000</v>
+      </c>
+      <c r="I340" s="6" t="s">
+        <v>1876</v>
+      </c>
+      <c r="K340" s="3" t="s">
+        <v>1877</v>
+      </c>
+      <c r="L340" s="3" t="s">
+        <v>1878</v>
+      </c>
+      <c r="M340" s="3" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="341" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B341" s="6">
+        <v>634</v>
+      </c>
+      <c r="C341" s="2">
+        <v>46163</v>
+      </c>
+      <c r="D341" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F341" s="6" t="s">
+        <v>1885</v>
+      </c>
+      <c r="H341" s="6">
+        <v>27000</v>
+      </c>
+      <c r="I341" s="6" t="s">
+        <v>1881</v>
+      </c>
+      <c r="K341" s="3" t="s">
+        <v>1882</v>
+      </c>
+      <c r="L341" s="3" t="s">
+        <v>1883</v>
+      </c>
+      <c r="M341" s="3" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="342" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B342" s="6">
+        <v>635</v>
+      </c>
+      <c r="C342" s="2">
+        <v>46163</v>
+      </c>
+      <c r="D342" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F342" s="6" t="s">
+        <v>1890</v>
+      </c>
+      <c r="H342" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="I342" s="6" t="s">
+        <v>1886</v>
+      </c>
+      <c r="K342" s="3" t="s">
+        <v>1887</v>
+      </c>
+      <c r="L342" s="3" t="s">
+        <v>1888</v>
+      </c>
+      <c r="M342" s="3" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="343" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B343" s="6">
+        <v>637</v>
+      </c>
+      <c r="C343" s="2">
+        <v>46163</v>
+      </c>
+      <c r="D343" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F343" s="5" t="s">
+        <v>1895</v>
+      </c>
+      <c r="H343" s="6">
+        <v>40000</v>
+      </c>
+      <c r="I343" s="6" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K343" s="3" t="s">
+        <v>1892</v>
+      </c>
+      <c r="L343" s="3" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M343" s="3" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="344" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B344" s="6">
+        <v>638</v>
+      </c>
+      <c r="C344" s="2">
+        <v>46164</v>
+      </c>
+      <c r="D344" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F344" s="6" t="s">
+        <v>1900</v>
+      </c>
+      <c r="H344" s="6">
+        <v>299000</v>
+      </c>
+      <c r="I344" s="6" t="s">
+        <v>1896</v>
+      </c>
+      <c r="K344" s="3" t="s">
+        <v>1897</v>
+      </c>
+      <c r="L344" s="3" t="s">
+        <v>1898</v>
+      </c>
+      <c r="M344" s="3" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="345" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B345" s="6">
+        <v>639</v>
+      </c>
+      <c r="C345" s="2">
+        <v>46164</v>
+      </c>
+      <c r="D345" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F345" s="6" t="s">
+        <v>1906</v>
+      </c>
+      <c r="H345" s="6">
+        <v>4200000</v>
+      </c>
+      <c r="I345" s="6" t="s">
+        <v>1901</v>
+      </c>
+      <c r="K345" s="3" t="s">
+        <v>1902</v>
+      </c>
+      <c r="L345" s="3" t="s">
+        <v>1903</v>
+      </c>
+      <c r="M345" s="3" t="s">
+        <v>1904</v>
+      </c>
+      <c r="N345" s="3" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="346" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B346" s="6">
+        <v>642</v>
+      </c>
+      <c r="C346" s="2">
+        <v>46165</v>
+      </c>
+      <c r="D346" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F346" s="6" t="s">
+        <v>1911</v>
+      </c>
+      <c r="H346" s="6">
+        <v>574000</v>
+      </c>
+      <c r="I346" s="6" t="s">
+        <v>1907</v>
+      </c>
+      <c r="K346" s="3" t="s">
+        <v>1908</v>
+      </c>
+      <c r="L346" s="3" t="s">
+        <v>1909</v>
+      </c>
+      <c r="M346" s="3" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="347" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B347" s="6">
+        <v>643</v>
+      </c>
+      <c r="C347" s="2">
+        <v>46165</v>
+      </c>
+      <c r="D347" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F347" s="6" t="s">
+        <v>1916</v>
+      </c>
+      <c r="H347" s="6">
+        <v>274000</v>
+      </c>
+      <c r="I347" s="6" t="s">
+        <v>1912</v>
+      </c>
+      <c r="K347" s="3" t="s">
+        <v>1913</v>
+      </c>
+      <c r="L347" s="3" t="s">
+        <v>1914</v>
+      </c>
+      <c r="M347" s="3" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="348" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B348" s="6">
+        <v>644</v>
+      </c>
+      <c r="C348" s="2">
+        <v>46166</v>
+      </c>
+      <c r="D348" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F348" s="6" t="s">
+        <v>1921</v>
+      </c>
+      <c r="H348" s="6">
+        <v>2900000</v>
+      </c>
+      <c r="I348" s="6" t="s">
+        <v>1917</v>
+      </c>
+      <c r="K348" s="3" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L348" s="3" t="s">
+        <v>1919</v>
+      </c>
+      <c r="M348" s="3" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="349" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B349" s="6">
+        <v>645</v>
+      </c>
+      <c r="C349" s="2">
+        <v>46166</v>
+      </c>
+      <c r="F349" s="6" t="s">
+        <v>1927</v>
+      </c>
+      <c r="H349" s="6">
+        <v>289000</v>
+      </c>
+      <c r="I349" s="6" t="s">
+        <v>1922</v>
+      </c>
+      <c r="K349" s="3" t="s">
+        <v>1923</v>
+      </c>
+      <c r="L349" s="3" t="s">
+        <v>1924</v>
+      </c>
+      <c r="M349" s="3" t="s">
+        <v>1925</v>
+      </c>
+      <c r="N349" s="3" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="350" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B350" s="6">
+        <v>646</v>
+      </c>
+      <c r="C350" s="2">
+        <v>46166</v>
+      </c>
+      <c r="F350" s="6" t="s">
+        <v>1932</v>
+      </c>
+      <c r="H350" s="6">
+        <v>3200000</v>
+      </c>
+      <c r="I350" s="6" t="s">
+        <v>1928</v>
+      </c>
+      <c r="K350" s="3" t="s">
+        <v>1929</v>
+      </c>
+      <c r="L350" s="3" t="s">
+        <v>1930</v>
+      </c>
+      <c r="M350" s="3" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="351" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B351" s="6">
+        <v>648</v>
+      </c>
+      <c r="C351" s="2">
+        <v>46166</v>
+      </c>
+      <c r="D351" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F351" s="6" t="s">
+        <v>1937</v>
+      </c>
+      <c r="H351" s="6">
+        <v>444000</v>
+      </c>
+      <c r="I351" s="6" t="s">
+        <v>1933</v>
+      </c>
+      <c r="K351" s="3" t="s">
+        <v>1934</v>
+      </c>
+      <c r="L351" s="3" t="s">
+        <v>1935</v>
+      </c>
+      <c r="M351" s="3" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="352" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B352" s="6">
+        <v>651</v>
+      </c>
+      <c r="C352" s="2">
+        <v>46166</v>
+      </c>
+      <c r="D352" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F352" s="6" t="s">
+        <v>1943</v>
+      </c>
+      <c r="H352" s="6">
+        <v>2100000</v>
+      </c>
+      <c r="I352" s="6" t="s">
+        <v>1938</v>
+      </c>
+      <c r="K352" s="3" t="s">
+        <v>1939</v>
+      </c>
+      <c r="L352" s="3" t="s">
+        <v>1940</v>
+      </c>
+      <c r="M352" s="3" t="s">
+        <v>1941</v>
+      </c>
+      <c r="N352" s="3" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="353" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B353" s="6">
+        <v>654</v>
+      </c>
+      <c r="C353" s="2">
+        <v>46167</v>
+      </c>
+      <c r="F353" s="6" t="s">
+        <v>1948</v>
+      </c>
+      <c r="H353" s="6">
+        <v>152000</v>
+      </c>
+      <c r="I353" s="6" t="s">
+        <v>1944</v>
+      </c>
+      <c r="K353" s="3" t="s">
+        <v>1945</v>
+      </c>
+      <c r="L353" s="3" t="s">
+        <v>1946</v>
+      </c>
+      <c r="M353" s="3" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="354" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B354" s="6">
+        <v>655</v>
+      </c>
+      <c r="C354" s="2">
+        <v>46168</v>
+      </c>
+      <c r="F354" s="6" t="s">
+        <v>1953</v>
+      </c>
+      <c r="H354" s="6">
+        <v>58000</v>
+      </c>
+      <c r="I354" s="6" t="s">
+        <v>1949</v>
+      </c>
+      <c r="K354" s="3" t="s">
+        <v>1950</v>
+      </c>
+      <c r="L354" s="3" t="s">
+        <v>1951</v>
+      </c>
+      <c r="M354" s="3" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="355" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B355" s="6">
+        <v>657</v>
+      </c>
+      <c r="C355" s="2">
+        <v>46169</v>
+      </c>
+      <c r="F355" s="6" t="s">
+        <v>1958</v>
+      </c>
+      <c r="H355" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="I355" s="6" t="s">
+        <v>1954</v>
+      </c>
+      <c r="K355" s="3" t="s">
+        <v>1955</v>
+      </c>
+      <c r="L355" s="3" t="s">
+        <v>1956</v>
+      </c>
+      <c r="M355" s="3" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="356" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B356" s="6">
+        <v>658</v>
+      </c>
+      <c r="C356" s="2">
+        <v>46169</v>
+      </c>
+      <c r="F356" s="6" t="s">
+        <v>1963</v>
+      </c>
+      <c r="H356" s="6">
+        <v>215000</v>
+      </c>
+      <c r="I356" s="6" t="s">
+        <v>1959</v>
+      </c>
+      <c r="K356" s="3" t="s">
+        <v>1960</v>
+      </c>
+      <c r="L356" s="3" t="s">
+        <v>1961</v>
+      </c>
+      <c r="M356" s="3" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="357" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B357" s="6">
+        <v>659</v>
+      </c>
+      <c r="C357" s="2">
+        <v>46169</v>
+      </c>
+      <c r="F357" s="6" t="s">
+        <v>1968</v>
+      </c>
+      <c r="H357" s="6">
+        <v>510000</v>
+      </c>
+      <c r="I357" s="6" t="s">
+        <v>1964</v>
+      </c>
+      <c r="K357" s="3" t="s">
+        <v>1965</v>
+      </c>
+      <c r="L357" s="3" t="s">
+        <v>1966</v>
+      </c>
+      <c r="M357" s="3" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="358" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B358" s="6">
+        <v>661</v>
+      </c>
+      <c r="C358" s="2">
+        <v>46170</v>
+      </c>
+      <c r="F358" s="6" t="s">
+        <v>1973</v>
+      </c>
+      <c r="H358" s="6">
+        <v>781000</v>
+      </c>
+      <c r="I358" s="6" t="s">
+        <v>1969</v>
+      </c>
+      <c r="K358" s="3" t="s">
+        <v>1970</v>
+      </c>
+      <c r="L358" s="3" t="s">
+        <v>1971</v>
+      </c>
+      <c r="M358" s="3" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="359" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B359" s="6">
+        <v>663</v>
+      </c>
+      <c r="C359" s="2">
+        <v>46170</v>
+      </c>
+      <c r="D359" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F359" s="5" t="s">
+        <v>1978</v>
+      </c>
+      <c r="H359" s="6">
+        <v>545000</v>
+      </c>
+      <c r="I359" s="6" t="s">
+        <v>1974</v>
+      </c>
+      <c r="K359" s="3" t="s">
+        <v>1975</v>
+      </c>
+      <c r="L359" s="3" t="s">
+        <v>1976</v>
+      </c>
+      <c r="M359" s="3" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="360" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B360" s="6">
+        <v>664</v>
+      </c>
+      <c r="C360" s="2">
+        <v>46170</v>
+      </c>
+      <c r="F360" s="6" t="s">
+        <v>1983</v>
+      </c>
+      <c r="H360" s="6">
+        <v>1900000</v>
+      </c>
+      <c r="I360" s="6" t="s">
+        <v>1979</v>
+      </c>
+      <c r="K360" s="3" t="s">
+        <v>1980</v>
+      </c>
+      <c r="L360" s="3" t="s">
+        <v>1981</v>
+      </c>
+      <c r="M360" s="3" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="361" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B361" s="6">
+        <v>665</v>
+      </c>
+      <c r="C361" s="2">
+        <v>46170</v>
+      </c>
+      <c r="F361" s="6" t="s">
+        <v>1988</v>
+      </c>
+      <c r="H361" s="6">
+        <v>111000</v>
+      </c>
+      <c r="I361" s="6" t="s">
+        <v>1984</v>
+      </c>
+      <c r="K361" s="3" t="s">
+        <v>1985</v>
+      </c>
+      <c r="L361" s="3" t="s">
+        <v>1986</v>
+      </c>
+      <c r="M361" s="3" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="362" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B362" s="6">
+        <v>666</v>
+      </c>
+      <c r="C362" s="2">
+        <v>46171</v>
+      </c>
+      <c r="F362" s="8" t="s">
+        <v>1993</v>
+      </c>
+      <c r="H362" s="6">
+        <v>127000</v>
+      </c>
+      <c r="I362" s="6" t="s">
+        <v>1989</v>
+      </c>
+      <c r="K362" s="3" t="s">
+        <v>1990</v>
+      </c>
+      <c r="L362" s="3" t="s">
+        <v>1991</v>
+      </c>
+      <c r="M362" s="3" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="363" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B363" s="6">
+        <v>668</v>
+      </c>
+      <c r="C363" s="2">
+        <v>46172</v>
+      </c>
+      <c r="F363" s="6" t="s">
+        <v>1998</v>
+      </c>
+      <c r="H363" s="6">
+        <v>406000</v>
+      </c>
+      <c r="I363" s="6" t="s">
+        <v>1994</v>
+      </c>
+      <c r="K363" s="3" t="s">
+        <v>1995</v>
+      </c>
+      <c r="L363" s="3" t="s">
+        <v>1996</v>
+      </c>
+      <c r="M363" s="3" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="364" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B364" s="6">
+        <v>669</v>
+      </c>
+      <c r="C364" s="2">
+        <v>46172</v>
+      </c>
+      <c r="F364" s="5" t="s">
+        <v>2003</v>
+      </c>
+      <c r="H364" s="6">
+        <v>816000</v>
+      </c>
+      <c r="I364" s="6" t="s">
+        <v>1999</v>
+      </c>
+      <c r="K364" s="3" t="s">
+        <v>2000</v>
+      </c>
+      <c r="L364" s="3" t="s">
+        <v>2001</v>
+      </c>
+      <c r="M364" s="3" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="365" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B365" s="6">
+        <v>671</v>
+      </c>
+      <c r="C365" s="2">
+        <v>46172</v>
+      </c>
+      <c r="F365" s="5" t="s">
+        <v>2007</v>
+      </c>
+      <c r="H365" s="6">
+        <v>66000</v>
+      </c>
+      <c r="I365" s="6" t="s">
+        <v>2004</v>
+      </c>
+      <c r="K365" s="3" t="s">
+        <v>2005</v>
+      </c>
+      <c r="L365" s="3" t="s">
+        <v>2006</v>
+      </c>
+      <c r="M365" s="3" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="366" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B366" s="6">
+        <v>672</v>
+      </c>
+      <c r="C366" s="2">
+        <v>46172</v>
+      </c>
+      <c r="F366" s="6" t="s">
+        <v>2012</v>
+      </c>
+      <c r="H366" s="6">
+        <v>47000</v>
+      </c>
+      <c r="I366" s="6" t="s">
+        <v>2008</v>
+      </c>
+      <c r="K366" s="3" t="s">
+        <v>2009</v>
+      </c>
+      <c r="L366" s="3" t="s">
+        <v>2010</v>
+      </c>
+      <c r="M366" s="3" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="367" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B367" s="6">
+        <v>674</v>
+      </c>
+      <c r="C367" s="2">
+        <v>46173</v>
+      </c>
+      <c r="D367" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F367" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="H367" s="6">
+        <v>104000</v>
+      </c>
+      <c r="I367" s="6" t="s">
+        <v>2013</v>
+      </c>
+      <c r="K367" s="3" t="s">
+        <v>2014</v>
+      </c>
+      <c r="L367" s="3" t="s">
+        <v>2015</v>
+      </c>
+      <c r="M367" s="3" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="368" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B368" s="6">
+        <v>680</v>
+      </c>
+      <c r="C368" s="2">
+        <v>46173</v>
+      </c>
+      <c r="D368" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F368" s="9" t="s">
+        <v>2023</v>
+      </c>
+      <c r="H368" s="6">
+        <v>375000</v>
+      </c>
+      <c r="I368" s="6" t="s">
+        <v>2018</v>
+      </c>
+      <c r="K368" s="3" t="s">
+        <v>2019</v>
+      </c>
+      <c r="L368" s="3" t="s">
+        <v>2020</v>
+      </c>
+      <c r="M368" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="N368" s="3" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="369" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B369" s="6">
+        <v>681</v>
+      </c>
+      <c r="C369" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D369" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F369" s="9" t="s">
+        <v>2025</v>
+      </c>
+      <c r="H369" s="6">
+        <v>92000</v>
+      </c>
+      <c r="I369" s="6" t="s">
+        <v>2024</v>
+      </c>
+      <c r="K369" s="3" t="s">
+        <v>2026</v>
+      </c>
+      <c r="L369" s="3" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="370" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B370" s="6">
+        <v>683</v>
+      </c>
+      <c r="C370" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F370" s="9" t="s">
+        <v>2031</v>
+      </c>
+      <c r="H370" s="6">
+        <v>65000</v>
+      </c>
+      <c r="I370" s="6" t="s">
+        <v>2028</v>
+      </c>
+      <c r="K370" s="3" t="s">
+        <v>2029</v>
+      </c>
+      <c r="L370" s="3" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="371" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B371" s="6">
+        <v>684</v>
+      </c>
+      <c r="C371" s="2">
+        <v>46144</v>
+      </c>
+      <c r="D371" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F371" s="9" t="s">
+        <v>2035</v>
+      </c>
+      <c r="H371" s="6">
+        <v>3000000</v>
+      </c>
+      <c r="I371" s="6" t="s">
+        <v>2032</v>
+      </c>
+      <c r="K371" s="3" t="s">
+        <v>2033</v>
+      </c>
+      <c r="L371" s="3" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="372" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B372" s="6">
+        <v>685</v>
+      </c>
+      <c r="C372" s="2">
+        <v>46144</v>
+      </c>
+      <c r="D372" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F372" s="5" t="s">
+        <v>2040</v>
+      </c>
+      <c r="H372" s="6">
+        <v>265000</v>
+      </c>
+      <c r="I372" s="6" t="s">
+        <v>2036</v>
+      </c>
+      <c r="K372" s="3" t="s">
+        <v>2037</v>
+      </c>
+      <c r="L372" s="3" t="s">
+        <v>2038</v>
+      </c>
+      <c r="M372" s="3" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="373" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B373" s="6">
+        <v>686</v>
+      </c>
+      <c r="C373" s="2">
+        <v>46144</v>
+      </c>
+      <c r="D373" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F373" s="9" t="s">
+        <v>2045</v>
+      </c>
+      <c r="H373" s="6">
+        <v>3100000</v>
+      </c>
+      <c r="I373" s="6" t="s">
+        <v>2041</v>
+      </c>
+      <c r="K373" s="3" t="s">
+        <v>2042</v>
+      </c>
+      <c r="L373" s="3" t="s">
+        <v>2043</v>
+      </c>
+      <c r="M373" s="3" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="374" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B374" s="6">
+        <v>687</v>
+      </c>
+      <c r="C374" s="2">
+        <v>46144</v>
+      </c>
+      <c r="D374" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F374" s="9" t="s">
+        <v>2050</v>
+      </c>
+      <c r="H374" s="6">
+        <v>378000</v>
+      </c>
+      <c r="I374" s="6" t="s">
+        <v>2046</v>
+      </c>
+      <c r="K374" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="L374" s="3" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M374" s="3" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="375" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B375" s="6">
+        <v>692</v>
+      </c>
+      <c r="D375" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F375" s="9" t="s">
+        <v>2052</v>
+      </c>
+      <c r="H375" s="6">
+        <v>129000</v>
+      </c>
+      <c r="I375" s="6" t="s">
+        <v>2051</v>
+      </c>
+      <c r="K375" s="3" t="s">
+        <v>2053</v>
+      </c>
+      <c r="L375" s="3" t="s">
+        <v>2054</v>
+      </c>
+      <c r="M375" s="3" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="376" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B376" s="6">
+        <v>693</v>
+      </c>
+      <c r="C376" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F376" s="9" t="s">
+        <v>2060</v>
+      </c>
+      <c r="H376" s="6">
+        <v>117000</v>
+      </c>
+      <c r="I376" s="6" t="s">
+        <v>2056</v>
+      </c>
+      <c r="K376" s="3" t="s">
+        <v>2057</v>
+      </c>
+      <c r="L376" s="3" t="s">
+        <v>2058</v>
+      </c>
+      <c r="M376" s="3" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="377" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B377" s="6">
+        <v>694</v>
+      </c>
+      <c r="C377" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F377" s="9" t="s">
+        <v>2065</v>
+      </c>
+      <c r="H377" s="6">
+        <v>259000</v>
+      </c>
+      <c r="I377" s="6" t="s">
+        <v>2061</v>
+      </c>
+      <c r="K377" s="3" t="s">
+        <v>2062</v>
+      </c>
+      <c r="L377" s="3" t="s">
+        <v>2063</v>
+      </c>
+      <c r="M377" s="3" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="378" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B378" s="6">
+        <v>695</v>
+      </c>
+      <c r="C378" s="2">
+        <v>46145</v>
+      </c>
+      <c r="D378" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F378" s="5" t="s">
+        <v>2070</v>
+      </c>
+      <c r="H378" s="6">
+        <v>213000</v>
+      </c>
+      <c r="I378" s="6" t="s">
+        <v>2066</v>
+      </c>
+      <c r="K378" s="3" t="s">
+        <v>2067</v>
+      </c>
+      <c r="L378" s="3" t="s">
+        <v>2068</v>
+      </c>
+      <c r="M378" s="3" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="379" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B379" s="6">
+        <v>698</v>
+      </c>
+      <c r="C379" s="7">
+        <v>46146</v>
+      </c>
+      <c r="F379" s="9" t="s">
+        <v>2075</v>
+      </c>
+      <c r="H379" s="6">
+        <v>417000</v>
+      </c>
+      <c r="I379" s="6" t="s">
+        <v>2071</v>
+      </c>
+      <c r="K379" s="3" t="s">
+        <v>2072</v>
+      </c>
+      <c r="L379" s="3" t="s">
+        <v>2073</v>
+      </c>
+      <c r="M379" s="3" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="380" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B380" s="6">
+        <v>700</v>
+      </c>
+      <c r="C380" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D380" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F380" s="9" t="s">
+        <v>2080</v>
+      </c>
+      <c r="H380" s="6">
+        <v>37000</v>
+      </c>
+      <c r="I380" s="6" t="s">
+        <v>2076</v>
+      </c>
+      <c r="K380" s="3" t="s">
+        <v>2077</v>
+      </c>
+      <c r="L380" s="3" t="s">
+        <v>2078</v>
+      </c>
+      <c r="M380" s="3" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="381" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B381" s="6">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="382" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B382" s="6">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="383" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B383" s="6">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="384" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B384" s="6">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="385" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B385" s="6">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="386" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B386" s="6">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="387" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B387" s="6">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="388" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B388" s="6">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="389" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B389" s="6">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="390" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B390" s="6">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="391" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B391" s="6">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="392" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B392" s="6">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="393" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B393" s="6">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="394" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B394" s="6">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="395" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B395" s="6">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="396" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B396" s="6">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="397" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B397" s="6">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="398" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B398" s="6">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="399" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B399" s="6">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="400" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B400" s="6">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="401" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B401" s="6">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="402" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B402" s="6">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="403" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B403" s="6">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="404" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B404" s="6">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="405" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B405" s="6">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="406" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B406" s="6">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="407" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B407" s="6">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="408" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B408" s="6">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="409" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B409" s="6">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="410" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B410" s="6">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="411" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B411" s="6">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="412" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B412" s="6">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="413" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B413" s="6">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="414" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B414" s="6">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="415" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B415" s="6">
+        <v>784</v>
       </c>
     </row>
   </sheetData>

--- a/BBDD NEWS.xlsx
+++ b/BBDD NEWS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EBD61C-B437-4153-A5D0-91E35C486DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E0DC8D-5B17-4533-842F-41D16D19BAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2399" uniqueCount="2081">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2567" uniqueCount="2247">
   <si>
     <t>id</t>
   </si>
@@ -25516,6 +25516,1320 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> es básicamente esto</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZSg7hHFWB-/</t>
+  </si>
+  <si>
+    <t>El rapero estadounidense Blueface soltó un comentario que generó un incómodo silencio de forma inmediata.</t>
+  </si>
+  <si>
+    <t>Comentó que, cuando su hijo, que tuvo con Chrisean Rock y actualmente tiene2 años, cumpla la mayoría de edad, se lo llevará de samaritanas junto al Dandy de Barcelona y tendrán un festín los dos juntos con la mujer de compañía.</t>
+  </si>
+  <si>
+    <t>Blueface ha sido un rapero siempre envuelto en polémicas. Hace menos de un año salió de prisión tras pasar dos años encerrado por no cumplir los términos de su libertad condicional. Desde contar con el apoyo de Drake en 2018 hasta convertirse en más meme andante que músico.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Blueface</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> es un</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> padre ejemplar</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZVIlCrgnEy/</t>
+  </si>
+  <si>
+    <t>"Mírame con esos ojitos lindos" es lo que hay que decirle a Bad Bunny en referencia a sus ojitos dilatados.</t>
+  </si>
+  <si>
+    <t>Esta gira, con motivo de su álbum 'DeBÍ TiRAR MáS FOToS', está siendo muy dura y las diez fechas en el estadio Metropolitano de Madrid lo están dejando agotado, por lo que tirar de sustancias externas es una gran idea para mantener la energía bien alta.</t>
+  </si>
+  <si>
+    <t>La charca española ha elegido el concierto de Bad Bunny como el lugar máximo de reunión, colapsando incluso los alrededores del estadio aquellos que se quedaron sin entrada.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Menuda puestada lleva </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bad Bunny</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZaLQ-zifoE/</t>
+  </si>
+  <si>
+    <t>Simón Pérez da señales de mejora a pasos agigantados, mucho más recuperado de salud y dejando de lado sus adicciones. Una verdadera muestra de superación y convicción.</t>
+  </si>
+  <si>
+    <t>Con un físico el cual es el pináculo del bodybuilding, con su panza que representa la verdadera salud, se puede ver al maestro siendo feliz y haciendo actividades lúdicas en sus streams.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El maestro </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Simón Pérez</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> se encuentra muchísimo </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mejor</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZaMfNRTX1C/</t>
+  </si>
+  <si>
+    <t>En honor al mes del Orgullo, el futbolista brasileño Richarlison ha hecho un acto con el objetivo de hermanar a la comunidad futbolística con la comunidad LGTBIQ+.</t>
+  </si>
+  <si>
+    <t>Es bien sabido que en el panorama futbolístico poca representación del colectivo LGTBIQ4KFHD+ se puede ver, pero están aprovechando que este año coincide el mes del orgullo con el inicio del Mundial para crear ese enlace.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Richarlison</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> le enseña a patear a unos </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bujarrillas</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZcpOYSAPDr/</t>
+  </si>
+  <si>
+    <t>Claramente se refería a los Funko Pops, ¿no?</t>
+  </si>
+  <si>
+    <t>Jordi Wild ha entrevistado al crítico literario Jesús G. Maestro en su podcast The Wild Project, y entre muchas cosas de las que han hablado, como lo son la genialidad a la hora de escribir de Miguel de Cervantes, la importancia del amor, o el problema de la vivienda en España, también ha hecho un breve comentario sobre la infantilización de la sociedad actual.</t>
+  </si>
+  <si>
+    <t>Hace especial hincapié en los adultos que compran muñequitos, y pese a aclarar que no se refiere a todo tipo de muñequitos y se refiere a unos en especial, para que Jordi Wild no se sienta atacado, todo apunta a que se refiere a los Funko Pops, y justo Jordi tiene uno bien visible en el plano ahí apoyado en la mesa.</t>
+  </si>
+  <si>
+    <r>
+      <t>Jesús G. Maestro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hiere los sentimientos de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jordi Wild</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sin darse cuenta</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZfiR_rT7I1/</t>
+  </si>
+  <si>
+    <t>Estos dos aficionados mexicanos protagonizaron un momento muy panchístico al ser enfocados por las cámaras.</t>
+  </si>
+  <si>
+    <t>Ocurrió durante la celebración de un gol entre el partido de inauguración del Mundial entre México y Sudáfrica, que acabó 2-0, otorgando tres puntitos al conjunto azteca.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Primera </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>panchitada</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> del mundial</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZfoqa-lTWp/</t>
+  </si>
+  <si>
+    <t>El lateral izquierdo de la selección española y del Chelsea FC, Marc Cucurella, ha concedido recientemente una entrevista a la revista GQ bajo el ya clásico formato 'Los 10 Esenciales' donde distintas celebridades pasan por el plató de la revista para mostrar cuáles son los 10 objetos sin los que no puede vivir.</t>
+  </si>
+  <si>
+    <t>Su primer ítem consistía en el fuet típico español, donde comenta que ha intentado introducírselo a sus compañeros de equipo en Inglaterra, y aunque les gusta, son tímidos y desconfiados. Narra cómo se lo pasan en grande en la habitación del hotel, y cómo le gusta especialmente que sean gruesos.</t>
+  </si>
+  <si>
+    <r>
+      <t>Cucurella</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fuet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> out of context</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZf1TbXjq8q/</t>
+  </si>
+  <si>
+    <t>España es un experimento sociológico.</t>
+  </si>
+  <si>
+    <t>El Hormiguero, pese a la imagen que se ha ganado en el territorio español de programa casposo y boomer, es innegable que es el programa que se ve más gordo desde el punto de vista internacional, así que seguirá siendo muy atractivo durante mucho tiempo para las estrellas internacionales que vienen de fuera a promocionarse.</t>
+  </si>
+  <si>
+    <t>Es el caso de Tom Holland y Zendaya, quienes se casaron recientemente en secreto a principios de año, y esta sería su primera entrevista pública siendo marido y mujer, para promocionar la nueva película de Spiderman. Le han brindado esta oportunidad a nada más y nada menos que Pablo Motos.</t>
+  </si>
+  <si>
+    <t>Y el plantel de invitados que se queda para esta semana en el programa es cuanto menos curioso y una muestra de lo que es España. El día previo a la visita de la pareja de Hollywood visitarán el programa J. J. Vaquero y Pablo Chiapella, quien interpreta a Amador Rivas en La Que Se Avecina, y juntos son el epítome del cuñadismo, el cual es producto nacional. Al día siguiente, nada más y nada menos que Alberto Núñez Feijóo, el cabecilla de la organización terrorista conocida como 'Partido Popular', que lidera actualmente la oposición en el Congreso y planea derrocar a Pedro Sánchez. Para rematar la Niña Pastori, para redondear la marca España.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Tom Holland </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Zendaya</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> entre el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Capitán Salami</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Feijóo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> es surrealista</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZhMP0ejENq/</t>
+  </si>
+  <si>
+    <t>España es una nación completamente charquificada y no hay vuelta atrás. No supimos parar a Peldanyos a tiempo y ahora sufrimos las consecuencias.</t>
+  </si>
+  <si>
+    <t>En este vídeo podemos ver escenificada la visita del Papa León XIV a España, coincidiendo con los conciertos de Bad Bunny con su DeBí TiRAR MáS FOToS World Tour. El Papa León XIV recibió como obsequio un producto muy español, una smash burger con colores vomitivos, y le fue entregada a manos de algo todavía más típico español, dos barrigudos enanos con principios de alopecia.</t>
+  </si>
+  <si>
+    <t>Los gemelos de Alicante, el Dandy de Barcelona, David Evil y Pájaro Azul en un mismo vídeo. Este plantel mete miedo al miedo. Son los protagonistas de las parálisis de sueño que tengo cada noche. Zona Gemelos ha hecho un daño irreparable en la sociedad.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Resumen de la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>visita</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> del </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Papa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>España</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZhnqy1jp-j/</t>
+  </si>
+  <si>
+    <t>Joey Bragg, un actor y comediante que se hizo conocido por interpretar a Joey Rooney en la serie de Disney Channel llamada Liv y Maddie, protagonizada por Dove Cameron, fue entrevistado por Sam Salem en su podcast, y entre otras cosas, contó una curiosa anécdota sobre su época en el canal infantil.</t>
+  </si>
+  <si>
+    <t>Concretamente, habló del mítico spot publicitario que multitud de actores infantiles grabaron, el cual consistía en sujetar la varita mágica y dibujar el logo de Disney Channel inspirado en el afable Mickey Mouse. En el anuncio, cada uno tenía su oportunidad de llevar a cabo alguna acción jocosa ante la cámara, o de soltar algún comentario ingenioso. Hasta ahora se podría pensar que había completa libertad para ello, pero Joey supo encontrar el límite.</t>
+  </si>
+  <si>
+    <t>Al actor no se le ocurrió otra cosa mejor que hacer como que se introducía la varita por la puerta trasera y que la sacaba por la boca. Esto enfadó mucho al director de la grabación, ya que según él estaba faltándole el respeto a una gran institución muy respetada. Tuvo que acabar grabando una cuña muy alejada de lo que él tenía en mente, y bastante más comedida, sin llegar a soltar ninguna palabra.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La promo de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Disney Channel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> que le</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> censuraron</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZkxE5gz87M/</t>
+  </si>
+  <si>
+    <t>Zlatan Ibrahimovic fue preguntado por su predicción para el Brasil - Marruecos del Mundial 2026 en el programa en el que sale regularmente Thierry Henry.</t>
+  </si>
+  <si>
+    <t>Aprovechó la situación para lanzar una pullita a la selección de Marruecos, diciendo que ganó la Copa de Naciones Africana sin ganar la final contra Senegal, así que la calidad debe estar ahí o si no no se explica por qué ganaron. Aún así, le daba la victoria a la selección brasileña.</t>
+  </si>
+  <si>
+    <t>Finalmente el partido terminó en empate 1 a 1 entre ambas selecciones.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ibrahimovic </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">le tira beef a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Marruecos</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZk-KfhjNJW/</t>
+  </si>
+  <si>
+    <t>El reportero quería seguir sonsacándole información a Marcos Llorente pero tenían el tiempo al cuello.</t>
+  </si>
+  <si>
+    <t>Los jugadores pagan multas por el tiempo que se atrasan en llegar al entrenamiento, y Llorente no iba a permitir que dos jueguecillos cutres para hacerle nombrar a compañeros de equipo le hiciese llegar tarde.</t>
+  </si>
+  <si>
+    <t>El entrevistador se pensó por un momento cubrir los gastos de la multa pero rápidamente se arrepintió al ver que no podía costeárselo.</t>
+  </si>
+  <si>
+    <r>
+      <t>Llorente</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> llevaba demasiado rato expuesto a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>luz artificial</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZk-7Btjkjf/</t>
+  </si>
+  <si>
+    <t>Recibimos la triste noticia de que Gaspi ha fallecido a sus 23 años en un accidente de helicóptero en Brasil junto al cantante estadounidense Oliver Tree.</t>
+  </si>
+  <si>
+    <t>El youtuber argentino conocido por su humor negro y por su característica irreverencia grababa principalmente vídeos haciendo de reportero bizarro en las calles de Argentina y más recientemente se le podía ver esa faceta de cineasta que siempre había querido mostrar.</t>
+  </si>
+  <si>
+    <t>El que boxeó en la última Velada de Ibai hoy en día lamentablemente ya no se encuentra entre nosotros. Nos demostró a través de sus vídeos y entrevistas (como la que dio en el podcast The Wild Project de Jordi Wild) lo mucho que había madurado, tras varios años de altibajos, excesos y problemas personales, y el joven tenía un brillante futuro por delante, que ahora lamentablemente no será posible realizar. Descanse en paz Gaspar Prim Díaz.</t>
+  </si>
+  <si>
+    <t>Descanse en paz Gaspi a sus 23 años</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZnkuYKDKNA/</t>
+  </si>
+  <si>
+    <t>España ha empatado su primer partido de este Mundial contra Cabo Verde con prácticamente ningún jugador español dando la talla, y pese a tener la mayoría del tiempo el balón, no logrando conectar para anotar algún gol.</t>
+  </si>
+  <si>
+    <t>El portero rival, Vozinha, de 40 años, ha estado imbatible y ha sido la absoluta revelación del partido.</t>
+  </si>
+  <si>
+    <t>Quizás cuando ha entrado Lamine Yamal al campo, en el minuto 71, se ha tenido un poco de esperanza, pero no ha habido suficiente tiempo para hacerse con la victoria.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Resumen de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pedri</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> contra </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cabo Verde</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZnmewaDXID/</t>
+  </si>
+  <si>
+    <t>Metan esto en un edit de Top Respect Moments in Football.</t>
+  </si>
+  <si>
+    <t>En el Costa de Marfil - Ecuador, estos dos jugadores representaron un momento digno de premio Nobel cuando, tras una confrontación, evitaron pelearse, establecieron la paz mundial, se abrazaron y cantaron Imagine de John Lennon al unísono.</t>
+  </si>
+  <si>
+    <t>El ecuatoriano Moisés Caicedo logró ecualizar la llama interna de un Christ Inao Oulaï que estaba engorilado tras la falta que recibió, pero de inmediato entendió que la violencia no era la solución. Un aplauso para estos dos civilizados zagales.</t>
+  </si>
+  <si>
+    <r>
+      <t>Iban a darse de hostias</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pero recordaron que</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> simio no mata simio</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZp_s3nTQmQ/</t>
+  </si>
+  <si>
+    <t>Menos mal que fue con perdón.</t>
+  </si>
+  <si>
+    <t>Nunca es mal momento para recordar esta rueda de prensa de Julen Lopetegui cuando era entrenador del Sevilla FC.</t>
+  </si>
+  <si>
+    <t>El que más adelante fue en un visto y no visto seleccionador de España y entrenador del Real Madrid, quería dibujar una situación con los números y no se le acabó de entender bien.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cómo olvidar estas </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>declaraciones</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lopetegui</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZqJit_D58S/</t>
+  </si>
+  <si>
+    <t>Mientras todos estamos conmovidos con el fallecimiento del youtuber argentino Gaspi, muchos influencers han aprovechado el suceso para decir orgullosos lo mucho que conocían a Gaspi, lo gran amigos que eran, y lo mucho que les ha afectado la tragedia.</t>
+  </si>
+  <si>
+    <t>En un stream de MrStiven, el cantante De La Ghetto mostró que hace apenas una semana Gaspi le respondió a una story de Instagram en la que salía el cantante como invitado sorpresa en el concierto de Bad Bunny en Madrid, y le respondió de vuelta.</t>
+  </si>
+  <si>
+    <t>Según relata él, vio que Gaspi le seguía, así que decidió seguirle de vuelta, y eso fue lo que provocó su muerte. Actualmente la policía está investigando al cantante puertorriqueño.</t>
+  </si>
+  <si>
+    <t>Gaspi murió porque De La Ghetto le dio follow</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZsEaY1iQ9f/</t>
+  </si>
+  <si>
+    <t>Si buceamos en el archivo de la televisión nacional española logramos dar con el looksmaxxer primigenio, un gigachad con un mentón envidiable que parece sacado de Jojo's, el cianotipo que ha servido de guía para todos los demás que han venido después. Mucho anterior a Zyzz o a Rafa Mora, este contenido videográfico data de 2005.</t>
+  </si>
+  <si>
+    <t>Ni Kappah, ni Simón Pérez, ni mucho menos Rubenmaxxing. El looksmaxxer más antiguo de este país es este chico que apareció en el mítico Diario de Patricia y tenía claras sus prioridades en la vida: cultivar su cuerpo y dejar de lado todo lo demás. Cuando la presentadora le pregunta por qué nunca le ha preocupado no cultivar la mente, los niveles de cortisol de este looksmaxxer no se ven ni inmutados.</t>
+  </si>
+  <si>
+    <t>Me pregunto qué será hoy en día de este genio con las cejas pintadas. ¿Habrá perseguido su sueño de ascender? ¿O habrá sucumbido a la sociedad para encajar?</t>
+  </si>
+  <si>
+    <t>El looksmaxxer primigenio</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZsIYBhz2Ds/</t>
+  </si>
+  <si>
+    <t>Enrique Cerezo está más gaga que Florentino, y mira que es difícil.</t>
+  </si>
+  <si>
+    <t>El presidente del Atlético de Madrid fue arroyado con preguntas sobre el temita del momento: la continuidad del argentino Julián Álvarez entre las filas del Atleti, y las diferentes ofertas que le llegan por el jugador, entre ellas la del Real Madrid de Florentino Pérez.</t>
+  </si>
+  <si>
+    <t>Al contestar, Cerezo comete un gazapo fruto de su profundo amor por el vino, y menciona a Julián López, reconocido actor español muy chanante, diciendo que en su contrato figura como jugador del Atleti y cuando eso cambie se enterarán.</t>
+  </si>
+  <si>
+    <t>Esto se suma a esa colección de momentos míticos que Enrique Cerezo nos daba al salir de esas comidas de empresa en las que la sobremesa se alargaba de más, donde se inventó a jugadores como Tom Ford o Smith.</t>
+  </si>
+  <si>
+    <t>Julián López se une a Tom Ford y Smith</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZ0XQKzTwp0/</t>
+  </si>
+  <si>
+    <t>Por lo que sea, en esta tienda de Adidas, las equipaciones con alarma antirrobo son las de Marruecos y Argelia.</t>
+  </si>
+  <si>
+    <t>Por lo que sea estas son las camisetas con alarma antirrobo</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZ2wHMpzuiB/</t>
+  </si>
+  <si>
+    <t>Arda Guler está carrileando la selección turca. O eso es lo que él piensa.</t>
+  </si>
+  <si>
+    <t>A Turquía no se le está dando nada bien este Mundial. Su clasificación pasada la fase de grupos está en peligro, y su estrella Arda Guler no acaba de dar buenos resultados.</t>
+  </si>
+  <si>
+    <t>Resumen de Arda Guler en este mundial</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZ7x1rtTDij/</t>
+  </si>
+  <si>
+    <t>Según medios brasileños, Raphinha podría estar planteándose abandonar la Copa del Mundo para gestionar algunos problemas personales y su supuesta crisis financiera que ha salido a la luz recientemente.</t>
+  </si>
+  <si>
+    <t>Al parecer el jugador del FC Barcelona no tiene suficiente cobrando 1,39 millones mensuales y como buen brasileño ha gestionado mal su patrimonio.</t>
+  </si>
+  <si>
+    <t>Raphinha arreglando sus problemas financieros</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZ-eX3rzfCa/</t>
+  </si>
+  <si>
+    <t>Y pensar que estos dos van a ser compañeros de equipo</t>
+  </si>
+  <si>
+    <t>Marc Cucurella es uno de los recientes fichajes del Real Madrid, y va a cumplir su sueño de ser compañero de equipo del dictador Kylian Mbappé.</t>
+  </si>
+  <si>
+    <t>Con este dato, no hay que olvidar esta interacción que tuvieron estos dos futbolistas cuando se enfrentaron con sus respectivas selecciones.</t>
+  </si>
+  <si>
+    <t>Va a haber muy buen ambiente en el vestuario del Real Madrid sin duda.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DaAPyzJz8jU/</t>
+  </si>
+  <si>
+    <t>Este es Yaw Dabo, un actor y comediante ghanés de 28 años, muy popular en su país, que cuenta con una estatura excepcionalmente baja.</t>
+  </si>
+  <si>
+    <t>A simple vista puede confundirse con un afable niño, y eso es justo lo que le pasó al futbolista inglés Jude Bellingham, que al saludarlo durante este Mundial en Estados Unidos le estrujó los mofletes y le frotó la cabecilla.</t>
+  </si>
+  <si>
+    <t>Para ponernos en perspectiva: Bellingham es del año 2003 y cumple este mes de junio 23 años, lo que lo hace 5 años menor que el supuesto niño. Es el nuevo Hasbulla, solo que más tostado.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bellingham </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>se pensó que este</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> enano </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>era un</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> niño</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DaDoS3djEU8/</t>
+  </si>
+  <si>
+    <t>Ecuador ha ganado a Alemania en un frenético partido y logra clasificar a dieciseisavos de este Mundial.</t>
+  </si>
+  <si>
+    <t>Todos los aficionados ecuatorianos residentes en España se han lanzado a las calles a celebrarlo, y están prendiendo su material de trabajo de Glovo y celebrándolo por todo lo grande.</t>
+  </si>
+  <si>
+    <t>Aficionados de Ecuador liándola tras clasificarse en el Mundial</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DaDyiC5jDnd/</t>
+  </si>
+  <si>
+    <t>Inolvidable este momento del dictador Kylian Mbappé, cuando agarró la muñeca del árbitro para señalarle el reloj.</t>
+  </si>
+  <si>
+    <t>Mbappé no es consciente de lo graciosos que son sus manierismos vistos desde fuera. Nunca cambies, dictadorcillo francés.</t>
+  </si>
+  <si>
+    <t>El dictador Mbappé no es consciente de lo gracioso que es</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DaGE-1CzIaK/</t>
+  </si>
+  <si>
+    <t>En una pachanguilla entre streamers americanos organizada por Tota, participaron los futbolistas Paul Pogba y Marcelo Vieira.</t>
+  </si>
+  <si>
+    <t>El defensa brasileño de 38 años dejó claro por qué fue un jugador élite, ya que sin necesidad de cansarse en exceso, jugó demostrando calidad en cada una de sus jugadas.</t>
+  </si>
+  <si>
+    <t>En este ejemplo, se le puede ver metiendo un gol de tacón sin mirar a la portería con el que Tota, que le había hecho el pase, enloquece.</t>
+  </si>
+  <si>
+    <r>
+      <t>Marcelo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> demuestra que la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>calidad</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nunca se pierde</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DaI15LgzJos/</t>
+  </si>
+  <si>
+    <t>El uruguayo Agustín Canobbio fue expulsado en el partido contra España en una fuerte entrada contra Pau Cubarsí en el minuto 95.</t>
+  </si>
+  <si>
+    <t>Lo sorprendente es que esa tarjeta roja no llegase antes, y es que el partido fue una completa carnicería por parte de los uruguayos. En la acción en la que Nicolás de la Cruz recibió una tarjeta amarilla por lesionar a Nico Williams, Canobbio se acercó acelerado al punto caliente y apartó de forma agresiva el brazo del árbitro, ante lo cual este no reaccionó.</t>
+  </si>
+  <si>
+    <r>
+      <t>Canobbio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tendría que haberse ido </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>expulsado</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en este momento</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DaYD6H4TNPi/</t>
+  </si>
+  <si>
+    <t>Si alguien se está gozando este Mundial es el panda Borja Iglesias.</t>
+  </si>
+  <si>
+    <t>Muy lejos de preocuparse por no tener minutos en el terreno de juego, el menda más bien se lo está gozando con sus compañeros de selección y cobrando todas las primas por avanzar de fases.</t>
+  </si>
+  <si>
+    <t>En este Mundial a la selección española le está yendo francamente bien. Acaban de pasar de dieciseisavos contra Austria con un fulminante 3-0 en el que han brillado jugadores como Oyarzabal o Pedro Porro.</t>
+  </si>
+  <si>
+    <r>
+      <t>Borja Iglesias</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sin jugar un partido pero </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cobrando</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> todas las primas</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DaakdDsTnbN/</t>
+  </si>
+  <si>
+    <t>Esto es lo más cerca que ha estado Kylian Mbappé de sujetar la orejona.</t>
+  </si>
+  <si>
+    <t>En el partido entre Francia y Paraguay, pudo experimentar un poco lo que es alzar el trofeo de la Champions League cuando le tocó ser marcado por el defensa paraguayo Juan José Cáceres, el cual tiene el mote cariñoso de nambi radar.</t>
+  </si>
+  <si>
+    <t>La Champions es un torneo que se la ha resistido siempre a Mbappé, casi que huye de él. Se fue del PSG al Real Madrid, equipo que las ganaba sin parar, para empezar la sequía blanca de Champions. Y su marcha del PSG desencadenó que el equipo francés ganara dos seguidas.</t>
+  </si>
+  <si>
+    <t>Lo más cerca que ha estado Mbappé de sujetar la Champions</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DadOtaaTJtG/</t>
+  </si>
+  <si>
+    <t>El delantero inglés Harry Kane ha representado en una entrevista postpartido lo que es un guiri promedio de vacaciones en Benidorm tras unos días de fiesta.</t>
+  </si>
+  <si>
+    <t>La periodista entrevistó a Harry Kane tras un partido en el que Inglaterra ganó a México por 3 goles contra 2, donde Harry marcó un penalti y Jude Bellingham metió un doblete.</t>
+  </si>
+  <si>
+    <t>Kane lo dio todo, hasta tal punto de que estaba completamente afónico.</t>
+  </si>
+  <si>
+    <r>
+      <t>Guiri promedio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> después de tres días seguidos de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fiesta</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/Daf1DW3TP6v/</t>
+  </si>
+  <si>
+    <t>Pedri tuvo uno de sus partidos más soporíferos en mucho tiempo con la selección española.</t>
+  </si>
+  <si>
+    <t>No fue ni top 3 mejores Pedros del partido.</t>
+  </si>
+  <si>
+    <t>Esta es una actuación que te podría perfectamente firmar Dani Ceballos, si supiese firmar, claro.</t>
+  </si>
+  <si>
+    <t>El partido de Pedri te lo firma Ceballos si supiese firmar</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DagIOVuT-QQ/</t>
+  </si>
+  <si>
+    <t>El bicholover iShowSpeed logró ponerle una maldición a Leo Messi como el chamán ese africano que le puso una a Harry Kane.</t>
+  </si>
+  <si>
+    <t>Durante el Argentina - Egipto, el streamer estadounidense Speed, que se encontraba justo detrás de la portería, logró con sus gestos distraer a Messi, quien acabó fallando el penalti.</t>
+  </si>
+  <si>
+    <t>Argentina acabó remontando un partido que estaba prácticamente perdido marcando 3 goles en unos 15 minutos, donde el juego de Messi fue clave.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Messi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> falló el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>penalti</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> porque </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IShowSpeed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> logró distraerlo</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DagTsEFzXnQ/</t>
+  </si>
+  <si>
+    <t>Lautaro del Campo, también conocido como La Cobra, es el mejor streamer de fútbol con mucha diferencia del segundo.</t>
+  </si>
+  <si>
+    <t>Su retransmisión del partido entre Egipto y Argentina fue iniciada con un entrañable momento en el que los jugadores de la selección argentina acogieron al streamer durante su calentamiento.</t>
+  </si>
+  <si>
+    <t>En un instante se vio agotado y tuvo que dejar al equipo a su suerte, el cual logró ganar el partido pero con muchas dificultades.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">thinks he's on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DapO-i7CJas/</t>
+  </si>
+  <si>
+    <t>Mikel Merino lo ha vuelto a hacer. Ya lo hizo en el partido pasado con Portugal, marcando el gol de la victoria en el minuto 90+1, pero por si eso no fuera poco, también ha marcado el gol de la victoria en cuartos de final contra Bélgica.</t>
+  </si>
+  <si>
+    <t>Esta vez, en el minuto 88, Merino ha logrado materializar un gol para España que les permite avanzar a semifinales, la cual será contra Francia.</t>
+  </si>
+  <si>
+    <t>Mikel Merino es como tu colega el que llega tardísimo a la fiesta y aún así triunfa.</t>
+  </si>
+  <si>
+    <r>
+      <t>Mikel Merino</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> es el típico colega que llega a la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fiesta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a las 3:30AM y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>folla</t>
     </r>
   </si>
 </sst>
@@ -25597,7 +26911,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
@@ -38072,7 +39386,7 @@
       <c r="D367" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F367" s="9" t="s">
+      <c r="F367" s="6" t="s">
         <v>2017</v>
       </c>
       <c r="H367" s="6">
@@ -38101,7 +39415,7 @@
       <c r="D368" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F368" s="9" t="s">
+      <c r="F368" s="6" t="s">
         <v>2023</v>
       </c>
       <c r="H368" s="6">
@@ -38128,12 +39442,12 @@
         <v>681</v>
       </c>
       <c r="C369" s="2">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="D369" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F369" s="9" t="s">
+      <c r="F369" s="6" t="s">
         <v>2025</v>
       </c>
       <c r="H369" s="6">
@@ -38154,9 +39468,9 @@
         <v>683</v>
       </c>
       <c r="C370" s="2">
-        <v>46144</v>
-      </c>
-      <c r="F370" s="9" t="s">
+        <v>46175</v>
+      </c>
+      <c r="F370" s="6" t="s">
         <v>2031</v>
       </c>
       <c r="H370" s="6">
@@ -38177,12 +39491,12 @@
         <v>684</v>
       </c>
       <c r="C371" s="2">
-        <v>46144</v>
+        <v>46175</v>
       </c>
       <c r="D371" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F371" s="9" t="s">
+      <c r="F371" s="6" t="s">
         <v>2035</v>
       </c>
       <c r="H371" s="6">
@@ -38203,7 +39517,7 @@
         <v>685</v>
       </c>
       <c r="C372" s="2">
-        <v>46144</v>
+        <v>46175</v>
       </c>
       <c r="D372" s="6" t="s">
         <v>31</v>
@@ -38232,12 +39546,12 @@
         <v>686</v>
       </c>
       <c r="C373" s="2">
-        <v>46144</v>
+        <v>46175</v>
       </c>
       <c r="D373" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F373" s="9" t="s">
+      <c r="F373" s="6" t="s">
         <v>2045</v>
       </c>
       <c r="H373" s="6">
@@ -38261,12 +39575,12 @@
         <v>687</v>
       </c>
       <c r="C374" s="2">
-        <v>46144</v>
+        <v>46175</v>
       </c>
       <c r="D374" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F374" s="9" t="s">
+      <c r="F374" s="6" t="s">
         <v>2050</v>
       </c>
       <c r="H374" s="6">
@@ -38292,7 +39606,7 @@
       <c r="D375" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F375" s="9" t="s">
+      <c r="F375" s="6" t="s">
         <v>2052</v>
       </c>
       <c r="H375" s="6">
@@ -38316,9 +39630,9 @@
         <v>693</v>
       </c>
       <c r="C376" s="2">
-        <v>46145</v>
-      </c>
-      <c r="F376" s="9" t="s">
+        <v>46176</v>
+      </c>
+      <c r="F376" s="6" t="s">
         <v>2060</v>
       </c>
       <c r="H376" s="6">
@@ -38342,9 +39656,9 @@
         <v>694</v>
       </c>
       <c r="C377" s="2">
-        <v>46145</v>
-      </c>
-      <c r="F377" s="9" t="s">
+        <v>46176</v>
+      </c>
+      <c r="F377" s="6" t="s">
         <v>2065</v>
       </c>
       <c r="H377" s="6">
@@ -38368,7 +39682,7 @@
         <v>695</v>
       </c>
       <c r="C378" s="2">
-        <v>46145</v>
+        <v>46176</v>
       </c>
       <c r="D378" s="6" t="s">
         <v>39</v>
@@ -38397,9 +39711,9 @@
         <v>698</v>
       </c>
       <c r="C379" s="7">
-        <v>46146</v>
-      </c>
-      <c r="F379" s="9" t="s">
+        <v>46177</v>
+      </c>
+      <c r="F379" s="6" t="s">
         <v>2075</v>
       </c>
       <c r="H379" s="6">
@@ -38423,12 +39737,12 @@
         <v>700</v>
       </c>
       <c r="C380" s="7">
-        <v>46146</v>
+        <v>46177</v>
       </c>
       <c r="D380" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F380" s="9" t="s">
+      <c r="F380" s="6" t="s">
         <v>2080</v>
       </c>
       <c r="H380" s="6">
@@ -38447,179 +39761,893 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="381" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B381" s="6">
         <v>705</v>
       </c>
-    </row>
-    <row r="382" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C381" s="7">
+        <v>46180</v>
+      </c>
+      <c r="D381" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F381" s="6" t="s">
+        <v>2085</v>
+      </c>
+      <c r="H381" s="6">
+        <v>161000</v>
+      </c>
+      <c r="I381" s="6" t="s">
+        <v>2081</v>
+      </c>
+      <c r="K381" s="3" t="s">
+        <v>2082</v>
+      </c>
+      <c r="L381" s="3" t="s">
+        <v>2083</v>
+      </c>
+      <c r="M381" s="3" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="382" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B382" s="6">
         <v>711</v>
       </c>
-    </row>
-    <row r="383" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C382" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D382" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F382" s="6" t="s">
+        <v>2090</v>
+      </c>
+      <c r="H382" s="6">
+        <v>294000</v>
+      </c>
+      <c r="I382" s="6" t="s">
+        <v>2086</v>
+      </c>
+      <c r="K382" s="3" t="s">
+        <v>2087</v>
+      </c>
+      <c r="L382" s="3" t="s">
+        <v>2088</v>
+      </c>
+      <c r="M382" s="3" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="383" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B383" s="6">
         <v>712</v>
       </c>
-    </row>
-    <row r="384" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C383" s="7">
+        <v>46183</v>
+      </c>
+      <c r="F383" s="6" t="s">
+        <v>2094</v>
+      </c>
+      <c r="H383" s="6">
+        <v>286000</v>
+      </c>
+      <c r="I383" s="6" t="s">
+        <v>2091</v>
+      </c>
+      <c r="K383" s="3" t="s">
+        <v>2092</v>
+      </c>
+      <c r="L383" s="3" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="384" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B384" s="6">
         <v>713</v>
       </c>
-    </row>
-    <row r="385" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C384" s="7">
+        <v>46183</v>
+      </c>
+      <c r="F384" s="6" t="s">
+        <v>2098</v>
+      </c>
+      <c r="H384" s="6">
+        <v>551000</v>
+      </c>
+      <c r="I384" s="6" t="s">
+        <v>2095</v>
+      </c>
+      <c r="K384" s="3" t="s">
+        <v>2096</v>
+      </c>
+      <c r="L384" s="3" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="385" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B385" s="6">
         <v>716</v>
       </c>
-    </row>
-    <row r="386" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C385" s="7">
+        <v>46184</v>
+      </c>
+      <c r="F385" s="5" t="s">
+        <v>2103</v>
+      </c>
+      <c r="H385" s="6">
+        <v>43000</v>
+      </c>
+      <c r="I385" s="6" t="s">
+        <v>2099</v>
+      </c>
+      <c r="K385" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="L385" s="3" t="s">
+        <v>2101</v>
+      </c>
+      <c r="M385" s="3" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="386" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B386" s="6">
         <v>719</v>
       </c>
-    </row>
-    <row r="387" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C386" s="7">
+        <v>46185</v>
+      </c>
+      <c r="F386" s="6" t="s">
+        <v>2107</v>
+      </c>
+      <c r="H386" s="6">
+        <v>59000</v>
+      </c>
+      <c r="I386" s="6" t="s">
+        <v>2104</v>
+      </c>
+      <c r="K386" s="3" t="s">
+        <v>2105</v>
+      </c>
+      <c r="L386" s="3" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="387" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B387" s="6">
         <v>720</v>
       </c>
-    </row>
-    <row r="388" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C387" s="7">
+        <v>46185</v>
+      </c>
+      <c r="F387" s="5" t="s">
+        <v>2111</v>
+      </c>
+      <c r="H387" s="6">
+        <v>139000</v>
+      </c>
+      <c r="I387" s="6" t="s">
+        <v>2108</v>
+      </c>
+      <c r="K387" s="3" t="s">
+        <v>2109</v>
+      </c>
+      <c r="L387" s="3" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="388" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B388" s="6">
         <v>722</v>
       </c>
-    </row>
-    <row r="389" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C388" s="7">
+        <v>46185</v>
+      </c>
+      <c r="F388" s="6" t="s">
+        <v>2117</v>
+      </c>
+      <c r="H388" s="6">
+        <v>92000</v>
+      </c>
+      <c r="I388" s="6" t="s">
+        <v>2112</v>
+      </c>
+      <c r="K388" s="3" t="s">
+        <v>2113</v>
+      </c>
+      <c r="L388" s="3" t="s">
+        <v>2114</v>
+      </c>
+      <c r="M388" s="3" t="s">
+        <v>2115</v>
+      </c>
+      <c r="N388" s="3" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="389" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B389" s="6">
         <v>723</v>
       </c>
-    </row>
-    <row r="390" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C389" s="7">
+        <v>46186</v>
+      </c>
+      <c r="F389" s="5" t="s">
+        <v>2122</v>
+      </c>
+      <c r="H389" s="6">
+        <v>152000</v>
+      </c>
+      <c r="I389" s="6" t="s">
+        <v>2118</v>
+      </c>
+      <c r="K389" s="3" t="s">
+        <v>2119</v>
+      </c>
+      <c r="L389" s="3" t="s">
+        <v>2120</v>
+      </c>
+      <c r="M389" s="3" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="390" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B390" s="6">
         <v>727</v>
       </c>
-    </row>
-    <row r="391" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C390" s="7">
+        <v>46186</v>
+      </c>
+      <c r="F390" s="6" t="s">
+        <v>2127</v>
+      </c>
+      <c r="H390" s="6">
+        <v>85000</v>
+      </c>
+      <c r="I390" s="6" t="s">
+        <v>2123</v>
+      </c>
+      <c r="K390" s="3" t="s">
+        <v>2124</v>
+      </c>
+      <c r="L390" s="3" t="s">
+        <v>2125</v>
+      </c>
+      <c r="M390" s="3" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="391" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B391" s="6">
         <v>729</v>
       </c>
-    </row>
-    <row r="392" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C391" s="7">
+        <v>46187</v>
+      </c>
+      <c r="F391" s="5" t="s">
+        <v>2132</v>
+      </c>
+      <c r="H391" s="6">
+        <v>192000</v>
+      </c>
+      <c r="I391" s="6" t="s">
+        <v>2128</v>
+      </c>
+      <c r="K391" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="L391" s="3" t="s">
+        <v>2130</v>
+      </c>
+      <c r="M391" s="3" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="392" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B392" s="6">
         <v>731</v>
       </c>
-    </row>
-    <row r="393" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C392" s="7">
+        <v>46187</v>
+      </c>
+      <c r="F392" s="5" t="s">
+        <v>2137</v>
+      </c>
+      <c r="H392" s="6">
+        <v>973000</v>
+      </c>
+      <c r="I392" s="6" t="s">
+        <v>2133</v>
+      </c>
+      <c r="K392" s="3" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L392" s="3" t="s">
+        <v>2135</v>
+      </c>
+      <c r="M392" s="3" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="393" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B393" s="6">
         <v>732</v>
       </c>
-    </row>
-    <row r="394" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C393" s="7">
+        <v>46187</v>
+      </c>
+      <c r="F393" s="5" t="s">
+        <v>2142</v>
+      </c>
+      <c r="H393" s="6">
+        <v>177000</v>
+      </c>
+      <c r="I393" s="6" t="s">
+        <v>2138</v>
+      </c>
+      <c r="K393" s="3" t="s">
+        <v>2139</v>
+      </c>
+      <c r="L393" s="3" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M393" s="3" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="394" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B394" s="6">
         <v>735</v>
       </c>
-    </row>
-    <row r="395" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C394" s="7">
+        <v>46188</v>
+      </c>
+      <c r="F394" s="5" t="s">
+        <v>2147</v>
+      </c>
+      <c r="H394" s="6">
+        <v>1800000</v>
+      </c>
+      <c r="I394" s="6" t="s">
+        <v>2143</v>
+      </c>
+      <c r="K394" s="3" t="s">
+        <v>2144</v>
+      </c>
+      <c r="L394" s="3" t="s">
+        <v>2145</v>
+      </c>
+      <c r="M394" s="3" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="395" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B395" s="6">
         <v>736</v>
       </c>
-    </row>
-    <row r="396" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C395" s="7">
+        <v>46188</v>
+      </c>
+      <c r="F395" s="5" t="s">
+        <v>2152</v>
+      </c>
+      <c r="H395" s="6">
+        <v>389000</v>
+      </c>
+      <c r="I395" s="6" t="s">
+        <v>2148</v>
+      </c>
+      <c r="K395" s="3" t="s">
+        <v>2149</v>
+      </c>
+      <c r="L395" s="3" t="s">
+        <v>2150</v>
+      </c>
+      <c r="M395" s="3" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="396" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B396" s="6">
         <v>740</v>
       </c>
-    </row>
-    <row r="397" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C396" s="7">
+        <v>46189</v>
+      </c>
+      <c r="F396" s="9" t="s">
+        <v>2157</v>
+      </c>
+      <c r="H396" s="6">
+        <v>65000</v>
+      </c>
+      <c r="I396" s="6" t="s">
+        <v>2153</v>
+      </c>
+      <c r="K396" s="3" t="s">
+        <v>2154</v>
+      </c>
+      <c r="L396" s="3" t="s">
+        <v>2155</v>
+      </c>
+      <c r="M396" s="3" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="397" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B397" s="6">
         <v>741</v>
       </c>
-    </row>
-    <row r="398" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C397" s="7">
+        <v>46189</v>
+      </c>
+      <c r="F397" s="5" t="s">
+        <v>2162</v>
+      </c>
+      <c r="H397" s="6">
+        <v>280000</v>
+      </c>
+      <c r="I397" s="6" t="s">
+        <v>2158</v>
+      </c>
+      <c r="K397" s="3" t="s">
+        <v>2159</v>
+      </c>
+      <c r="L397" s="3" t="s">
+        <v>2160</v>
+      </c>
+      <c r="M397" s="3" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="398" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B398" s="6">
         <v>743</v>
       </c>
-    </row>
-    <row r="399" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C398" s="7">
+        <v>46190</v>
+      </c>
+      <c r="F398" s="5" t="s">
+        <v>2167</v>
+      </c>
+      <c r="H398" s="6">
+        <v>476000</v>
+      </c>
+      <c r="I398" s="6" t="s">
+        <v>2163</v>
+      </c>
+      <c r="K398" s="3" t="s">
+        <v>2164</v>
+      </c>
+      <c r="L398" s="3" t="s">
+        <v>2165</v>
+      </c>
+      <c r="M398" s="3" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="399" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B399" s="6">
         <v>744</v>
       </c>
-    </row>
-    <row r="400" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C399" s="7">
+        <v>46190</v>
+      </c>
+      <c r="F399" s="5" t="s">
+        <v>2173</v>
+      </c>
+      <c r="H399" s="6">
+        <v>399000</v>
+      </c>
+      <c r="I399" s="6" t="s">
+        <v>2168</v>
+      </c>
+      <c r="K399" s="3" t="s">
+        <v>2169</v>
+      </c>
+      <c r="L399" s="3" t="s">
+        <v>2170</v>
+      </c>
+      <c r="M399" s="3" t="s">
+        <v>2171</v>
+      </c>
+      <c r="N399" s="3" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="400" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B400" s="6">
         <v>750</v>
       </c>
-    </row>
-    <row r="401" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C400" s="7">
+        <v>46193</v>
+      </c>
+      <c r="F400" s="5" t="s">
+        <v>2176</v>
+      </c>
+      <c r="H400" s="6">
+        <v>238000</v>
+      </c>
+      <c r="I400" s="6" t="s">
+        <v>2174</v>
+      </c>
+      <c r="K400" s="3" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="401" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B401" s="6">
         <v>751</v>
       </c>
-    </row>
-    <row r="402" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C401" s="7">
+        <v>46194</v>
+      </c>
+      <c r="F401" s="5" t="s">
+        <v>2180</v>
+      </c>
+      <c r="H401" s="6">
+        <v>139000</v>
+      </c>
+      <c r="I401" s="6" t="s">
+        <v>2177</v>
+      </c>
+      <c r="K401" s="3" t="s">
+        <v>2178</v>
+      </c>
+      <c r="L401" s="3" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="402" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B402" s="6">
         <v>755</v>
       </c>
-    </row>
-    <row r="403" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C402" s="7">
+        <v>46196</v>
+      </c>
+      <c r="F402" s="5" t="s">
+        <v>2184</v>
+      </c>
+      <c r="H402" s="6">
+        <v>506000</v>
+      </c>
+      <c r="I402" s="6" t="s">
+        <v>2181</v>
+      </c>
+      <c r="K402" s="3" t="s">
+        <v>2182</v>
+      </c>
+      <c r="L402" s="3" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="403" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B403" s="6">
         <v>758</v>
       </c>
-    </row>
-    <row r="404" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C403" s="7">
+        <v>46197</v>
+      </c>
+      <c r="F403" s="5" t="s">
+        <v>2186</v>
+      </c>
+      <c r="H403" s="6">
+        <v>2900000</v>
+      </c>
+      <c r="I403" s="6" t="s">
+        <v>2185</v>
+      </c>
+      <c r="K403" s="3" t="s">
+        <v>2187</v>
+      </c>
+      <c r="L403" s="3" t="s">
+        <v>2188</v>
+      </c>
+      <c r="M403" s="3" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="404" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B404" s="6">
         <v>759</v>
       </c>
-    </row>
-    <row r="405" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C404" s="7">
+        <v>46198</v>
+      </c>
+      <c r="F404" s="5" t="s">
+        <v>2194</v>
+      </c>
+      <c r="H404" s="6">
+        <v>129000</v>
+      </c>
+      <c r="I404" s="6" t="s">
+        <v>2190</v>
+      </c>
+      <c r="K404" s="3" t="s">
+        <v>2191</v>
+      </c>
+      <c r="L404" s="3" t="s">
+        <v>2192</v>
+      </c>
+      <c r="M404" s="3" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="405" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B405" s="6">
         <v>762</v>
       </c>
-    </row>
-    <row r="406" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C405" s="7">
+        <v>46199</v>
+      </c>
+      <c r="F405" s="5" t="s">
+        <v>2198</v>
+      </c>
+      <c r="H405" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="I405" s="6" t="s">
+        <v>2195</v>
+      </c>
+      <c r="K405" s="3" t="s">
+        <v>2196</v>
+      </c>
+      <c r="L405" s="3" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="406" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B406" s="6">
         <v>764</v>
       </c>
-    </row>
-    <row r="407" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C406" s="7">
+        <v>46199</v>
+      </c>
+      <c r="F406" s="5" t="s">
+        <v>2202</v>
+      </c>
+      <c r="H406" s="6">
+        <v>2500000</v>
+      </c>
+      <c r="I406" s="6" t="s">
+        <v>2199</v>
+      </c>
+      <c r="K406" s="3" t="s">
+        <v>2200</v>
+      </c>
+      <c r="L406" s="3" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="407" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B407" s="6">
         <v>767</v>
       </c>
-    </row>
-    <row r="408" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C407" s="7">
+        <v>46200</v>
+      </c>
+      <c r="F407" s="5" t="s">
+        <v>2207</v>
+      </c>
+      <c r="H407" s="6">
+        <v>857000</v>
+      </c>
+      <c r="I407" s="6" t="s">
+        <v>2203</v>
+      </c>
+      <c r="K407" s="3" t="s">
+        <v>2204</v>
+      </c>
+      <c r="L407" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="M407" s="3" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="408" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B408" s="6">
         <v>770</v>
       </c>
-    </row>
-    <row r="409" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C408" s="7">
+        <v>46201</v>
+      </c>
+      <c r="F408" s="5" t="s">
+        <v>2211</v>
+      </c>
+      <c r="H408" s="6">
+        <v>227000</v>
+      </c>
+      <c r="I408" s="6" t="s">
+        <v>2208</v>
+      </c>
+      <c r="K408" s="3" t="s">
+        <v>2209</v>
+      </c>
+      <c r="L408" s="3" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="409" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B409" s="6">
         <v>774</v>
       </c>
-    </row>
-    <row r="410" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C409" s="7">
+        <v>46207</v>
+      </c>
+      <c r="F409" s="5" t="s">
+        <v>2216</v>
+      </c>
+      <c r="H409" s="6">
+        <v>1800000</v>
+      </c>
+      <c r="I409" s="6" t="s">
+        <v>2212</v>
+      </c>
+      <c r="K409" s="3" t="s">
+        <v>2213</v>
+      </c>
+      <c r="L409" s="3" t="s">
+        <v>2214</v>
+      </c>
+      <c r="M409" s="3" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="410" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B410" s="6">
         <v>775</v>
       </c>
-    </row>
-    <row r="411" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C410" s="7">
+        <v>46208</v>
+      </c>
+      <c r="F410" s="5" t="s">
+        <v>2221</v>
+      </c>
+      <c r="H410" s="6">
+        <v>1100000</v>
+      </c>
+      <c r="I410" s="6" t="s">
+        <v>2217</v>
+      </c>
+      <c r="K410" s="3" t="s">
+        <v>2218</v>
+      </c>
+      <c r="L410" s="3" t="s">
+        <v>2219</v>
+      </c>
+      <c r="M410" s="3" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="411" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B411" s="6">
         <v>776</v>
       </c>
-    </row>
-    <row r="412" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C411" s="7">
+        <v>46209</v>
+      </c>
+      <c r="F411" s="5" t="s">
+        <v>2226</v>
+      </c>
+      <c r="H411" s="6">
+        <v>54000</v>
+      </c>
+      <c r="I411" s="6" t="s">
+        <v>2222</v>
+      </c>
+      <c r="K411" s="3" t="s">
+        <v>2223</v>
+      </c>
+      <c r="L411" s="3" t="s">
+        <v>2224</v>
+      </c>
+      <c r="M411" s="3" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="412" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B412" s="6">
         <v>779</v>
       </c>
-    </row>
-    <row r="413" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C412" s="7">
+        <v>46210</v>
+      </c>
+      <c r="F412" s="5" t="s">
+        <v>2231</v>
+      </c>
+      <c r="H412" s="6">
+        <v>238000</v>
+      </c>
+      <c r="I412" s="6" t="s">
+        <v>2227</v>
+      </c>
+      <c r="K412" s="3" t="s">
+        <v>2228</v>
+      </c>
+      <c r="L412" s="3" t="s">
+        <v>2229</v>
+      </c>
+      <c r="M412" s="3" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="413" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B413" s="6">
         <v>780</v>
       </c>
-    </row>
-    <row r="414" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C413" s="7">
+        <v>46210</v>
+      </c>
+      <c r="F413" s="9" t="s">
+        <v>2236</v>
+      </c>
+      <c r="H413" s="6">
+        <v>805000</v>
+      </c>
+      <c r="I413" s="6" t="s">
+        <v>2232</v>
+      </c>
+      <c r="K413" s="3" t="s">
+        <v>2233</v>
+      </c>
+      <c r="L413" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="M413" s="3" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="414" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B414" s="6">
         <v>781</v>
       </c>
-    </row>
-    <row r="415" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C414" s="7">
+        <v>46210</v>
+      </c>
+      <c r="F414" s="5" t="s">
+        <v>2241</v>
+      </c>
+      <c r="H414" s="6">
+        <v>988000</v>
+      </c>
+      <c r="I414" s="6" t="s">
+        <v>2237</v>
+      </c>
+      <c r="K414" s="3" t="s">
+        <v>2238</v>
+      </c>
+      <c r="L414" s="3" t="s">
+        <v>2239</v>
+      </c>
+      <c r="M414" s="3" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="415" spans="2:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B415" s="6">
         <v>784</v>
+      </c>
+      <c r="C415" s="7">
+        <v>46214</v>
+      </c>
+      <c r="F415" s="5" t="s">
+        <v>2246</v>
+      </c>
+      <c r="H415" s="6">
+        <v>5300000</v>
+      </c>
+      <c r="I415" s="6" t="s">
+        <v>2242</v>
+      </c>
+      <c r="K415" s="3" t="s">
+        <v>2243</v>
+      </c>
+      <c r="L415" s="3" t="s">
+        <v>2244</v>
+      </c>
+      <c r="M415" s="3" t="s">
+        <v>2245</v>
       </c>
     </row>
   </sheetData>
